--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -570,13 +570,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="D2" t="n">
-        <v>21.90414778532685</v>
+        <v>21.94736451349033</v>
       </c>
       <c r="E2" t="n">
-        <v>2.649441600808605</v>
+        <v>2.766768218662275</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.295412204256244</v>
+        <v>-1.343755282634725</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>0.1412456392075651</v>
+        <v>0.1463532815536431</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001484785124081059</v>
+        <v>0.001481861422009717</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001484785124081059</v>
+        <v>0.001481861422009717</v>
       </c>
       <c r="X2" t="n">
         <v>0.03252295278732637</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.093865355235462</v>
+        <v>3.212068818003286</v>
       </c>
     </row>
     <row r="3">
@@ -653,13 +653,13 @@
         <v>9.283333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>24.05923551807384</v>
+        <v>24.15921957614428</v>
       </c>
       <c r="E3" t="n">
-        <v>1.141303698996739</v>
+        <v>1.145676400792977</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8593776337987036</v>
+        <v>-0.9199320657109662</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.04656417835443825</v>
+        <v>0.04654885228669232</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004277320963704851</v>
+        <v>0.004259619071213121</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004017468428302058</v>
+        <v>0.004000927121195224</v>
       </c>
       <c r="X3" t="n">
         <v>0.1029090724521696</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.120298533735026</v>
+        <v>1.124583943411706</v>
       </c>
     </row>
     <row r="4">
@@ -736,13 +736,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>24.77268809228702</v>
+        <v>24.78520015052234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3909939650415275</v>
+        <v>0.3549297903157393</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.226662046390678</v>
+        <v>-0.2324157917266303</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.003842087191651498</v>
+        <v>0.002379050554110678</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003398407529152446</v>
+        <v>0.003396691945955462</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003350211476126097</v>
+        <v>0.003366863637048577</v>
       </c>
       <c r="X4" t="n">
         <v>0.08418768973017335</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09517882762215352</v>
+        <v>0.05896524415184423</v>
       </c>
     </row>
     <row r="5">
@@ -819,13 +819,13 @@
         <v>13.15</v>
       </c>
       <c r="D5" t="n">
-        <v>25.55755469146949</v>
+        <v>25.52936787515874</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4285991589614797</v>
+        <v>0.4247827633206231</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01374980761621421</v>
+        <v>0.02421244228691488</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.004644306008744943</v>
+        <v>0.00451333120799062</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002802332196263887</v>
+        <v>0.002805426233814838</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002718079287151608</v>
+        <v>0.002723458954427426</v>
       </c>
       <c r="X5" t="n">
         <v>0.07162075836968011</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1186971048224192</v>
+        <v>0.115222492751227</v>
       </c>
     </row>
     <row r="6">
@@ -902,13 +902,13 @@
         <v>15.15</v>
       </c>
       <c r="D6" t="n">
-        <v>26.52397387472312</v>
+        <v>26.51727820874701</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4485086783228001</v>
+        <v>0.4565985853136878</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01280234260742574</v>
+        <v>-0.01156002969159746</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -955,19 +955,19 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>0.004363500136320473</v>
+        <v>0.00467285042783293</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004286411711977421</v>
+        <v>0.004287494039538852</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004183164297161491</v>
+        <v>0.004176898982023491</v>
       </c>
       <c r="X6" t="n">
         <v>0.1136926722647963</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1157373636181149</v>
+        <v>0.1239112748227083</v>
       </c>
     </row>
     <row r="7">
@@ -985,13 +985,13 @@
         <v>17.1</v>
       </c>
       <c r="D7" t="n">
-        <v>27.33259068603333</v>
+        <v>27.336621249569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3802771695130964</v>
+        <v>0.3818331051817658</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02928478232179146</v>
+        <v>-0.03239071966445572</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1038,19 +1038,19 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>-0.003590733905795075</v>
+        <v>-0.003535867629664758</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008576982722137571</v>
+        <v>0.008575718115458847</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008700461953821473</v>
+        <v>0.008697292661400426</v>
       </c>
       <c r="X7" t="n">
         <v>0.2344311580653662</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.09814406010955845</v>
+        <v>-0.0966586741807568</v>
       </c>
     </row>
     <row r="8">
@@ -1068,13 +1068,13 @@
         <v>18.15</v>
       </c>
       <c r="D8" t="n">
-        <v>27.71243354711543</v>
+        <v>27.71586757332252</v>
       </c>
       <c r="E8" t="n">
-        <v>0.352754082873016</v>
+        <v>0.3511872001999183</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01812639682461964</v>
+        <v>-0.0201447979836277</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>-0.01066597591190639</v>
+        <v>-0.01072408683700126</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01245217194545731</v>
+        <v>0.0124506291077784</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01293505824701726</v>
+        <v>0.0129360861395104</v>
       </c>
       <c r="X8" t="n">
         <v>0.3450799875557407</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.2955801486738396</v>
+        <v>-0.297227370619138</v>
       </c>
     </row>
     <row r="9">
@@ -1151,13 +1151,13 @@
         <v>19.16666666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06220633394021</v>
+        <v>28.06306419986345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.342285434983685</v>
+        <v>0.3396073054888795</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.006786826796083723</v>
+        <v>-0.007464977064400441</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>-0.01986944509974919</v>
+        <v>-0.01996525050408979</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0172187913778917</v>
+        <v>0.01721826501290685</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01842874062079043</v>
+        <v>0.01843401115738567</v>
       </c>
       <c r="X9" t="n">
         <v>0.4831972764674675</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.5575804681300589</v>
+        <v>-0.5602861066626278</v>
       </c>
     </row>
     <row r="10">
@@ -1234,13 +1234,13 @@
         <v>20.13333333333334</v>
       </c>
       <c r="D10" t="n">
-        <v>28.39147068543616</v>
+        <v>28.38960715368643</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3389511543182806</v>
+        <v>0.3359988058690107</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0001116849254426677</v>
+        <v>-8.842180868606775e-07</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>-0.03026604090839843</v>
+        <v>-0.03036925123769535</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02162190239001286</v>
+        <v>0.02162332168057842</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02408736760693919</v>
+        <v>0.02409735677715759</v>
       </c>
       <c r="X10" t="n">
         <v>0.6138776078694121</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.8592974132150057</v>
+        <v>-0.8621711121897764</v>
       </c>
     </row>
     <row r="11">
@@ -1317,13 +1317,13 @@
         <v>10.5</v>
       </c>
       <c r="D11" t="n">
-        <v>26.69145309571078</v>
+        <v>26.90576270140085</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8134625588328568</v>
+        <v>0.4768870689450928</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.43954721797159</v>
+        <v>-1.884045409374397</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>0.03232851343233704</v>
+        <v>0.01957634192483895</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005776488224851725</v>
+        <v>0.005730477378495867</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00552884292313</v>
+        <v>0.005581711678475328</v>
       </c>
       <c r="X11" t="n">
         <v>0.1541828645115554</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8628949999332802</v>
+        <v>0.5267164103912014</v>
       </c>
     </row>
     <row r="12">
@@ -1400,13 +1400,13 @@
         <v>12.25</v>
       </c>
       <c r="D12" t="n">
-        <v>26.65311597876561</v>
+        <v>26.14540462095952</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.005810554401408652</v>
+        <v>-0.1807580605032388</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1637940475849494</v>
+        <v>-0.03320424263343408</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>-0.01119116119163786</v>
+        <v>-0.01788672368346078</v>
       </c>
       <c r="V12" t="n">
-        <v>0.003323907882975883</v>
+        <v>0.003388454055007017</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003517243579328763</v>
+        <v>0.003703461135519619</v>
       </c>
       <c r="X12" t="n">
         <v>0.08859250230768947</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.2982793171777847</v>
+        <v>-0.4676556280473815</v>
       </c>
     </row>
     <row r="13">
@@ -1483,13 +1483,13 @@
         <v>14.36666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>26.68202623302077</v>
+        <v>26.41239494873913</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4267071201364878</v>
+        <v>0.6260520196969441</v>
       </c>
       <c r="F13" t="n">
-        <v>0.224155456203944</v>
+        <v>0.2906134019905942</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>-0.002159116125110338</v>
+        <v>0.005551541158314535</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0006467522300865029</v>
+        <v>0.00065335460880864</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0006891476685905666</v>
+        <v>0.0005432342243975793</v>
       </c>
       <c r="X13" t="n">
         <v>0.01725665996943276</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0576095930903322</v>
+        <v>0.1466294976475842</v>
       </c>
     </row>
     <row r="14">
@@ -1566,13 +1566,13 @@
         <v>16.36666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>28.31600500677294</v>
+        <v>28.60921997767586</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9124663425295276</v>
+        <v>1.036148024359556</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06681355908669991</v>
+        <v>-0.08046043146725339</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>0.01660748072661906</v>
+        <v>0.02060035451617961</v>
       </c>
       <c r="V14" t="n">
-        <v>0.006991070313086991</v>
+        <v>0.006919419059399134</v>
       </c>
       <c r="W14" t="n">
-        <v>0.006655958281680099</v>
+        <v>0.006507997618334095</v>
       </c>
       <c r="X14" t="n">
         <v>0.1979591819880729</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4702575074048302</v>
+        <v>0.589360073971491</v>
       </c>
     </row>
     <row r="15">
@@ -1649,13 +1649,13 @@
         <v>18.3</v>
       </c>
       <c r="D15" t="n">
-        <v>30.25854242389568</v>
+        <v>30.49607407770099</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7125913349319077</v>
+        <v>0.3470076505793394</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2315382207953283</v>
+        <v>-0.5460393706624851</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1702,19 +1702,19 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>0.01987610556165762</v>
+        <v>0.007704782304053718</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02408237874456443</v>
+        <v>0.02389480288689215</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02321948068965366</v>
+        <v>0.02356291405558334</v>
       </c>
       <c r="X15" t="n">
         <v>0.7286976789107263</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.601421983359246</v>
+        <v>0.2349656118969819</v>
       </c>
     </row>
     <row r="16">
@@ -1732,13 +1732,13 @@
         <v>19.36666666666667</v>
       </c>
       <c r="D16" t="n">
-        <v>30.84669647792873</v>
+        <v>30.49607407770099</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3901975163800557</v>
+        <v>-0.3470076505793358</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3729501889893923</v>
+        <v>-0.7552393190100266</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1785,19 +1785,19 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>0.01802613182238104</v>
+        <v>-0.006002205126870144</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03668647152063631</v>
+        <v>0.03710826675459588</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03534134900753256</v>
+        <v>0.03756130499155563</v>
       </c>
       <c r="X16" t="n">
         <v>1.131656451843245</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5560466169961201</v>
+        <v>-0.1830436921785885</v>
       </c>
     </row>
     <row r="17">
@@ -1815,13 +1815,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D17" t="n">
-        <v>30.89887988078042</v>
+        <v>30.97593657564373</v>
       </c>
       <c r="E17" t="n">
-        <v>2.233794122914519</v>
+        <v>1.702464341763148</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.703333547076863</v>
+        <v>-1.99122392921793</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1868,19 +1868,19 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>0.07719764402011454</v>
+        <v>0.05986481881725748</v>
       </c>
       <c r="V17" t="n">
-        <v>0.002665044063479796</v>
+        <v>0.002658414417699906</v>
       </c>
       <c r="W17" t="n">
-        <v>0.002415380766685625</v>
+        <v>0.002465288474968639</v>
       </c>
       <c r="X17" t="n">
         <v>0.08234687639444917</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.385320729656766</v>
+        <v>1.854368830795771</v>
       </c>
     </row>
     <row r="18">
@@ -1898,13 +1898,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>32.44142377184905</v>
+        <v>32.06916300779451</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9335646748834137</v>
+        <v>0.8457530478826385</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.875063755176267</v>
+        <v>-0.4855263396745825</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>0.01596779318247201</v>
+        <v>0.01356364238017025</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001312865070175834</v>
+        <v>0.001328104886506724</v>
       </c>
       <c r="W18" t="n">
-        <v>0.001232617739754924</v>
+        <v>0.001259148530008072</v>
       </c>
       <c r="X18" t="n">
         <v>0.04259121209683257</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5180179453338167</v>
+        <v>0.4349746584691095</v>
       </c>
     </row>
     <row r="19">
@@ -1981,13 +1981,13 @@
         <v>11.96666666666666</v>
       </c>
       <c r="D19" t="n">
-        <v>32.94154030130098</v>
+        <v>32.74125786872719</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3599284067761737</v>
+        <v>0.6248667002441746</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3857770911210205</v>
+        <v>-0.2052850684266847</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2034,19 +2034,19 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>-0.01304869134972544</v>
+        <v>-0.004889975030627713</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0008976812172023368</v>
+        <v>0.0009031724472148775</v>
       </c>
       <c r="W19" t="n">
-        <v>0.000974800236789819</v>
+        <v>0.0009322494558017368</v>
       </c>
       <c r="X19" t="n">
         <v>0.0295710019941917</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.4298439919762179</v>
+        <v>-0.1601039334494191</v>
       </c>
     </row>
     <row r="20">
@@ -2064,13 +2064,13 @@
         <v>12.96666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>33.11299292387466</v>
+        <v>33.26408713703984</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2193297400873746</v>
+        <v>0.4532018555371362</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08441974228211516</v>
+        <v>-0.1408090739834827</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>-0.02414546328281751</v>
+        <v>-0.01714478067395405</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001199127514792181</v>
+        <v>0.001193680762936769</v>
       </c>
       <c r="W20" t="n">
-        <v>0.001366312353781091</v>
+        <v>0.001311853177397105</v>
       </c>
       <c r="X20" t="n">
         <v>0.03970670091213688</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.7995285548276116</v>
+        <v>-0.5703054782838444</v>
       </c>
     </row>
     <row r="21">
@@ -2147,13 +2147,13 @@
         <v>14.05</v>
       </c>
       <c r="D21" t="n">
-        <v>33.40678925938469</v>
+        <v>33.67334030860047</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5748685658658061</v>
+        <v>0.336871367418091</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4562261621977117</v>
+        <v>-0.08982491806961665</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2200,19 +2200,19 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>-0.01490992801453295</v>
+        <v>-0.02211396666571151</v>
       </c>
       <c r="V21" t="n">
-        <v>0.002283368665355401</v>
+        <v>0.002265294001306065</v>
       </c>
       <c r="W21" t="n">
-        <v>0.002414683439122582</v>
+        <v>0.002458514514707374</v>
       </c>
       <c r="X21" t="n">
         <v>0.07628001580501038</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.4980928230540984</v>
+        <v>-0.7446511251075507</v>
       </c>
     </row>
     <row r="22">
@@ -2230,13 +2230,13 @@
         <v>14.93333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>34.13331149340144</v>
+        <v>33.94145095962335</v>
       </c>
       <c r="E22" t="n">
-        <v>1.070087435681565</v>
+        <v>0.2701716160299412</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6650241090832518</v>
+        <v>-0.06119338696015625</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2283,19 +2283,19 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>0.0008903347551768859</v>
+        <v>-0.02249997190019291</v>
       </c>
       <c r="V22" t="n">
-        <v>0.00339667032848518</v>
+        <v>0.003415870656222101</v>
       </c>
       <c r="W22" t="n">
-        <v>0.00338653621268722</v>
+        <v>0.003673421235716655</v>
       </c>
       <c r="X22" t="n">
         <v>0.1159396063625789</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.03039007353185408</v>
+        <v>-0.763681692843301</v>
       </c>
     </row>
     <row r="23">
@@ -2313,13 +2313,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D23" t="n">
-        <v>29.27979654368249</v>
+        <v>29.50002045375516</v>
       </c>
       <c r="E23" t="n">
-        <v>1.968853614753954</v>
+        <v>1.154448483606217</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.792138006022656</v>
+        <v>-2.599403986552142</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2366,19 +2366,19 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>0.0679577701438254</v>
+        <v>0.03984885440305574</v>
       </c>
       <c r="V23" t="n">
-        <v>0.002171392694003044</v>
+        <v>0.002155182786958192</v>
       </c>
       <c r="W23" t="n">
-        <v>0.002036109500216239</v>
+        <v>0.002076448063670487</v>
       </c>
       <c r="X23" t="n">
         <v>0.06357793629684773</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.989789683373548</v>
+        <v>1.175542019948856</v>
       </c>
     </row>
     <row r="24">
@@ -2396,13 +2396,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>30.58525753746805</v>
+        <v>30.03193620630886</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8382629088769171</v>
+        <v>0.6948205432293904</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.736254002251828</v>
+        <v>-0.145240400931089</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2449,19 +2449,19 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>0.005384674261734224</v>
+        <v>0.001113312725761866</v>
       </c>
       <c r="V24" t="n">
-        <v>0.001637513087263281</v>
+        <v>0.00166768333386379</v>
       </c>
       <c r="W24" t="n">
-        <v>0.001615860851638156</v>
+        <v>0.001663124127076932</v>
       </c>
       <c r="X24" t="n">
         <v>0.05008375949492182</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1646916490505168</v>
+        <v>0.03343493675775222</v>
       </c>
     </row>
     <row r="25">
@@ -2479,13 +2479,13 @@
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>31.09951252865547</v>
+        <v>30.88306102035976</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3742258271403891</v>
+        <v>0.7859965146668575</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.330239523885744</v>
+        <v>-0.1340465429635165</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2532,19 +2532,19 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>-0.02574787930166702</v>
+        <v>-0.01233032053743415</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001117690791236708</v>
+        <v>0.001125524401299257</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001257526630730451</v>
+        <v>0.001192959288930269</v>
       </c>
       <c r="X25" t="n">
         <v>0.03475963876522885</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.8007464949285026</v>
+        <v>-0.3807980415581744</v>
       </c>
     </row>
     <row r="26">
@@ -2562,13 +2562,13 @@
         <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>31.3105361887845</v>
+        <v>31.57132226167865</v>
       </c>
       <c r="E26" t="n">
-        <v>0.198950616907771</v>
+        <v>0.415708750928097</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.03027597005130039</v>
+        <v>-0.3471285004430657</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>-0.04218450406868358</v>
+        <v>-0.03537132505043111</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0005439678299067449</v>
+        <v>0.0005394745358670995</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0008180953476856608</v>
+        <v>0.0007674293396487528</v>
       </c>
       <c r="X26" t="n">
         <v>0.01703192442382971</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.320819441248444</v>
+        <v>-1.116719501989747</v>
       </c>
     </row>
     <row r="27">
@@ -2645,13 +2645,13 @@
         <v>14.05</v>
       </c>
       <c r="D27" t="n">
-        <v>31.50612380638622</v>
+        <v>31.7073273294973</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3270225106538085</v>
+        <v>0.07675691324638123</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2020212066664041</v>
+        <v>-0.2010329824318151</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>-0.04305609581154686</v>
+        <v>-0.05101495077145059</v>
       </c>
       <c r="V27" t="n">
-        <v>-6.983484559359728e-05</v>
+        <v>-6.939169827867749e-05</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0002352937468371053</v>
+        <v>0.0002898453091343708</v>
       </c>
       <c r="X27" t="n">
         <v>-0.002200225291271741</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.356530685258223</v>
+        <v>-1.617547742808574</v>
       </c>
     </row>
     <row r="28">
@@ -2728,13 +2728,13 @@
         <v>14.91666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>31.89022696244574</v>
+        <v>31.73610005685744</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5593693879450825</v>
+        <v>-0.01035831164603707</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3341638947749972</v>
+        <v>-2.151935303947722e-06</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>-0.03694101358039363</v>
+        <v>-0.05480786681970858</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.0005525454326814507</v>
+        <v>-0.0005552288789014829</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.0002917087220623052</v>
+        <v>-0.0001663567120984929</v>
       </c>
       <c r="X28" t="n">
         <v>-0.01762079925527425</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1.178057307301543</v>
+        <v>-1.739387945293189</v>
       </c>
     </row>
     <row r="29">
@@ -2811,13 +2811,13 @@
         <v>10.06666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>32.1722099408478</v>
+        <v>31.85382879710079</v>
       </c>
       <c r="E29" t="n">
-        <v>0.707301664466268</v>
+        <v>0.8623569150695829</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.942919424195476</v>
+        <v>-1.752467504723467</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -2864,19 +2864,19 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>0.01725440175726392</v>
+        <v>0.02234185349890289</v>
       </c>
       <c r="V29" t="n">
-        <v>0.001188027837066629</v>
+        <v>0.001199902254549623</v>
       </c>
       <c r="W29" t="n">
-        <v>0.001165302101415717</v>
+        <v>0.001170181728185258</v>
       </c>
       <c r="X29" t="n">
         <v>0.03822148098967892</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.5551122357384279</v>
+        <v>0.7116735763639597</v>
       </c>
     </row>
     <row r="30">
@@ -2894,13 +2894,13 @@
         <v>11.11666666666667</v>
       </c>
       <c r="D30" t="n">
-        <v>31.73988227303304</v>
+        <v>31.83035277974918</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05385396511644558</v>
+        <v>0.2620274003173293</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02705240706237722</v>
+        <v>-0.0744549171525824</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2947,19 +2947,19 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>-0.01067550311139266</v>
+        <v>-0.004140233686431001</v>
       </c>
       <c r="V30" t="n">
-        <v>0.001360364769149424</v>
+        <v>0.001356498243043499</v>
       </c>
       <c r="W30" t="n">
-        <v>0.001389747358315305</v>
+        <v>0.001367861175509034</v>
       </c>
       <c r="X30" t="n">
         <v>0.0431778176211845</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.3388392119610011</v>
+        <v>-0.1317850988297001</v>
       </c>
     </row>
     <row r="31">
@@ -2977,13 +2977,13 @@
         <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>32.13344672385298</v>
+        <v>32.27314335993289</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5603212606629562</v>
+        <v>0.5658040026736622</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3437661981741477</v>
+        <v>0.200859545251626</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -3030,19 +3030,19 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>0.00785090253290148</v>
+        <v>0.007945309412866825</v>
       </c>
       <c r="V31" t="n">
-        <v>0.001410039768395712</v>
+        <v>0.001403936309238141</v>
       </c>
       <c r="W31" t="n">
-        <v>0.001378887229783353</v>
+        <v>0.001372545629770688</v>
       </c>
       <c r="X31" t="n">
         <v>0.04530943777625759</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.2522765582751521</v>
+        <v>0.2564201097204752</v>
       </c>
     </row>
     <row r="32">
@@ -3060,13 +3060,13 @@
         <v>12.91666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>32.75625668859781</v>
+        <v>32.85318326629564</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6570381253092883</v>
+        <v>0.6138587594580578</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04067714968584588</v>
+        <v>0.01312591605095265</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>0.01320014848713912</v>
+        <v>0.01182665729059543</v>
       </c>
       <c r="V32" t="n">
-        <v>0.001449561274254363</v>
+        <v>0.001445284641078882</v>
       </c>
       <c r="W32" t="n">
-        <v>0.001380575143152895</v>
+        <v>0.001383658951160251</v>
       </c>
       <c r="X32" t="n">
         <v>0.04748220118532685</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.432387452172335</v>
+        <v>0.3885433393956031</v>
       </c>
     </row>
     <row r="33">
@@ -3143,13 +3143,13 @@
         <v>14.16666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>33.53938799215553</v>
+        <v>33.5882702710447</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5973752035511506</v>
+        <v>0.563281856249187</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.04659673704326886</v>
+        <v>-0.03965254189883066</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -3196,19 +3196,19 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>0.01386777576349243</v>
+        <v>0.01282681721411007</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001498633967497358</v>
+        <v>0.001496452948857194</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001401997188973545</v>
+        <v>0.001407200111008052</v>
       </c>
       <c r="X33" t="n">
         <v>0.05026326609411727</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4651167119199837</v>
+        <v>0.4308306033048176</v>
       </c>
     </row>
     <row r="34">
@@ -3226,13 +3226,13 @@
         <v>15.75</v>
       </c>
       <c r="D34" t="n">
-        <v>34.42681055341428</v>
+        <v>34.4304200052972</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5258705350722535</v>
+        <v>0.5021211205829497</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.04347434076316148</v>
+        <v>-0.03742428023697117</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>0.01453966378119044</v>
+        <v>0.01384828246872307</v>
       </c>
       <c r="V34" t="n">
-        <v>0.001555928175116516</v>
+        <v>0.001555765062151862</v>
       </c>
       <c r="W34" t="n">
-        <v>0.001422008993618066</v>
+        <v>0.001428227296302813</v>
       </c>
       <c r="X34" t="n">
         <v>0.0535656445194559</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.5005542505053826</v>
+        <v>0.4768021817501293</v>
       </c>
     </row>
     <row r="35">
@@ -3309,13 +3309,13 @@
         <v>17.75</v>
       </c>
       <c r="D35" t="n">
-        <v>35.39112373630353</v>
+        <v>35.35947170641381</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4431824914069873</v>
+        <v>0.4303131145899908</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.03983935126362285</v>
+        <v>-0.03483021240685444</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -3362,19 +3362,19 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>0.01483565883992953</v>
+        <v>0.01448290988117382</v>
       </c>
       <c r="V35" t="n">
-        <v>0.001610135080234354</v>
+        <v>0.001611576392596405</v>
       </c>
       <c r="W35" t="n">
-        <v>0.001430900348563791</v>
+        <v>0.001436446716125748</v>
       </c>
       <c r="X35" t="n">
         <v>0.05698448985673704</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5250506377135312</v>
+        <v>0.5121080421699066</v>
       </c>
     </row>
     <row r="36">
@@ -3392,13 +3392,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D36" t="n">
-        <v>36.94565770426932</v>
+        <v>36.90294229304569</v>
       </c>
       <c r="E36" t="n">
-        <v>0.284672487384773</v>
+        <v>0.2894638946962118</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0330118757323387</v>
+        <v>-0.02995786418167946</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>0.01374954112533501</v>
+        <v>0.01388829799400032</v>
       </c>
       <c r="V36" t="n">
-        <v>0.001674330666669242</v>
+        <v>0.001676268716009134</v>
       </c>
       <c r="W36" t="n">
-        <v>0.00142226601502559</v>
+        <v>0.001421365581058319</v>
       </c>
       <c r="X36" t="n">
         <v>0.06185924769452287</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.5079858400074013</v>
+        <v>0.5125190594212161</v>
       </c>
     </row>
     <row r="37">
@@ -3475,13 +3475,13 @@
         <v>23.75</v>
       </c>
       <c r="D37" t="n">
-        <v>37.37263356747</v>
+        <v>37.34261184491389</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2319394611418337</v>
+        <v>0.2411660453854987</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.02992349343528483</v>
+        <v>-0.02775387620182451</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>0.0125649815468165</v>
+        <v>0.01281705022982444</v>
       </c>
       <c r="V37" t="n">
-        <v>0.001663619557944517</v>
+        <v>0.001664957030669107</v>
       </c>
       <c r="W37" t="n">
-        <v>0.001403505201260744</v>
+        <v>0.001399411151259112</v>
       </c>
       <c r="X37" t="n">
         <v>0.06217384413473686</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4695864511311953</v>
+        <v>0.4786221317290983</v>
       </c>
     </row>
     <row r="38">
@@ -3558,13 +3558,13 @@
         <v>26.25</v>
       </c>
       <c r="D38" t="n">
-        <v>37.86155950740491</v>
+        <v>37.8606431368698</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1635669362179168</v>
+        <v>0.1763744800731999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.02503796202126905</v>
+        <v>-0.02426737373029872</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -3611,19 +3611,19 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>0.009856556106216902</v>
+        <v>0.0101949418713682</v>
       </c>
       <c r="V38" t="n">
-        <v>0.001584682353749132</v>
+        <v>0.001584720709046247</v>
       </c>
       <c r="W38" t="n">
-        <v>0.001346558041265088</v>
+        <v>0.001338415381262659</v>
       </c>
       <c r="X38" t="n">
         <v>0.05999854523680726</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3731845855536065</v>
+        <v>0.3859870559930031</v>
       </c>
     </row>
     <row r="39">
@@ -3641,13 +3641,13 @@
         <v>27.91666666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>38.09861169026139</v>
+        <v>38.12033611842607</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1244048305694658</v>
+        <v>0.1377613598500584</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.02190141821751917</v>
+        <v>-0.02202901585331096</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0.007919468046409125</v>
+        <v>0.008267985217046022</v>
       </c>
       <c r="V39" t="n">
-        <v>0.001499635808012634</v>
+        <v>0.001498781179389131</v>
       </c>
       <c r="W39" t="n">
-        <v>0.001290809087633514</v>
+        <v>0.00128088873168627</v>
       </c>
       <c r="X39" t="n">
         <v>0.05713404232628472</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.3017207378935743</v>
+        <v>0.3151783754959723</v>
       </c>
     </row>
     <row r="40">
@@ -3724,13 +3724,13 @@
         <v>30.78333333333333</v>
       </c>
       <c r="D40" t="n">
-        <v>38.36734244472576</v>
+        <v>38.42623164499421</v>
       </c>
       <c r="E40" t="n">
-        <v>0.06948934560510711</v>
+        <v>0.08022683510465001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01674483575858813</v>
+        <v>-0.01834908096718654</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -3777,19 +3777,19 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>0.005052211606982032</v>
+        <v>0.005328867197648854</v>
       </c>
       <c r="V40" t="n">
-        <v>0.001306261603118239</v>
+        <v>0.00130425972320819</v>
       </c>
       <c r="W40" t="n">
-        <v>0.001155140604225533</v>
+        <v>0.001145107722561769</v>
       </c>
       <c r="X40" t="n">
         <v>0.05011778624923392</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1938399328282979</v>
+        <v>0.204768285342266</v>
       </c>
     </row>
     <row r="41">
@@ -3807,13 +3807,13 @@
         <v>33.71666666666666</v>
       </c>
       <c r="D41" t="n">
-        <v>38.49837843298384</v>
+        <v>38.58207991880084</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02761008611919902</v>
+        <v>0.03156883889350492</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0117309675131365</v>
+        <v>-0.01477099241380605</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -3860,19 +3860,19 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>0.00282988831759466</v>
+        <v>0.002930938446158824</v>
       </c>
       <c r="V41" t="n">
-        <v>0.001060169505293938</v>
+        <v>0.00105786953175706</v>
       </c>
       <c r="W41" t="n">
-        <v>0.0009665769365223807</v>
+        <v>0.0009611452374981006</v>
       </c>
       <c r="X41" t="n">
         <v>0.04081480681791529</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1089461113738392</v>
+        <v>0.1130817013667857</v>
       </c>
     </row>
     <row r="42">
@@ -3890,13 +3890,13 @@
         <v>36.74999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>38.52861220710172</v>
+        <v>38.610206628559</v>
       </c>
       <c r="E42" t="n">
-        <v>1.246305529534197e-05</v>
+        <v>-0.007537166611712109</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.005293057087266991</v>
+        <v>-0.007252583323883788</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -3943,19 +3943,19 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>0.001271592252182027</v>
+        <v>0.001076057011114318</v>
       </c>
       <c r="V42" t="n">
-        <v>0.0007537726782938218</v>
+        <v>0.0007521797408048471</v>
       </c>
       <c r="W42" t="n">
-        <v>0.0007084201026021043</v>
+        <v>0.0007138822248728211</v>
       </c>
       <c r="X42" t="n">
         <v>0.0290418152142911</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.04899268476987639</v>
+        <v>0.04154678354323343</v>
       </c>
     </row>
     <row r="43">
@@ -3973,13 +3973,13 @@
         <v>39.24999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>38.50813227567679</v>
+        <v>38.55672832406908</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.005380082671812447</v>
+        <v>-0.01404876282709977</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.001030988424734784</v>
+        <v>-0.0004380237515939963</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -4026,19 +4026,19 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>0.0007532701297637439</v>
+        <v>0.0005286169748632762</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0004502963104570966</v>
+        <v>0.0004497287669375862</v>
       </c>
       <c r="W43" t="n">
-        <v>0.0004223217800877304</v>
+        <v>0.0004301220245453036</v>
       </c>
       <c r="X43" t="n">
         <v>0.01734006988633109</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.02900702579625847</v>
+        <v>0.0203817410872946</v>
       </c>
     </row>
     <row r="44">
@@ -4056,13 +4056,13 @@
         <v>46.53333333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>38.52861220710172</v>
+        <v>38.610206628559</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01100386246812946</v>
+        <v>0.0287338807648343</v>
       </c>
       <c r="F44" t="n">
-        <v>0.005530012261789766</v>
+        <v>0.01218611810178183</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -4109,19 +4109,19 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>0.000624739936952795</v>
+        <v>0.001083341852967938</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.0005249533532954774</v>
+        <v>-0.0005238439765556357</v>
       </c>
       <c r="W44" t="n">
-        <v>-0.0005478681617593275</v>
+        <v>-0.0005634958511517288</v>
       </c>
       <c r="X44" t="n">
         <v>-0.02022572417593911</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.02407036276114341</v>
+        <v>0.04182805279245808</v>
       </c>
     </row>
     <row r="45">
@@ -4139,13 +4139,13 @@
         <v>12.81666666666666</v>
       </c>
       <c r="D45" t="n">
-        <v>24.49794379362827</v>
+        <v>24.68889995641544</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4521706072614453</v>
+        <v>0.4683694028493468</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.06189192941126924</v>
+        <v>-0.08062752562744983</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -4192,19 +4192,19 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>0.02206378333645542</v>
+        <v>0.02257714050178286</v>
       </c>
       <c r="V45" t="n">
-        <v>0.003118352624790683</v>
+        <v>0.003094233743329843</v>
       </c>
       <c r="W45" t="n">
-        <v>0.003053248186169309</v>
+        <v>0.00302812978833972</v>
       </c>
       <c r="X45" t="n">
         <v>0.07639322733083535</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.5405173240512769</v>
+        <v>0.5574047631504522</v>
       </c>
     </row>
     <row r="46">
@@ -4222,13 +4222,13 @@
         <v>14.25</v>
       </c>
       <c r="D46" t="n">
-        <v>25.1190264320092</v>
+        <v>25.31373903863702</v>
       </c>
       <c r="E46" t="n">
-        <v>0.415516544927705</v>
+        <v>0.4070633236283516</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.02474601114727429</v>
+        <v>-0.03999284415639892</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -4275,19 +4275,19 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>0.01291890048475715</v>
+        <v>0.01245772251766014</v>
       </c>
       <c r="V46" t="n">
-        <v>0.002425044925870336</v>
+        <v>0.002406391544874938</v>
       </c>
       <c r="W46" t="n">
-        <v>0.002336659122449342</v>
+        <v>0.002321816523026087</v>
       </c>
       <c r="X46" t="n">
         <v>0.06091476759174676</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.3245102027491114</v>
+        <v>0.315351536827801</v>
       </c>
     </row>
     <row r="47">
@@ -4305,13 +4305,13 @@
         <v>15.75</v>
       </c>
       <c r="D47" t="n">
-        <v>25.7143642179953</v>
+        <v>25.87901339418912</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3796950830314882</v>
+        <v>0.3514361884151525</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.02282520085588392</v>
+        <v>-0.03353544752169235</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -4358,19 +4358,19 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>0.01071301830702301</v>
+        <v>0.00952711205653349</v>
       </c>
       <c r="V47" t="n">
-        <v>0.00175467991656586</v>
+        <v>0.001743516175570568</v>
       </c>
       <c r="W47" t="n">
-        <v>0.001649811370585271</v>
+        <v>0.001650849678072112</v>
       </c>
       <c r="X47" t="n">
         <v>0.04512047846057613</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.275478454620841</v>
+        <v>0.2465522605189709</v>
       </c>
     </row>
     <row r="48">
@@ -4388,13 +4388,13 @@
         <v>17.75</v>
       </c>
       <c r="D48" t="n">
-        <v>26.42789631927808</v>
+        <v>26.51411675247832</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3368600779639706</v>
+        <v>0.2938301181373864</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.02045269624248116</v>
+        <v>-0.02555954101228416</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>0.0109061566477308</v>
+        <v>0.009241799548130016</v>
       </c>
       <c r="V48" t="n">
-        <v>0.001102720811710549</v>
+        <v>0.001099134908134269</v>
       </c>
       <c r="W48" t="n">
-        <v>0.0009685751640328625</v>
+        <v>0.000985830493883179</v>
       </c>
       <c r="X48" t="n">
         <v>0.02914259128099655</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2882267771280351</v>
+        <v>0.2450381522221206</v>
       </c>
     </row>
     <row r="49">
@@ -4471,13 +4471,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>27.70072835809506</v>
+        <v>27.56466149717262</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2572901866479924</v>
+        <v>0.2135249130505557</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01606282761716979</v>
+        <v>-0.01080164273625846</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -4524,19 +4524,19 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>0.01224676059052313</v>
+        <v>0.01070487856881287</v>
       </c>
       <c r="V49" t="n">
-        <v>0.0002329777313350133</v>
+        <v>0.0002341277744280816</v>
       </c>
       <c r="W49" t="n">
-        <v>6.10655905385959e-05</v>
+        <v>8.311781506497117e-05</v>
       </c>
       <c r="X49" t="n">
         <v>0.006453652849196456</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.339244188384705</v>
+        <v>0.2950763541176645</v>
       </c>
     </row>
     <row r="50">
@@ -4554,13 +4554,13 @@
         <v>23.75</v>
       </c>
       <c r="D50" t="n">
-        <v>28.10618617952874</v>
+        <v>27.90200526919842</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2319928168977157</v>
+        <v>0.2004775134057626</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01407211063616783</v>
+        <v>-0.004341779320751256</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -4607,19 +4607,19 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>0.01204437474977316</v>
+        <v>0.0109752773023198</v>
       </c>
       <c r="V50" t="n">
-        <v>6.531630339965662e-05</v>
+        <v>6.579427414616336e-05</v>
       </c>
       <c r="W50" t="n">
-        <v>-0.0001025170476882296</v>
+        <v>-8.826080120155897e-05</v>
       </c>
       <c r="X50" t="n">
         <v>0.001835792183909335</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.3385214391331394</v>
+        <v>0.3062322451202408</v>
       </c>
     </row>
     <row r="51">
@@ -4637,13 +4637,13 @@
         <v>26.25</v>
       </c>
       <c r="D51" t="n">
-        <v>28.64386118691368</v>
+        <v>28.39596624092639</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2009612073597893</v>
+        <v>0.2026980418518516</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0109326309643531</v>
+        <v>0.002663315221819396</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -4690,19 +4690,19 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>0.01068191935259054</v>
+        <v>0.01080433215319584</v>
       </c>
       <c r="V51" t="n">
-        <v>-5.017271922451634e-06</v>
+        <v>-5.061072381350162e-06</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.0001495383361958823</v>
+        <v>-0.000152514438970206</v>
       </c>
       <c r="X51" t="n">
         <v>-0.0001437140404837041</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.3059714151454102</v>
+        <v>0.3067994510779046</v>
       </c>
     </row>
     <row r="52">
@@ -4720,13 +4720,13 @@
         <v>27.91666666666666</v>
       </c>
       <c r="D52" t="n">
-        <v>28.96312009296423</v>
+        <v>28.73947814752466</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1843846144756647</v>
+        <v>0.2091092381586437</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.008901652291602401</v>
+        <v>0.00312787002091983</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -4773,19 +4773,19 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>0.009552581993302903</v>
+        <v>0.01046242349453234</v>
       </c>
       <c r="V52" t="n">
-        <v>3.478942026938983e-06</v>
+        <v>3.506014103856397e-06</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.000123507417960572</v>
+        <v>-0.000136657527570694</v>
       </c>
       <c r="X52" t="n">
         <v>0.0001007610157226942</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.2766725794699196</v>
+        <v>0.3006845913912608</v>
       </c>
     </row>
     <row r="53">
@@ -4803,13 +4803,13 @@
         <v>30.7</v>
       </c>
       <c r="D53" t="n">
-        <v>29.44299319235574</v>
+        <v>29.3354530945887</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1644624453651566</v>
+        <v>0.2144738188390969</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.005653854142682241</v>
+        <v>0.0001867597164298407</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -4856,19 +4856,19 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>0.0079536835586646</v>
+        <v>0.009678970363111127</v>
       </c>
       <c r="V53" t="n">
-        <v>3.065108018757976e-05</v>
+        <v>3.076344320953171e-05</v>
       </c>
       <c r="W53" t="n">
-        <v>-7.299415716891363e-05</v>
+        <v>-9.582654525136444e-05</v>
       </c>
       <c r="X53" t="n">
         <v>0.0009024595453012609</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.2341802508719136</v>
+        <v>0.2839369810909607</v>
       </c>
     </row>
     <row r="54">
@@ -4886,13 +4886,13 @@
         <v>33.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29.9180428917296</v>
+        <v>29.99077163834306</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1522442521237526</v>
+        <v>0.2092258601148522</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.002306842777105907</v>
+        <v>-0.003687345484199168</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -4939,19 +4939,19 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>0.006754510432644329</v>
+        <v>0.008642141506427718</v>
       </c>
       <c r="V54" t="n">
-        <v>4.900134090875597e-05</v>
+        <v>4.888251081829854e-05</v>
       </c>
       <c r="W54" t="n">
-        <v>-3.797539753177769e-05</v>
+        <v>-6.213108111183558e-05</v>
       </c>
       <c r="X54" t="n">
         <v>0.001466024219060425</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.2020817328364881</v>
+        <v>0.2591844923855197</v>
       </c>
     </row>
     <row r="55">
@@ -4969,13 +4969,13 @@
         <v>36.75</v>
       </c>
       <c r="D55" t="n">
-        <v>30.36441901562919</v>
+        <v>30.6018281992158</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1503375270647895</v>
+        <v>0.1923604369357763</v>
       </c>
       <c r="F55" t="n">
-        <v>0.001626391730103559</v>
+        <v>-0.008239993382676031</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -5022,19 +5022,19 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>0.006121912736337415</v>
+        <v>0.007456717671039857</v>
       </c>
       <c r="V55" t="n">
-        <v>5.527485268731127e-05</v>
+        <v>5.484603001815776e-05</v>
       </c>
       <c r="W55" t="n">
-        <v>-2.307884195777648e-05</v>
+        <v>-3.985128123262358e-05</v>
       </c>
       <c r="X55" t="n">
         <v>0.001678388788024696</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.1858883235032663</v>
+        <v>0.2281891930992183</v>
       </c>
     </row>
     <row r="56">
@@ -5052,13 +5052,13 @@
         <v>39.33333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>30.75622895087086</v>
+        <v>31.07356626059552</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1595708678456065</v>
+        <v>0.165249536401546</v>
       </c>
       <c r="F56" t="n">
-        <v>0.004219532357862998</v>
+        <v>-0.01124150682098886</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -5105,19 +5105,19 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>0.006135991785462943</v>
+        <v>0.006265756249527881</v>
       </c>
       <c r="V56" t="n">
-        <v>4.842643580783609e-05</v>
+        <v>4.79318831475481e-05</v>
       </c>
       <c r="W56" t="n">
-        <v>-2.978026594894044e-05</v>
+        <v>-3.111316763550425e-05</v>
       </c>
       <c r="X56" t="n">
         <v>0.001489414546980458</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1887199681943611</v>
+        <v>0.1946993919924451</v>
       </c>
     </row>
     <row r="57">
@@ -5135,13 +5135,13 @@
         <v>46.93333333333334</v>
       </c>
       <c r="D57" t="n">
-        <v>32.14565737977434</v>
+        <v>31.94134358797329</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2060681923921539</v>
+        <v>0.0631129181715524</v>
       </c>
       <c r="F57" t="n">
-        <v>0.008016605680702123</v>
+        <v>-0.01563655060795684</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -5188,19 +5188,19 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>0.007061072516470514</v>
+        <v>0.002626521099334869</v>
       </c>
       <c r="V57" t="n">
-        <v>8.303042474814183e-06</v>
+        <v>8.35615314271211e-06</v>
       </c>
       <c r="W57" t="n">
-        <v>-7.874507341036715e-05</v>
+        <v>-2.423042277860768e-05</v>
       </c>
       <c r="X57" t="n">
         <v>0.0002669067586050903</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.2269828178482022</v>
+        <v>0.08389461287491637</v>
       </c>
     </row>
     <row r="58">
@@ -5218,13 +5218,13 @@
         <v>10.13333333333333</v>
       </c>
       <c r="D58" t="n">
-        <v>27.6820262224195</v>
+        <v>27.3483074314982</v>
       </c>
       <c r="E58" t="n">
-        <v>1.528888314475401</v>
+        <v>1.528676938769382</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.289454724126297</v>
+        <v>-1.115294966596787</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -5271,19 +5271,19 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>0.05945800591186536</v>
+        <v>0.06012422753422365</v>
       </c>
       <c r="V58" t="n">
-        <v>0.001090215218210349</v>
+        <v>0.001103518612044737</v>
       </c>
       <c r="W58" t="n">
-        <v>0.0009575974672742633</v>
+        <v>0.0009677784852073051</v>
       </c>
       <c r="X58" t="n">
         <v>0.03017936625857966</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.645918078785031</v>
+        <v>1.644295858687297</v>
       </c>
     </row>
     <row r="59">
@@ -5301,13 +5301,13 @@
         <v>11.56666666666667</v>
       </c>
       <c r="D59" t="n">
-        <v>28.6328130121517</v>
+        <v>28.46405037547181</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4818298852329832</v>
+        <v>0.6022852657586331</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.390496584403931</v>
+        <v>-0.360053881150505</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -5354,19 +5354,19 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.007180981049318367</v>
+        <v>0.01151259578173216</v>
       </c>
       <c r="V59" t="n">
-        <v>0.0008969775900507867</v>
+        <v>0.000902295747556234</v>
       </c>
       <c r="W59" t="n">
-        <v>0.0008713384920761881</v>
+        <v>0.0008609472688623766</v>
       </c>
       <c r="X59" t="n">
         <v>0.02568299161201464</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.2056116876289377</v>
+        <v>0.3276951062836685</v>
       </c>
     </row>
     <row r="60">
@@ -5384,13 +5384,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>29.00959789988407</v>
+        <v>28.97786920043766</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3393147461468509</v>
+        <v>0.4478876670289793</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.07623267057361967</v>
+        <v>-0.09375374226497546</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -5437,19 +5437,19 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>0.002743599749419692</v>
+        <v>0.006503159819879348</v>
       </c>
       <c r="V60" t="n">
-        <v>0.0007983468461517041</v>
+        <v>0.0007992209789928847</v>
       </c>
       <c r="W60" t="n">
-        <v>0.0007860297983548474</v>
+        <v>0.0007699938900783005</v>
       </c>
       <c r="X60" t="n">
         <v>0.02315972099150155</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.07959072552888796</v>
+        <v>0.1884477146500055</v>
       </c>
     </row>
     <row r="61">
@@ -5467,13 +5467,13 @@
         <v>14.13333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>29.5009685640624</v>
+        <v>29.59718463877531</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3317898541146982</v>
+        <v>0.4015261467971136</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.004414699244993117</v>
+        <v>-0.02828585116984849</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -5520,19 +5520,19 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>0.006161129062847553</v>
+        <v>0.008480747496735483</v>
       </c>
       <c r="V61" t="n">
-        <v>0.0006987019005542094</v>
+        <v>0.0006964305238984141</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0006645143300337535</v>
+        <v>0.0006495245736151253</v>
       </c>
       <c r="X61" t="n">
         <v>0.02061238280390039</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.1817592748021969</v>
+        <v>0.2510062495357116</v>
       </c>
     </row>
     <row r="62">
@@ -5550,13 +5550,13 @@
         <v>16.85</v>
       </c>
       <c r="D62" t="n">
-        <v>30.38604944373159</v>
+        <v>30.58366178364559</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3233990471364363</v>
+        <v>0.3414107011147993</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.002210540986952472</v>
+        <v>-0.01805098696945927</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -5603,19 +5603,19 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>0.01101921643202252</v>
+        <v>0.01153937859759997</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0005568426274757067</v>
+        <v>0.0005532446614977355</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0004788539010684022</v>
+        <v>0.0004721021781200712</v>
       </c>
       <c r="X62" t="n">
         <v>0.01692024761085423</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.334830455334616</v>
+        <v>0.3529164522224361</v>
       </c>
     </row>
     <row r="63">
@@ -5633,13 +5633,13 @@
         <v>22.4</v>
       </c>
       <c r="D63" t="n">
-        <v>32.15372939173055</v>
+        <v>32.23233890740552</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3210867398122836</v>
+        <v>0.2874586621503354</v>
       </c>
       <c r="F63" t="n">
-        <v>0.001534729473765345</v>
+        <v>-0.0006600694074655467</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -5686,19 +5686,19 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>0.01637646662611292</v>
+        <v>0.01530880996608005</v>
       </c>
       <c r="V63" t="n">
-        <v>0.000348490198391928</v>
+        <v>0.0003476402865753588</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0002032882832466225</v>
+        <v>0.0002122357847532248</v>
       </c>
       <c r="X63" t="n">
         <v>0.01120525953476454</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.5265644762887414</v>
+        <v>0.4934387510957593</v>
       </c>
     </row>
     <row r="64">
@@ -5716,13 +5716,13 @@
         <v>24.05</v>
       </c>
       <c r="D64" t="n">
-        <v>32.6847909758343</v>
+        <v>32.70193637387037</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3245762653317463</v>
+        <v>0.2908143446361375</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00283005915963172</v>
+        <v>0.005958378862213135</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -5769,19 +5769,19 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>0.01665582251877981</v>
+        <v>0.01561820252417522</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0002976187991140823</v>
+        <v>0.0002974627596454867</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0001452584038340783</v>
+        <v>0.0001546689767463408</v>
       </c>
       <c r="X64" t="n">
         <v>0.009727608239522602</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.544392077556912</v>
+        <v>0.5107454652197997</v>
       </c>
     </row>
     <row r="65">
@@ -5799,13 +5799,13 @@
         <v>25.55</v>
       </c>
       <c r="D65" t="n">
-        <v>33.17536550085145</v>
+        <v>33.14662582651447</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3297966202645242</v>
+        <v>0.3051036837037131</v>
       </c>
       <c r="F65" t="n">
-        <v>0.002356905619938968</v>
+        <v>0.009105086945152135</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -5852,19 +5852,19 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>0.01614011034749322</v>
+        <v>0.01540376887744909</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0002555725631114712</v>
+        <v>0.0002557941564727905</v>
       </c>
       <c r="W65" t="n">
-        <v>0.0001049490161522152</v>
+        <v>0.0001119176927437326</v>
       </c>
       <c r="X65" t="n">
         <v>0.008478713193212481</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.5354540600021621</v>
+        <v>0.5105829632989139</v>
       </c>
     </row>
     <row r="66">
@@ -5882,13 +5882,13 @@
         <v>27.01666666666667</v>
       </c>
       <c r="D66" t="n">
-        <v>33.6630065215925</v>
+        <v>33.60650743528318</v>
       </c>
       <c r="E66" t="n">
-        <v>0.331642475307321</v>
+        <v>0.3178538665585267</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.0006942422289595851</v>
+        <v>0.006226158618857267</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>0.0152854783221557</v>
+        <v>0.01489174538373089</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0002209300877437384</v>
+        <v>0.0002213015142634324</v>
       </c>
       <c r="W66" t="n">
-        <v>7.631658212372236e-05</v>
+        <v>8.017619307994671e-05</v>
       </c>
       <c r="X66" t="n">
         <v>0.007437170984533468</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.5145551564443881</v>
+        <v>0.5004595519626962</v>
       </c>
     </row>
     <row r="67">
@@ -5965,13 +5965,13 @@
         <v>30.05</v>
       </c>
       <c r="D67" t="n">
-        <v>34.66371872579222</v>
+        <v>34.5976290083399</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3172858729876955</v>
+        <v>0.3212622662351068</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.008628784912759153</v>
+        <v>-0.00402119203103507</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -6018,19 +6018,19 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>0.01309174983064569</v>
+        <v>0.01322416726636053</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0001728070869525385</v>
+        <v>0.0001731371896756962</v>
       </c>
       <c r="W67" t="n">
-        <v>4.680971952456418e-05</v>
+        <v>4.562229347686444e-05</v>
       </c>
       <c r="X67" t="n">
         <v>0.005990136255946315</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.4538087337579402</v>
+        <v>0.4575248330257741</v>
       </c>
     </row>
     <row r="68">
@@ -6048,13 +6048,13 @@
         <v>33.05</v>
       </c>
       <c r="D68" t="n">
-        <v>35.57813461613436</v>
+        <v>35.54515317446911</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2798404352259274</v>
+        <v>0.2939337794328081</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.01680362063193006</v>
+        <v>-0.01481686994613171</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -6101,19 +6101,19 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>0.01054151037633381</v>
+        <v>0.01094529989548966</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0001533299475232635</v>
+        <v>0.0001534722184735378</v>
       </c>
       <c r="W68" t="n">
-        <v>5.060135605658079e-05</v>
+        <v>4.670966747733546e-05</v>
       </c>
       <c r="X68" t="n">
         <v>0.005455193513667488</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.3750472752265814</v>
+        <v>0.3890523613256806</v>
       </c>
     </row>
     <row r="69">
@@ -6131,13 +6131,13 @@
         <v>35.71666666666666</v>
       </c>
       <c r="D69" t="n">
-        <v>36.26519980860697</v>
+        <v>36.27704743837425</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2247864944719238</v>
+        <v>0.2408935352022574</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.02540387016099038</v>
+        <v>-0.02587000667387462</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -6184,19 +6184,19 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>0.007931425284625664</v>
+        <v>0.008373401835163687</v>
       </c>
       <c r="V69" t="n">
-        <v>0.000160829667548178</v>
+        <v>0.0001607771425911803</v>
       </c>
       <c r="W69" t="n">
-        <v>8.22780838157204e-05</v>
+        <v>7.787537641016748e-05</v>
       </c>
       <c r="X69" t="n">
         <v>0.005832520028786509</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.2876347227139872</v>
+        <v>0.3037622955948031</v>
       </c>
     </row>
     <row r="70">
@@ -6214,13 +6214,13 @@
         <v>38.41666666666666</v>
       </c>
       <c r="D70" t="n">
-        <v>36.78228424672304</v>
+        <v>36.835696706298</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1431871064357388</v>
+        <v>0.1546969243125667</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.0316287160182974</v>
+        <v>-0.03362783079533318</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -6267,19 +6267,19 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0.004882182380189196</v>
+        <v>0.005189001400015388</v>
       </c>
       <c r="V70" t="n">
-        <v>0.0001990858490734699</v>
+        <v>0.0001987971708125328</v>
       </c>
       <c r="W70" t="n">
-        <v>0.0001493497074342836</v>
+        <v>0.0001460120295966885</v>
       </c>
       <c r="X70" t="n">
         <v>0.007322832290120574</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.1795778200524618</v>
+        <v>0.1911404817795225</v>
       </c>
     </row>
     <row r="71">
@@ -6297,13 +6297,13 @@
         <v>46.41666666666666</v>
       </c>
       <c r="D71" t="n">
-        <v>36.78228424672304</v>
+        <v>36.835696706298</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.1431871064357377</v>
+        <v>-0.1546969243125638</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.03996483719957174</v>
+        <v>-0.04372063136094942</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -6350,19 +6350,19 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>-0.004727090289107653</v>
+        <v>-0.005033909308933797</v>
       </c>
       <c r="V71" t="n">
-        <v>0.00037099240092809</v>
+        <v>0.0003704544549032005</v>
       </c>
       <c r="W71" t="n">
-        <v>0.0004299339387122765</v>
+        <v>0.0004331306696072843</v>
       </c>
       <c r="X71" t="n">
         <v>0.01364594794431124</v>
       </c>
       <c r="Y71" t="n">
-        <v>-0.1738731786738819</v>
+        <v>-0.1854275565508955</v>
       </c>
     </row>
     <row r="72">
@@ -6380,13 +6380,13 @@
         <v>10.08333333333333</v>
       </c>
       <c r="D72" t="n">
-        <v>22.7550570219956</v>
+        <v>22.70493261460721</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8154315760058175</v>
+        <v>0.8095150146725683</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6178923513600627</v>
+        <v>-0.6030494348381827</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>0.04592680060041407</v>
+        <v>0.04574532707586186</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.045066966500244</v>
+        <v>1.03864456869061</v>
       </c>
     </row>
     <row r="73">
@@ -6463,13 +6463,13 @@
         <v>11.2</v>
       </c>
       <c r="D73" t="n">
-        <v>23.31338769086442</v>
+        <v>23.26525215107486</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4489009626739628</v>
+        <v>0.4529433107423557</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.2062592192850646</v>
+        <v>-0.1999345879755507</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>0.02435038000474394</v>
+        <v>0.02456396897979753</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.5676898494704686</v>
+        <v>0.5714869321461707</v>
       </c>
     </row>
     <row r="74">
@@ -6546,13 +6546,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D74" t="n">
-        <v>23.87334480746527</v>
+        <v>23.83549408839162</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3813603406285093</v>
+        <v>0.3896822104788864</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.02127626603525196</v>
+        <v>-0.01912087657541039</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>0.02039997424611603</v>
+        <v>0.02077447913967906</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.4870156192409393</v>
+        <v>0.4951699747232352</v>
       </c>
     </row>
     <row r="75">
@@ -6629,13 +6629,13 @@
         <v>13.85</v>
       </c>
       <c r="D75" t="n">
-        <v>24.32421200879139</v>
+        <v>24.29745905343904</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3798361778873236</v>
+        <v>0.3899806387838662</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.002007947925256201</v>
+        <v>-0.0007188895655968197</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>0.02025147405166017</v>
+        <v>0.02068617890031077</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.4926011483231197</v>
+        <v>0.5026215848024155</v>
       </c>
     </row>
     <row r="76">
@@ -6712,13 +6712,13 @@
         <v>15.31666666666667</v>
       </c>
       <c r="D76" t="n">
-        <v>24.87916300213528</v>
+        <v>24.86868118062512</v>
       </c>
       <c r="E76" t="n">
-        <v>0.3755824823665321</v>
+        <v>0.3871609944455874</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.003811934374442154</v>
+        <v>-0.003152232424426527</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>0.01996791396703792</v>
+        <v>0.02043986293642015</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.4967849863985501</v>
+        <v>0.5083124347415087</v>
       </c>
     </row>
     <row r="77">
@@ -6795,13 +6795,13 @@
         <v>17.98333333333333</v>
       </c>
       <c r="D77" t="n">
-        <v>25.86717352522962</v>
+        <v>25.88991710410795</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3609970213513023</v>
+        <v>0.3727926284734087</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.006548620897526818</v>
+        <v>-0.006843666254660399</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>0.01918567558594298</v>
+        <v>0.01962902201719036</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.4962791995803485</v>
+        <v>0.5081937528597683</v>
       </c>
     </row>
     <row r="78">
@@ -6878,13 +6878,13 @@
         <v>23.56666666666667</v>
       </c>
       <c r="D78" t="n">
-        <v>27.77160328645161</v>
+        <v>27.85244440090797</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3118194120367637</v>
+        <v>0.3175668727475074</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.01127914206599798</v>
+        <v>-0.0132245234440517</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>0.01700789928688593</v>
+        <v>0.01718166418319534</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.4723366317313193</v>
+        <v>0.47855134637752</v>
       </c>
     </row>
     <row r="79">
@@ -6961,13 +6961,13 @@
         <v>25.13333333333333</v>
       </c>
       <c r="D79" t="n">
-        <v>28.24725212243168</v>
+        <v>28.33504989601718</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2930624064029619</v>
+        <v>0.295383108330789</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.01311373377644165</v>
+        <v>-0.01569914881581858</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>0.01625977611303667</v>
+        <v>0.01630953105759465</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.4592939953192389</v>
+        <v>0.4621313762975864</v>
       </c>
     </row>
     <row r="80">
@@ -7044,13 +7044,13 @@
         <v>26.68333333333333</v>
       </c>
       <c r="D80" t="n">
-        <v>28.68533069149266</v>
+        <v>28.77347494174718</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2709861119968053</v>
+        <v>0.2686888959857558</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.01517652676585166</v>
+        <v>-0.01848158800336817</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>0.01540456339472086</v>
+        <v>0.01529578606344143</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.4418849951356306</v>
+        <v>0.4401129170107577</v>
       </c>
     </row>
     <row r="81">
@@ -7127,13 +7127,13 @@
         <v>28.15</v>
       </c>
       <c r="D81" t="n">
-        <v>29.0666155901646</v>
+        <v>29.14789225999456</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2474313265274128</v>
+        <v>0.2398345941170521</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.01681485666939997</v>
+        <v>-0.02069148174897057</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>0.01451603799878851</v>
+        <v>0.01423167421311976</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.4219320964030077</v>
+        <v>0.4148233066433576</v>
       </c>
     </row>
     <row r="82">
@@ -7210,13 +7210,13 @@
         <v>31.18333333333333</v>
       </c>
       <c r="D82" t="n">
-        <v>29.73851507129508</v>
+        <v>29.77846555771898</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1916911875825731</v>
+        <v>0.1706834348307833</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.01966905005867627</v>
+        <v>-0.02454141704346991</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>0.0124849574353011</v>
+        <v>0.01177084175533188</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.3712840948541792</v>
+        <v>0.3505176057965108</v>
       </c>
     </row>
     <row r="83">
@@ -7293,13 +7293,13 @@
         <v>34.18333333333334</v>
       </c>
       <c r="D83" t="n">
-        <v>30.22512911004171</v>
+        <v>30.18014854935354</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1288471294861875</v>
+        <v>0.0918836944431245</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.02243699086140478</v>
+        <v>-0.02827500882794872</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="U83" t="n">
-        <v>0.01027545007842259</v>
+        <v>0.009057043657529436</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.3105768052841109</v>
+        <v>0.2733429230022186</v>
       </c>
     </row>
     <row r="84">
@@ -7376,13 +7376,13 @@
         <v>35.7</v>
       </c>
       <c r="D84" t="n">
-        <v>30.39497004602677</v>
+        <v>30.28729344170724</v>
       </c>
       <c r="E84" t="n">
-        <v>0.09367601066510289</v>
+        <v>0.04745994975275636</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.02375192891203302</v>
+        <v>-0.03004868906636723</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>0.009055564318615449</v>
+        <v>0.007540598768276501</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.2752436062141854</v>
+        <v>0.2283843276209666</v>
       </c>
     </row>
     <row r="85">
@@ -7459,13 +7459,13 @@
         <v>36.75</v>
       </c>
       <c r="D85" t="n">
-        <v>30.48002205897316</v>
+        <v>30.32027265253625</v>
       </c>
       <c r="E85" t="n">
-        <v>0.06832782351850142</v>
+        <v>0.01535759468346498</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.02453033231958895</v>
+        <v>-0.03109865392275937</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>0.008181315441372846</v>
+        <v>0.006446102990600344</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.2493666751244621</v>
+        <v>0.1954476002213318</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -2313,13 +2313,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D23" t="n">
-        <v>29.50002045375516</v>
+        <v>29.38709327217807</v>
       </c>
       <c r="E23" t="n">
-        <v>1.154448483606217</v>
+        <v>1.863914303451672</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.599403986552142</v>
+        <v>-1.937930766168051</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2355,10 +2355,10 @@
         <v>36.945</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.003671328671323693</v>
+        <v>0.1337619892107362</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02811750367545162</v>
+        <v>0.09494554408321854</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2366,19 +2366,19 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>0.03984885440305574</v>
+        <v>0.06414132474724349</v>
       </c>
       <c r="V23" t="n">
-        <v>0.002155182786958192</v>
+        <v>0.002163464610398861</v>
       </c>
       <c r="W23" t="n">
-        <v>0.002076448063670487</v>
+        <v>0.002036244995661479</v>
       </c>
       <c r="X23" t="n">
         <v>0.06357793629684773</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.175542019948856</v>
+        <v>1.884927092948308</v>
       </c>
     </row>
     <row r="24">
@@ -2396,13 +2396,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>30.03193620630886</v>
+        <v>30.51827123721507</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6948205432293904</v>
+        <v>0.7213387167597531</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.145240400931089</v>
+        <v>-0.6783927277655555</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         <v>0.02289665284659392</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.008859523896477145</v>
+        <v>-0.06729891126568134</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2449,19 +2449,19 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>0.001113312725761866</v>
+        <v>0.001613547458548002</v>
       </c>
       <c r="V24" t="n">
-        <v>0.00166768333386379</v>
+        <v>0.001641107358461638</v>
       </c>
       <c r="W24" t="n">
-        <v>0.001663124127076932</v>
+        <v>0.001634604904815281</v>
       </c>
       <c r="X24" t="n">
         <v>0.05008375949492182</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.03343493675775222</v>
+        <v>0.04924267899408696</v>
       </c>
     </row>
     <row r="25">
@@ -2479,13 +2479,13 @@
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>30.88306102035976</v>
+        <v>30.95476622841004</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7859965146668575</v>
+        <v>0.3716426023733312</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1340465429635165</v>
+        <v>-0.1702221617721579</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2532,19 +2532,19 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>-0.01233032053743415</v>
+        <v>-0.02577506307782374</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001125524401299257</v>
+        <v>0.001122917178851983</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001192959288930269</v>
+        <v>0.00126355522341435</v>
       </c>
       <c r="X25" t="n">
         <v>0.03475963876522885</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.3807980415581744</v>
+        <v>-0.797861052096557</v>
       </c>
     </row>
     <row r="26">
@@ -2562,13 +2562,13 @@
         <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>31.57132226167865</v>
+        <v>31.243749582257</v>
       </c>
       <c r="E26" t="n">
-        <v>0.415708750928097</v>
+        <v>0.3995574467914267</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3471285004430657</v>
+        <v>0.2133105311547059</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>-0.03537132505043111</v>
+        <v>-0.03575021874534758</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0005394745358670995</v>
+        <v>0.0005451306149727292</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0007674293396487528</v>
+        <v>0.0007779428209024674</v>
       </c>
       <c r="X26" t="n">
         <v>0.01703192442382971</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.116719501989747</v>
+        <v>-1.11697088199055</v>
       </c>
     </row>
     <row r="27">
@@ -2645,13 +2645,13 @@
         <v>14.05</v>
       </c>
       <c r="D27" t="n">
-        <v>31.7073273294973</v>
+        <v>31.78519283885927</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07675691324638123</v>
+        <v>0.8279322491309813</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2010329824318151</v>
+        <v>0.510325153787894</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>-0.05101495077145059</v>
+        <v>-0.02738801091550864</v>
       </c>
       <c r="V27" t="n">
-        <v>-6.939169827867749e-05</v>
+        <v>-6.922170654827162e-05</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0002898453091343708</v>
+        <v>0.0001231666903000812</v>
       </c>
       <c r="X27" t="n">
         <v>-0.002200225291271741</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.617547742808574</v>
+        <v>-0.8705332084222246</v>
       </c>
     </row>
     <row r="28">
@@ -2728,13 +2728,13 @@
         <v>14.91666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>31.73610005685744</v>
+        <v>32.72611599996809</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.01035831164603707</v>
+        <v>1.343428891889367</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.151935303947722e-06</v>
+        <v>0.679282483346842</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>-0.05480786681970858</v>
+        <v>-0.01343081083854204</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.0005552288789014829</v>
+        <v>-0.0005384323411703187</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.0001663567120984929</v>
+        <v>-0.0004460209975923221</v>
       </c>
       <c r="X28" t="n">
         <v>-0.01762079925527425</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1.739387945293189</v>
+        <v>-0.4395382734757554</v>
       </c>
     </row>
     <row r="29">
@@ -2832,13 +2832,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2.117754022569127</v>
+        <v>2.119179048041742</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0100179557286697</v>
+        <v>-0.009456372285179038</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.03346831723782027</v>
+        <v>-0.03398973697388988</v>
       </c>
       <c r="N29" t="n">
         <v>0.04237394890341881</v>
@@ -2864,19 +2864,19 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>0.02234185349890289</v>
+        <v>0.02261003493142559</v>
       </c>
       <c r="V29" t="n">
-        <v>0.001199902254549623</v>
+        <v>0.001200259006210183</v>
       </c>
       <c r="W29" t="n">
         <v>0.001170181728185258</v>
       </c>
       <c r="X29" t="n">
-        <v>0.03822148098967892</v>
+        <v>0.03823284489599749</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.7116735763639597</v>
+        <v>0.720216181802099</v>
       </c>
     </row>
     <row r="30">
@@ -2915,13 +2915,13 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2.087215716866762</v>
+        <v>2.088927690428526</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.02582351642175973</v>
+        <v>-0.02615655681116524</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.003182449610328446</v>
+        <v>-0.003872547638034603</v>
       </c>
       <c r="N30" t="n">
         <v>0.08735887304521579</v>
@@ -2947,19 +2947,19 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>-0.004140233686431001</v>
+        <v>-0.004289525333668436</v>
       </c>
       <c r="V30" t="n">
-        <v>0.001356498243043499</v>
+        <v>0.001356088509913993</v>
       </c>
       <c r="W30" t="n">
         <v>0.001367861175509034</v>
       </c>
       <c r="X30" t="n">
-        <v>0.0431778176211845</v>
+        <v>0.04316477567112677</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.1317850988297001</v>
+        <v>-0.1365371046283376</v>
       </c>
     </row>
     <row r="31">
@@ -2998,13 +2998,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.066827954913856</v>
+        <v>2.067795170069929</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.0198134799459786</v>
+        <v>-0.02063577719138032</v>
       </c>
       <c r="M31" t="n">
-        <v>0.006538852478252349</v>
+        <v>0.006350757477629117</v>
       </c>
       <c r="N31" t="n">
         <v>0.1275061606761601</v>
@@ -3030,19 +3030,19 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>0.007945309412866825</v>
+        <v>0.007552124862059606</v>
       </c>
       <c r="V31" t="n">
-        <v>0.001403936309238141</v>
+        <v>0.00140238289834316</v>
       </c>
       <c r="W31" t="n">
         <v>0.001372545629770688</v>
       </c>
       <c r="X31" t="n">
-        <v>0.04530943777625759</v>
+        <v>0.04525930432374699</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.2564201097204752</v>
+        <v>0.243730808345363</v>
       </c>
     </row>
     <row r="32">
@@ -3081,13 +3081,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.051773362756858</v>
+        <v>2.05200661583767</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.01407157940694259</v>
+        <v>-0.01471834531695149</v>
       </c>
       <c r="M32" t="n">
-        <v>0.005656133668469661</v>
+        <v>0.00589501481217024</v>
       </c>
       <c r="N32" t="n">
         <v>0.1711895453687214</v>
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>0.01182665729059543</v>
+        <v>0.01151224982399719</v>
       </c>
       <c r="V32" t="n">
-        <v>0.001445284641078882</v>
+        <v>0.001443646344088566</v>
       </c>
       <c r="W32" t="n">
         <v>0.001383658951160251</v>
       </c>
       <c r="X32" t="n">
-        <v>0.04748220118532685</v>
+        <v>0.04742837791405936</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.3885433393956031</v>
+        <v>0.3782140532751594</v>
       </c>
     </row>
     <row r="33">
@@ -3164,13 +3164,13 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2.038192318106796</v>
+        <v>2.037879477419884</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.008037363165663169</v>
+        <v>-0.008304745121873958</v>
       </c>
       <c r="M33" t="n">
-        <v>0.004520981411469255</v>
+        <v>0.004791853458431045</v>
       </c>
       <c r="N33" t="n">
         <v>0.233717249579028</v>
@@ -3196,19 +3196,19 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>0.01282681721411007</v>
+        <v>0.01269500588359046</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001496452948857194</v>
+        <v>0.001495535766120965</v>
       </c>
       <c r="W33" t="n">
-        <v>0.001407200111008052</v>
+        <v>0.001407200111008051</v>
       </c>
       <c r="X33" t="n">
-        <v>0.05026326609411727</v>
+        <v>0.05023245951248487</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4308306033048176</v>
+        <v>0.4264032887105389</v>
       </c>
     </row>
     <row r="34">
@@ -3247,13 +3247,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2.031137146384127</v>
+        <v>2.030740878677251</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.001493627936065167</v>
+        <v>-0.001397580689606936</v>
       </c>
       <c r="M34" t="n">
-        <v>0.003677054428447219</v>
+        <v>0.003858036097509609</v>
       </c>
       <c r="N34" t="n">
         <v>0.3170919465744321</v>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>0.01384828246872307</v>
+        <v>0.013895435626426</v>
       </c>
       <c r="V34" t="n">
-        <v>0.001555765062151862</v>
+        <v>0.001556199325996475</v>
       </c>
       <c r="W34" t="n">
-        <v>0.001428227296302813</v>
+        <v>0.001428227296302814</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0535656445194559</v>
+        <v>0.05358059640601906</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.4768021817501293</v>
+        <v>0.4784256847744172</v>
       </c>
     </row>
     <row r="35">
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2.035633519970628</v>
+        <v>2.035805105904229</v>
       </c>
       <c r="L35" t="n">
-        <v>0.004708907919431515</v>
+        <v>0.00504425939445094</v>
       </c>
       <c r="M35" t="n">
-        <v>0.00269458281162871</v>
+        <v>0.00277091710397757</v>
       </c>
       <c r="N35" t="n">
         <v>0.4275724209378097</v>
@@ -3362,19 +3362,19 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>0.01448290988117382</v>
+        <v>0.01464744162082032</v>
       </c>
       <c r="V35" t="n">
-        <v>0.001611576392596405</v>
+        <v>0.001613565936864088</v>
       </c>
       <c r="W35" t="n">
         <v>0.001436446716125748</v>
       </c>
       <c r="X35" t="n">
-        <v>0.05698448985673704</v>
+        <v>0.0570548390909788</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5121080421699066</v>
+        <v>0.5179257975627443</v>
       </c>
     </row>
     <row r="36">
@@ -3413,13 +3413,13 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2.079142224861755</v>
+        <v>2.081249820890327</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01256711206847716</v>
+        <v>0.01282653925998256</v>
       </c>
       <c r="M36" t="n">
-        <v>0.000849240225396646</v>
+        <v>0.000729018955751449</v>
       </c>
       <c r="N36" t="n">
         <v>0.6773094646637046</v>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>0.01388829799400032</v>
+        <v>0.01400682681814485</v>
       </c>
       <c r="V36" t="n">
-        <v>0.001676268716009134</v>
+        <v>0.001678444171120302</v>
       </c>
       <c r="W36" t="n">
         <v>0.001421365581058319</v>
       </c>
       <c r="X36" t="n">
-        <v>0.06185924769452287</v>
+        <v>0.06193952838895142</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.5125190594212161</v>
+        <v>0.5168931217786843</v>
       </c>
     </row>
     <row r="37">
@@ -3496,13 +3496,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.101707053763695</v>
+        <v>2.104126935900627</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01336444096894196</v>
+        <v>0.01335766586415282</v>
       </c>
       <c r="M37" t="n">
-        <v>3.949545837342826e-05</v>
+        <v>-0.0001620711106730724</v>
       </c>
       <c r="N37" t="n">
         <v>0.7736707373393487</v>
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>0.01281705022982444</v>
+        <v>0.01280651722767065</v>
       </c>
       <c r="V37" t="n">
-        <v>0.001664957030669107</v>
+        <v>0.001664738806095621</v>
       </c>
       <c r="W37" t="n">
         <v>0.001399411151259112</v>
       </c>
       <c r="X37" t="n">
-        <v>0.06217384413473686</v>
+        <v>0.06216569505919414</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4786221317290983</v>
+        <v>0.4782288019181078</v>
       </c>
     </row>
     <row r="38">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.134463944790217</v>
+        <v>2.136138838778407</v>
       </c>
       <c r="L38" t="n">
-        <v>0.01181729755773009</v>
+        <v>0.01114968656306303</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0008948971162764828</v>
+        <v>-0.001120220367477728</v>
       </c>
       <c r="N38" t="n">
         <v>0.9146965461484002</v>
@@ -3611,19 +3611,19 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>0.0101949418713682</v>
+        <v>0.009878069247843929</v>
       </c>
       <c r="V38" t="n">
-        <v>0.001584720709046247</v>
+        <v>0.001577065205328077</v>
       </c>
       <c r="W38" t="n">
         <v>0.001338415381262659</v>
       </c>
       <c r="X38" t="n">
-        <v>0.05999854523680726</v>
+        <v>0.05970870294250062</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3859870559930031</v>
+        <v>0.3739900546739069</v>
       </c>
     </row>
     <row r="39">
@@ -3662,13 +3662,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2.152731153105458</v>
+        <v>2.152882677952347</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0100190915286118</v>
+        <v>0.009019287453887026</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.001062381479664619</v>
+        <v>-0.001172038739690828</v>
       </c>
       <c r="N39" t="n">
         <v>1.004613956853115</v>
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0.008267985217046022</v>
+        <v>0.007803255159356828</v>
       </c>
       <c r="V39" t="n">
-        <v>0.001498781179389131</v>
+        <v>0.001486533797816385</v>
       </c>
       <c r="W39" t="n">
         <v>0.00128088873168627</v>
       </c>
       <c r="X39" t="n">
-        <v>0.05713404232628472</v>
+        <v>0.056667168024161</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.3151783754959723</v>
+        <v>0.2974627094925246</v>
       </c>
     </row>
     <row r="40">
@@ -3745,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.176811640371411</v>
+        <v>2.173674094847271</v>
       </c>
       <c r="L40" t="n">
-        <v>0.007055161721050418</v>
+        <v>0.00618308344552404</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0009308320182838202</v>
+        <v>-0.0007271339905342432</v>
       </c>
       <c r="N40" t="n">
         <v>1.147638215923621</v>
@@ -3777,19 +3777,19 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>0.005328867197648854</v>
+        <v>0.004932345324158175</v>
       </c>
       <c r="V40" t="n">
-        <v>0.00130425972320819</v>
+        <v>0.001292417196996624</v>
       </c>
       <c r="W40" t="n">
         <v>0.001145107722561769</v>
       </c>
       <c r="X40" t="n">
-        <v>0.05011778624923392</v>
+        <v>0.04966272259376639</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.204768285342266</v>
+        <v>0.1895314439792061</v>
       </c>
     </row>
     <row r="41">
@@ -3828,13 +3828,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>2.193469671369374</v>
+        <v>2.188600271910131</v>
       </c>
       <c r="L41" t="n">
-        <v>0.004634171927431985</v>
+        <v>0.004837282148425159</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.000716498340384688</v>
+        <v>-0.0001819506659246502</v>
       </c>
       <c r="N41" t="n">
         <v>1.273252413771963</v>
@@ -3860,19 +3860,19 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>0.002930938446158824</v>
+        <v>0.003028442712860842</v>
       </c>
       <c r="V41" t="n">
-        <v>0.00105786953175706</v>
+        <v>0.001061087283189659</v>
       </c>
       <c r="W41" t="n">
-        <v>0.0009611452374981006</v>
+        <v>0.0009611452374981003</v>
       </c>
       <c r="X41" t="n">
-        <v>0.04081480681791529</v>
+        <v>0.0409389543608467</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1130817013667857</v>
+        <v>0.116843618777107</v>
       </c>
     </row>
     <row r="42">
@@ -3911,13 +3911,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.204249697598105</v>
+        <v>2.202485451218219</v>
       </c>
       <c r="L42" t="n">
-        <v>0.002802193816956455</v>
+        <v>0.005153757308895945</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0004546411618555052</v>
+        <v>0.0004841143620388914</v>
       </c>
       <c r="N42" t="n">
         <v>1.374160465684623</v>
@@ -3943,19 +3943,19 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>0.001076057011114318</v>
+        <v>0.002144761606631627</v>
       </c>
       <c r="V42" t="n">
-        <v>0.0007521797408048471</v>
+        <v>0.0007902155798456332</v>
       </c>
       <c r="W42" t="n">
         <v>0.0007138822248728211</v>
       </c>
       <c r="X42" t="n">
-        <v>0.0290418152142911</v>
+        <v>0.03051038681894646</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.04154678354323343</v>
+        <v>0.0828096888010473</v>
       </c>
     </row>
     <row r="43">
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.209706430113592</v>
+        <v>2.216557122654333</v>
       </c>
       <c r="L43" t="n">
-        <v>0.001973230333554898</v>
+        <v>0.007146560847689637</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0002896734882714569</v>
+        <v>0.0009037293549751451</v>
       </c>
       <c r="N43" t="n">
         <v>1.430093764837538</v>
@@ -4026,19 +4026,19 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>0.0005286169748632762</v>
+        <v>0.002859805695050554</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0004497287669375862</v>
+        <v>0.0005361940506457551</v>
       </c>
       <c r="W43" t="n">
         <v>0.0004301220245453036</v>
       </c>
       <c r="X43" t="n">
-        <v>0.01734006988633109</v>
+        <v>0.02067388833973052</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.0203817410872946</v>
+        <v>0.1102647512436897</v>
       </c>
     </row>
     <row r="44">
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2.219633582472838</v>
+        <v>2.300815726331576</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0007527611609747797</v>
+        <v>0.01599081315979101</v>
       </c>
       <c r="M44" t="n">
-        <v>-4.546678795191661e-05</v>
+        <v>0.001524898282215161</v>
       </c>
       <c r="N44" t="n">
         <v>1.41318925985422</v>
@@ -4109,19 +4109,19 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>0.001083341852967938</v>
+        <v>0.007694266799697597</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.0005238439765556357</v>
+        <v>-0.0002818745868992157</v>
       </c>
       <c r="W44" t="n">
         <v>-0.0005634958511517288</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.02022572417593911</v>
+        <v>-0.01088323604351843</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.04182805279245808</v>
+        <v>0.2970772309915856</v>
       </c>
     </row>
     <row r="45">
@@ -4139,13 +4139,13 @@
         <v>12.81666666666666</v>
       </c>
       <c r="D45" t="n">
-        <v>24.68889995641544</v>
+        <v>24.45549776089937</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4683694028493468</v>
+        <v>0.445803291611619</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.08062752562744983</v>
+        <v>-0.06034668239199277</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2.290444306229041</v>
+        <v>2.291057164999081</v>
       </c>
       <c r="L45" t="n">
-        <v>0.008260008927685192</v>
+        <v>0.008306901990275284</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0205553572250682</v>
+        <v>-0.02078706591921876</v>
       </c>
       <c r="N45" t="n">
-        <v>0.07228700779647691</v>
+        <v>0.07790473552950697</v>
       </c>
       <c r="O45" t="n">
-        <v>0.07613253933762341</v>
+        <v>0.0634467239399686</v>
       </c>
       <c r="P45" t="n">
-        <v>0.01846914457861556</v>
+        <v>0.01087678132715291</v>
       </c>
       <c r="Q45" t="n">
         <v>31.995</v>
@@ -4192,19 +4192,19 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>0.02257714050178286</v>
+        <v>0.02185495879141676</v>
       </c>
       <c r="V45" t="n">
-        <v>0.003094233743329843</v>
+        <v>0.00260592489706846</v>
       </c>
       <c r="W45" t="n">
-        <v>0.00302812978833972</v>
+        <v>0.002536304364241857</v>
       </c>
       <c r="X45" t="n">
-        <v>0.07639322733083535</v>
+        <v>0.06372919048532963</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.5574047631504522</v>
+        <v>0.5344738957880404</v>
       </c>
     </row>
     <row r="46">
@@ -4222,13 +4222,13 @@
         <v>14.25</v>
       </c>
       <c r="D46" t="n">
-        <v>25.31373903863702</v>
+        <v>25.06915330805948</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4070633236283516</v>
+        <v>0.4114164825728679</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.03999284415639892</v>
+        <v>-0.02324528555518547</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -4243,22 +4243,22 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.281876722766255</v>
+        <v>2.282274629736696</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.00826724930615963</v>
+        <v>-0.008720976032358663</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.006194760464289825</v>
+        <v>-0.006476713703435878</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1718540470967996</v>
+        <v>0.1609355713051363</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06153739555295379</v>
+        <v>0.05281366605660436</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.01022264989225095</v>
+        <v>-0.00710389630350909</v>
       </c>
       <c r="Q46" t="n">
         <v>32.01</v>
@@ -4275,19 +4275,19 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>0.01245772251766014</v>
+        <v>0.01259008626540013</v>
       </c>
       <c r="V46" t="n">
-        <v>0.002406391544874938</v>
+        <v>0.002082188499211797</v>
       </c>
       <c r="W46" t="n">
-        <v>0.002321816523026087</v>
+        <v>0.002001364360438363</v>
       </c>
       <c r="X46" t="n">
-        <v>0.06091476759174676</v>
+        <v>0.05219870270301883</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.315351536827801</v>
+        <v>0.3156228027490097</v>
       </c>
     </row>
     <row r="47">
@@ -4305,13 +4305,13 @@
         <v>15.75</v>
       </c>
       <c r="D47" t="n">
-        <v>25.87901339418912</v>
+        <v>25.66003890680712</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3514361884151525</v>
+        <v>0.3777188338396273</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.03353544752169235</v>
+        <v>-0.02151288469179706</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -4326,22 +4326,22 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>2.265881292506861</v>
+        <v>2.26512177627356</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.009183291746274969</v>
+        <v>-0.009954277268090561</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0007310512656245724</v>
+        <v>0.0006985879566776481</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2517150544388291</v>
+        <v>0.2321269861735177</v>
       </c>
       <c r="O47" t="n">
-        <v>0.04614064345751816</v>
+        <v>0.04265153885005755</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.009379685711600999</v>
+        <v>-0.00637303148429085</v>
       </c>
       <c r="Q47" t="n">
         <v>32.01</v>
@@ -4358,19 +4358,19 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>0.00952711205653349</v>
+        <v>0.01032553116695748</v>
       </c>
       <c r="V47" t="n">
-        <v>0.001743516175570568</v>
+        <v>0.001622422962937229</v>
       </c>
       <c r="W47" t="n">
-        <v>0.001650849678072112</v>
+        <v>0.001529015683270528</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04512047846057613</v>
+        <v>0.04163143635226656</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.2465522605189709</v>
+        <v>0.2649535314775784</v>
       </c>
     </row>
     <row r="48">
@@ -4388,13 +4388,13 @@
         <v>17.75</v>
       </c>
       <c r="D48" t="n">
-        <v>26.51411675247832</v>
+        <v>26.37226351139624</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2938301181373864</v>
+        <v>0.3372323030258908</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.02555954101228416</v>
+        <v>-0.0193730955314233</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -4409,22 +4409,22 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.25146225148539</v>
+        <v>2.249162444068046</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.00414319927982193</v>
+        <v>-0.004501664606738176</v>
       </c>
       <c r="M48" t="n">
-        <v>0.002513933584402321</v>
+        <v>0.002741568290999149</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3250629330769729</v>
+        <v>0.304604985485553</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02974078052859898</v>
+        <v>0.03097672917945008</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.007391353161914887</v>
+        <v>-0.005470297797812553</v>
       </c>
       <c r="Q48" t="n">
         <v>31.98</v>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>0.009241799548130016</v>
+        <v>0.01078590074156519</v>
       </c>
       <c r="V48" t="n">
-        <v>0.001099134908134269</v>
+        <v>0.001151477456453691</v>
       </c>
       <c r="W48" t="n">
-        <v>0.000985830493883179</v>
+        <v>0.001026898118111597</v>
       </c>
       <c r="X48" t="n">
-        <v>0.02914259128099655</v>
+        <v>0.03036706690902902</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2450381522221206</v>
+        <v>0.2844486165643213</v>
       </c>
     </row>
     <row r="49">
@@ -4471,13 +4471,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>27.56466149717262</v>
+        <v>27.65634127581926</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2135249130505557</v>
+        <v>0.2614521506647343</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01080164273625846</v>
+        <v>-0.01541382259815037</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -4492,22 +4492,22 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>2.262297737274182</v>
+        <v>2.262309800373687</v>
       </c>
       <c r="L49" t="n">
-        <v>0.006693121938627589</v>
+        <v>0.007521757503957005</v>
       </c>
       <c r="M49" t="n">
-        <v>0.001532681339414351</v>
+        <v>0.001562657183201134</v>
       </c>
       <c r="N49" t="n">
-        <v>0.3888449911681286</v>
+        <v>0.3894306057887302</v>
       </c>
       <c r="O49" t="n">
-        <v>0.005303235334193024</v>
+        <v>0.0107188325742629</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.003712321885336485</v>
+        <v>-0.003799960777227666</v>
       </c>
       <c r="Q49" t="n">
         <v>31.995</v>
@@ -4524,19 +4524,19 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>0.01070487856881287</v>
+        <v>0.01277841909339471</v>
       </c>
       <c r="V49" t="n">
-        <v>0.0002341277744280816</v>
+        <v>0.0004343892229278844</v>
       </c>
       <c r="W49" t="n">
-        <v>8.311781506497117e-05</v>
+        <v>0.0002544555347030464</v>
       </c>
       <c r="X49" t="n">
-        <v>0.006453652849196456</v>
+        <v>0.0120136165958315</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.2950763541176645</v>
+        <v>0.3534043194123691</v>
       </c>
     </row>
     <row r="50">
@@ -4554,13 +4554,13 @@
         <v>23.75</v>
       </c>
       <c r="D50" t="n">
-        <v>27.90200526919842</v>
+        <v>28.06974006072264</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2004775134057626</v>
+        <v>0.2370918725330791</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.004341779320751256</v>
+        <v>-0.01361837208848466</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -4575,22 +4575,22 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>2.276140520773264</v>
+        <v>2.277722827112753</v>
       </c>
       <c r="L50" t="n">
-        <v>0.008627072778333855</v>
+        <v>0.009349276726921874</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0006643646156860147</v>
+        <v>0.0004784216143222239</v>
       </c>
       <c r="N50" t="n">
-        <v>0.3916480108607699</v>
+        <v>0.4016182045838965</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0003513601541866307</v>
+        <v>0.004946422586161653</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.002089204690189239</v>
+        <v>-0.003042496589870878</v>
       </c>
       <c r="Q50" t="n">
         <v>31.98</v>
@@ -4607,19 +4607,19 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>0.0109752773023198</v>
+        <v>0.01255118850536495</v>
       </c>
       <c r="V50" t="n">
-        <v>6.579427414616336e-05</v>
+        <v>0.000234947974791381</v>
       </c>
       <c r="W50" t="n">
-        <v>-8.826080120155897e-05</v>
+        <v>5.536719556029123e-05</v>
       </c>
       <c r="X50" t="n">
-        <v>0.001835792183909335</v>
+        <v>0.00659492858018728</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.3062322451202408</v>
+        <v>0.3523085987987239</v>
       </c>
     </row>
     <row r="51">
@@ -4637,13 +4637,13 @@
         <v>26.25</v>
       </c>
       <c r="D51" t="n">
-        <v>28.39596624092639</v>
+        <v>28.62141699802177</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2026980418518516</v>
+        <v>0.2067876727762741</v>
       </c>
       <c r="F51" t="n">
-        <v>0.002663315221819396</v>
+        <v>-0.0107868393137892</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -4658,22 +4658,22 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>2.298913462764915</v>
+        <v>2.301476496493114</v>
       </c>
       <c r="L51" t="n">
-        <v>0.008427962237032349</v>
+        <v>0.008227493564764821</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0004135900704281699</v>
+        <v>-0.0007861243739321921</v>
       </c>
       <c r="N51" t="n">
-        <v>0.3875372175159932</v>
+        <v>0.4051112484582827</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.001564450004481743</v>
+        <v>-0.001081258627303544</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.00014870938964822</v>
+        <v>-0.001847930289874596</v>
       </c>
       <c r="Q51" t="n">
         <v>31.98</v>
@@ -4690,19 +4690,19 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>0.01080433215319584</v>
+        <v>0.01079980405549942</v>
       </c>
       <c r="V51" t="n">
-        <v>-5.061072381350162e-06</v>
+        <v>1.282130564689127e-05</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.000152514438970206</v>
+        <v>-0.0001400405217158347</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.0001437140404837041</v>
+        <v>0.0003669639353787663</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.3067994510779046</v>
+        <v>0.3091056953693756</v>
       </c>
     </row>
     <row r="52">
@@ -4720,13 +4720,13 @@
         <v>27.91666666666666</v>
       </c>
       <c r="D52" t="n">
-        <v>28.73947814752466</v>
+        <v>28.95063745026737</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2091092381586437</v>
+        <v>0.1902927634632174</v>
       </c>
       <c r="F52" t="n">
-        <v>0.00312787002091983</v>
+        <v>-0.008955076321904357</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -4741,22 +4741,22 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>2.312203161427049</v>
+        <v>2.313773458892856</v>
       </c>
       <c r="L52" t="n">
-        <v>0.007367594504199215</v>
+        <v>0.006542385042578536</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0006469654449942448</v>
+        <v>-0.0009151848816731751</v>
       </c>
       <c r="N52" t="n">
-        <v>0.3850185423234447</v>
+        <v>0.4005552883271568</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.001126060460763079</v>
+        <v>-0.003535428893192888</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0003152317813900813</v>
+        <v>-0.001075146602099324</v>
       </c>
       <c r="Q52" t="n">
         <v>32.01</v>
@@ -4773,19 +4773,19 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>0.01046242349453234</v>
+        <v>0.009400590091008743</v>
       </c>
       <c r="V52" t="n">
-        <v>3.506014103856397e-06</v>
+        <v>-8.299733729467654e-05</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.000136657527570694</v>
+        <v>-0.0002130620407340354</v>
       </c>
       <c r="X52" t="n">
-        <v>0.0001007610157226942</v>
+        <v>-0.002402825821355735</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.3006845913912608</v>
+        <v>0.27215307554337</v>
       </c>
     </row>
     <row r="53">
@@ -4803,13 +4803,13 @@
         <v>30.7</v>
       </c>
       <c r="D53" t="n">
-        <v>29.3354530945887</v>
+        <v>29.44663520267652</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2144738188390969</v>
+        <v>0.1697457663601689</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0001867597164298407</v>
+        <v>-0.006025849868610385</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -4824,22 +4824,22 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>2.32989179938618</v>
+        <v>2.328098194900139</v>
       </c>
       <c r="L53" t="n">
-        <v>0.005516930369822814</v>
+        <v>0.004440787751949671</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0005999021027103894</v>
+        <v>-0.0004974838167732701</v>
       </c>
       <c r="N53" t="n">
-        <v>0.3836745572537825</v>
+        <v>0.3869878657170909</v>
       </c>
       <c r="O53" t="n">
-        <v>-6.040075839673642e-06</v>
+        <v>-0.004680945412155212</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0003402937690272116</v>
+        <v>0.0001606346812521692</v>
       </c>
       <c r="Q53" t="n">
         <v>31.995</v>
@@ -4856,19 +4856,19 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>0.009678970363111127</v>
+        <v>0.007671996076401387</v>
       </c>
       <c r="V53" t="n">
-        <v>3.076344320953171e-05</v>
+        <v>-0.0001338956363148501</v>
       </c>
       <c r="W53" t="n">
-        <v>-9.582654525136444e-05</v>
+        <v>-0.0002347210571808174</v>
       </c>
       <c r="X53" t="n">
-        <v>0.0009024595453012609</v>
+        <v>-0.003942775957793638</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.2839369810909607</v>
+        <v>0.2259144697381572</v>
       </c>
     </row>
     <row r="54">
@@ -4886,13 +4886,13 @@
         <v>33.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29.99077163834306</v>
+        <v>29.93609460971918</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2092258601148522</v>
+        <v>0.1558999872100433</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.003687345484199168</v>
+        <v>-0.003007141875694268</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -4907,22 +4907,22 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2.343916761655924</v>
+        <v>2.339283581624709</v>
       </c>
       <c r="L54" t="n">
-        <v>0.003904496922610412</v>
+        <v>0.003784353600139179</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0004552165880612599</v>
+        <v>7.581067507196008e-05</v>
       </c>
       <c r="N54" t="n">
-        <v>0.3852497996998289</v>
+        <v>0.3733579605501811</v>
       </c>
       <c r="O54" t="n">
-        <v>0.0008242750400914711</v>
+        <v>-0.002278602233229593</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0002020591873632122</v>
+        <v>0.001434166412932715</v>
       </c>
       <c r="Q54" t="n">
         <v>31.98</v>
@@ -4939,19 +4939,19 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>0.008642141506427718</v>
+        <v>0.006825500122633723</v>
       </c>
       <c r="V54" t="n">
-        <v>4.888251081829854e-05</v>
+        <v>-5.593935988448026e-05</v>
       </c>
       <c r="W54" t="n">
-        <v>-6.213108111183558e-05</v>
+        <v>-0.0001410658547978875</v>
       </c>
       <c r="X54" t="n">
-        <v>0.001466024219060425</v>
+        <v>-0.001674605969908931</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.2591844923855197</v>
+        <v>0.204328817429813</v>
       </c>
     </row>
     <row r="55">
@@ -4969,13 +4969,13 @@
         <v>36.75</v>
       </c>
       <c r="D55" t="n">
-        <v>30.6018281992158</v>
+        <v>30.390284223113</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1923604369357763</v>
+        <v>0.151400568340641</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.008239993382676031</v>
+        <v>0.0005402875017627914</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -4990,22 +4990,22 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>2.353582822173603</v>
+        <v>2.350981928724797</v>
       </c>
       <c r="L55" t="n">
-        <v>0.002755585205470978</v>
+        <v>0.004870577390689079</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0002851896605268836</v>
+        <v>0.0007495166867425111</v>
       </c>
       <c r="N55" t="n">
-        <v>0.3886308933324487</v>
+        <v>0.3729850955543391</v>
       </c>
       <c r="O55" t="n">
-        <v>0.00122337801467666</v>
+        <v>0.003931640023539254</v>
       </c>
       <c r="P55" t="n">
-        <v>3.961306235677705e-05</v>
+        <v>0.002930754982840081</v>
       </c>
       <c r="Q55" t="n">
         <v>32.01</v>
@@ -5022,19 +5022,19 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>0.007456717671039857</v>
+        <v>0.007053594521764335</v>
       </c>
       <c r="V55" t="n">
-        <v>5.484603001815776e-05</v>
+        <v>0.0001547981863926214</v>
       </c>
       <c r="W55" t="n">
-        <v>-3.985128123262358e-05</v>
+        <v>6.82282284617594e-05</v>
       </c>
       <c r="X55" t="n">
-        <v>0.001678388788024696</v>
+        <v>0.004704360881694189</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.2281891930992183</v>
+        <v>0.214360742311011</v>
       </c>
     </row>
     <row r="56">
@@ -5052,13 +5052,13 @@
         <v>39.33333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>31.07356626059552</v>
+        <v>30.78141132408451</v>
       </c>
       <c r="E56" t="n">
-        <v>0.165249536401546</v>
+        <v>0.1573345752518907</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.01124150682098886</v>
+        <v>0.002879070817613808</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -5073,22 +5073,22 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>2.359663815428079</v>
+        <v>2.365724564649334</v>
       </c>
       <c r="L56" t="n">
-        <v>0.002236362509041953</v>
+        <v>0.007668708110113567</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0001730926744980744</v>
+        <v>0.001193684057598926</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3920056135704909</v>
+        <v>0.3921643951281641</v>
       </c>
       <c r="O56" t="n">
-        <v>0.001117892700609307</v>
+        <v>0.01341735876529982</v>
       </c>
       <c r="P56" t="n">
-        <v>-6.748597936174069e-05</v>
+        <v>0.00391744027113252</v>
       </c>
       <c r="Q56" t="n">
         <v>32.01</v>
@@ -5105,19 +5105,19 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>0.006265756249527881</v>
+        <v>0.0083529398606636</v>
       </c>
       <c r="V56" t="n">
-        <v>4.79318831475481e-05</v>
+        <v>0.0004771904260518148</v>
       </c>
       <c r="W56" t="n">
-        <v>-3.111316763550425e-05</v>
+        <v>0.0003707714716539693</v>
       </c>
       <c r="X56" t="n">
-        <v>0.001489414546980458</v>
+        <v>0.01468859478421604</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1946993919924451</v>
+        <v>0.2571152776164274</v>
       </c>
     </row>
     <row r="57">
@@ -5135,13 +5135,13 @@
         <v>46.93333333333334</v>
       </c>
       <c r="D57" t="n">
-        <v>31.94134358797329</v>
+        <v>32.10975323236918</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0631129181715524</v>
+        <v>0.1922290848230235</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.01563655060795684</v>
+        <v>0.006303694859000092</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -5156,22 +5156,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>2.374031448869096</v>
+        <v>2.467871880708222</v>
       </c>
       <c r="L57" t="n">
-        <v>0.001544593659646765</v>
+        <v>0.01921216453696217</v>
       </c>
       <c r="M57" t="n">
-        <v>-8.95175955329075e-06</v>
+        <v>0.001844067633677023</v>
       </c>
       <c r="N57" t="n">
-        <v>0.3962880854534297</v>
+        <v>0.6281346125688212</v>
       </c>
       <c r="O57" t="n">
-        <v>9.073584374602595e-06</v>
+        <v>0.04868006687697835</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.0002243085249105499</v>
+        <v>0.005362219758256564</v>
       </c>
       <c r="Q57" t="n">
         <v>32.01</v>
@@ -5188,19 +5188,19 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>0.002626521099334869</v>
+        <v>0.01377153768226499</v>
       </c>
       <c r="V57" t="n">
-        <v>8.35615314271211e-06</v>
+        <v>0.001668341670143457</v>
       </c>
       <c r="W57" t="n">
-        <v>-2.423042277860768e-05</v>
+        <v>0.001398941297492627</v>
       </c>
       <c r="X57" t="n">
-        <v>0.0002669067586050903</v>
+        <v>0.05357003933558507</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.08389461287491637</v>
+        <v>0.4422006766078022</v>
       </c>
     </row>
     <row r="58">
@@ -5218,13 +5218,13 @@
         <v>10.13333333333333</v>
       </c>
       <c r="D58" t="n">
-        <v>27.3483074314982</v>
+        <v>27.35048884826322</v>
       </c>
       <c r="E58" t="n">
-        <v>1.528676938769382</v>
+        <v>1.525880117528869</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.115294966596787</v>
+        <v>-1.11687795447228</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -5239,22 +5239,22 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>2.127365951524089</v>
+        <v>2.128076816680966</v>
       </c>
       <c r="L58" t="n">
-        <v>0.00899374684160803</v>
+        <v>0.008849738016936448</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.03592025573400803</v>
+        <v>-0.03631360376504571</v>
       </c>
       <c r="N58" t="n">
-        <v>0.06174320854979103</v>
+        <v>0.0559861369961135</v>
       </c>
       <c r="O58" t="n">
-        <v>0.02991833792610701</v>
+        <v>0.03790605056055957</v>
       </c>
       <c r="P58" t="n">
-        <v>0.004322299855940482</v>
+        <v>0.007802512902614564</v>
       </c>
       <c r="Q58" t="n">
         <v>29.01</v>
@@ -5271,19 +5271,19 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>0.06012422753422365</v>
+        <v>0.05994842771092763</v>
       </c>
       <c r="V58" t="n">
-        <v>0.001103518612044737</v>
+        <v>0.00139444938472766</v>
       </c>
       <c r="W58" t="n">
-        <v>0.0009677784852073051</v>
+        <v>0.001271735640737716</v>
       </c>
       <c r="X58" t="n">
-        <v>0.03017936625857966</v>
+        <v>0.03813887234646138</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.644295858687297</v>
+        <v>1.63961880357864</v>
       </c>
     </row>
     <row r="59">
@@ -5301,13 +5301,13 @@
         <v>11.56666666666667</v>
       </c>
       <c r="D59" t="n">
-        <v>28.46405037547181</v>
+        <v>28.46082508258495</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6022852657586331</v>
+        <v>0.5992944122488968</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.360053881150505</v>
+        <v>-0.3593901699047911</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -5322,22 +5322,22 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>2.101395432153724</v>
+        <v>2.101209936580359</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.02027197462144348</v>
+        <v>-0.02085944669375994</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.008004647669356267</v>
+        <v>-0.008047887731083631</v>
       </c>
       <c r="N59" t="n">
-        <v>0.1022310869594348</v>
+        <v>0.1061209445179696</v>
       </c>
       <c r="O59" t="n">
-        <v>0.02666920580504741</v>
+        <v>0.03226238460085087</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.002189665929867298</v>
+        <v>-0.003760463504501162</v>
       </c>
       <c r="Q59" t="n">
         <v>28.995</v>
@@ -5354,19 +5354,19 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.01151259578173216</v>
+        <v>0.01112946783281489</v>
       </c>
       <c r="V59" t="n">
-        <v>0.000902295747556234</v>
+        <v>0.001096555870749458</v>
       </c>
       <c r="W59" t="n">
-        <v>0.0008609472688623766</v>
+        <v>0.001055057789264696</v>
       </c>
       <c r="X59" t="n">
-        <v>0.02568299161201464</v>
+        <v>0.03120888483068196</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.3276951062836685</v>
+        <v>0.3167538372520005</v>
       </c>
     </row>
     <row r="60">
@@ -5384,13 +5384,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>28.97786920043766</v>
+        <v>28.97201350550327</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4478876670289793</v>
+        <v>0.4463014702673647</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.09375374226497546</v>
+        <v>-0.09249258214162012</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -5405,22 +5405,22 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>2.077278721080258</v>
+        <v>2.07647899739963</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.01859795448544499</v>
+        <v>-0.01900830805976916</v>
       </c>
       <c r="M60" t="n">
-        <v>0.003248003278876897</v>
+        <v>0.003438903134404271</v>
       </c>
       <c r="N60" t="n">
-        <v>0.1302349601016103</v>
+        <v>0.1393172748434631</v>
       </c>
       <c r="O60" t="n">
-        <v>0.02432571948549465</v>
+        <v>0.028275276988164</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.002059196469469883</v>
+        <v>-0.00346125297583441</v>
       </c>
       <c r="Q60" t="n">
         <v>28.995</v>
@@ -5437,19 +5437,19 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>0.006503159819879348</v>
+        <v>0.006250466457274683</v>
       </c>
       <c r="V60" t="n">
-        <v>0.0007992209789928847</v>
+        <v>0.0009319321880903103</v>
       </c>
       <c r="W60" t="n">
-        <v>0.0007699938900783005</v>
+        <v>0.0009018756663659028</v>
       </c>
       <c r="X60" t="n">
-        <v>0.02315972099150155</v>
+        <v>0.02699995193956568</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.1884477146500055</v>
+        <v>0.1810885986158573</v>
       </c>
     </row>
     <row r="61">
@@ -5467,13 +5467,13 @@
         <v>14.13333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>29.59718463877531</v>
+        <v>29.59057689634123</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4015261467971136</v>
+        <v>0.40175875268321</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.02828585116984849</v>
+        <v>-0.02726865926126411</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -5488,22 +5488,22 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>2.056506540971785</v>
+        <v>2.055394457249715</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.01045860128395248</v>
+        <v>-0.01053053046023594</v>
       </c>
       <c r="M61" t="n">
-        <v>0.005052995665750842</v>
+        <v>0.005245462509269749</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1636983145325466</v>
+        <v>0.1770658577354137</v>
       </c>
       <c r="O61" t="n">
-        <v>0.0214448894691804</v>
+        <v>0.02351829144897399</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.001869923576551122</v>
+        <v>-0.003027186320082213</v>
       </c>
       <c r="Q61" t="n">
         <v>28.995</v>
@@ -5520,19 +5520,19 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>0.008480747496735483</v>
+        <v>0.008453890833230813</v>
       </c>
       <c r="V61" t="n">
-        <v>0.0006964305238984141</v>
+        <v>0.0007641324124643306</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0006495245736151253</v>
+        <v>0.0007135455166146369</v>
       </c>
       <c r="X61" t="n">
-        <v>0.02061238280390039</v>
+        <v>0.02261111891001251</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.2510062495357116</v>
+        <v>0.2501555067739906</v>
       </c>
     </row>
     <row r="62">
@@ -5550,13 +5550,13 @@
         <v>16.85</v>
       </c>
       <c r="D62" t="n">
-        <v>30.58366178364559</v>
+        <v>30.58143663893776</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3414107011147993</v>
+        <v>0.3432850398093028</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.01805098696945927</v>
+        <v>-0.01772006759000701</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -5571,22 +5571,22 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>2.046733815457519</v>
+        <v>2.046136056499152</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0007699931430980855</v>
+        <v>0.001028321747827049</v>
       </c>
       <c r="M62" t="n">
-        <v>0.003524164153454311</v>
+        <v>0.00359878262226218</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2150578774167018</v>
+        <v>0.2297892857166264</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01683934158891357</v>
+        <v>0.01638242028647034</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.001579655954233453</v>
+        <v>-0.002361504646655055</v>
       </c>
       <c r="Q62" t="n">
         <v>28.995</v>
@@ -5603,19 +5603,19 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>0.01153937859759997</v>
+        <v>0.01172784274873255</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0005532446614977355</v>
+        <v>0.0005394744902894036</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0004721021781200712</v>
+        <v>0.0004513513376708359</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01692024761085423</v>
+        <v>0.01649790494310864</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.3529164522224361</v>
+        <v>0.3586542799317901</v>
       </c>
     </row>
     <row r="63">
@@ -5633,13 +5633,13 @@
         <v>22.4</v>
       </c>
       <c r="D63" t="n">
-        <v>32.23233890740552</v>
+        <v>32.24347692611086</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2874586621503354</v>
+        <v>0.2880697065564881</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.0006600694074655467</v>
+        <v>-0.001495253333881036</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -5654,22 +5654,22 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>2.100525400041643</v>
+        <v>2.102143785444098</v>
       </c>
       <c r="L63" t="n">
-        <v>0.01342336372100172</v>
+        <v>0.01356350306130993</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0009263980985296924</v>
+        <v>0.0008007704937910308</v>
       </c>
       <c r="N63" t="n">
-        <v>0.2850909902199914</v>
+        <v>0.2864134953075173</v>
       </c>
       <c r="O63" t="n">
-        <v>0.009383391512969796</v>
+        <v>0.00628295733171122</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.001086437852673271</v>
+        <v>-0.001230388993487751</v>
       </c>
       <c r="Q63" t="n">
         <v>28.995</v>
@@ -5686,19 +5686,19 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>0.01530880996608005</v>
+        <v>0.01538642531270043</v>
       </c>
       <c r="V63" t="n">
-        <v>0.0003476402865753588</v>
+        <v>0.0002521738410450705</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0002122357847532248</v>
+        <v>0.0001154987590060771</v>
       </c>
       <c r="X63" t="n">
-        <v>0.01120525953476454</v>
+        <v>0.008130961425105476</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.4934387510957593</v>
+        <v>0.4961118495453845</v>
       </c>
     </row>
     <row r="64">
@@ -5716,13 +5716,13 @@
         <v>24.05</v>
       </c>
       <c r="D64" t="n">
-        <v>32.70193637387037</v>
+        <v>32.7132012455741</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2908143446361375</v>
+        <v>0.289749301117471</v>
       </c>
       <c r="F64" t="n">
-        <v>0.005958378862213135</v>
+        <v>0.004701876460281695</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -5737,22 +5737,22 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>2.124504248334809</v>
+        <v>2.126226732243604</v>
       </c>
       <c r="L64" t="n">
-        <v>0.01428797960705364</v>
+        <v>0.0141696542052645</v>
       </c>
       <c r="M64" t="n">
-        <v>-9.519851664598154e-05</v>
+        <v>-0.000293750307107845</v>
       </c>
       <c r="N64" t="n">
-        <v>0.2989865956549137</v>
+        <v>0.2948576507526223</v>
       </c>
       <c r="O64" t="n">
-        <v>0.007716826484273992</v>
+        <v>0.004541907741506215</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.0008851285948424789</v>
+        <v>-0.0007687188886404113</v>
       </c>
       <c r="Q64" t="n">
         <v>28.98</v>
@@ -5769,19 +5769,19 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>0.01561820252417522</v>
+        <v>0.01552148455655769</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0002974627596454867</v>
+        <v>0.0001989076379162201</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0001546689767463408</v>
+        <v>5.900606001244045e-05</v>
       </c>
       <c r="X64" t="n">
-        <v>0.009727608239522602</v>
+        <v>0.006506905588435094</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.5107454652197997</v>
+        <v>0.5077574479287422</v>
       </c>
     </row>
     <row r="65">
@@ -5799,13 +5799,13 @@
         <v>25.55</v>
       </c>
       <c r="D65" t="n">
-        <v>33.14662582651447</v>
+        <v>33.15473596368054</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3051036837037131</v>
+        <v>0.3018256708479612</v>
       </c>
       <c r="F65" t="n">
-        <v>0.009105086945152135</v>
+        <v>0.007836449475190063</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -5820,22 +5820,22 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>2.14560259630611</v>
+        <v>2.146900207468178</v>
       </c>
       <c r="L65" t="n">
-        <v>0.01330080708950798</v>
+        <v>0.01282750878536099</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.0008570637649848618</v>
+        <v>-0.001062783733013854</v>
       </c>
       <c r="N65" t="n">
-        <v>0.3096008091533328</v>
+        <v>0.3008853820577578</v>
       </c>
       <c r="O65" t="n">
-        <v>0.006559466523585245</v>
+        <v>0.003779460337428514</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.0006754470977203206</v>
+        <v>-0.0002878484120212748</v>
       </c>
       <c r="Q65" t="n">
         <v>29.01</v>
@@ -5852,19 +5852,19 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>0.01540376887744909</v>
+        <v>0.01507844375563558</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0002557941564727905</v>
+        <v>0.0001682178882382971</v>
       </c>
       <c r="W65" t="n">
-        <v>0.0001119176927437326</v>
+        <v>3.137821274756879e-05</v>
       </c>
       <c r="X65" t="n">
-        <v>0.008478713193212481</v>
+        <v>0.005577219668908662</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.5105829632989139</v>
+        <v>0.4999218214613053</v>
       </c>
     </row>
     <row r="66">
@@ -5882,13 +5882,13 @@
         <v>27.01666666666667</v>
       </c>
       <c r="D66" t="n">
-        <v>33.60650743528318</v>
+        <v>33.60812498901727</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3178538665585267</v>
+        <v>0.3130115732771155</v>
       </c>
       <c r="F66" t="n">
-        <v>0.006226158618857267</v>
+        <v>0.005570657085305637</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -5903,22 +5903,22 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>2.164013726761088</v>
+        <v>2.164344621577035</v>
       </c>
       <c r="L66" t="n">
-        <v>0.01175847298503752</v>
+        <v>0.0110278060126251</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.001043516318232963</v>
+        <v>-0.001154687881417951</v>
       </c>
       <c r="N66" t="n">
-        <v>0.3184804086726417</v>
+        <v>0.3060858078430974</v>
       </c>
       <c r="O66" t="n">
-        <v>0.005706662885009567</v>
+        <v>0.003673424091542817</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.0005026647215329997</v>
+        <v>0.0001083999204683676</v>
       </c>
       <c r="Q66" t="n">
         <v>29.01</v>
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>0.01489174538373089</v>
+        <v>0.01440878570365691</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0002213015142634324</v>
+        <v>0.0001557063292271108</v>
       </c>
       <c r="W66" t="n">
-        <v>8.017619307994671e-05</v>
+        <v>2.447839510156408e-05</v>
       </c>
       <c r="X66" t="n">
-        <v>0.007437170984533468</v>
+        <v>0.005232997774245813</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.5004595519626962</v>
+        <v>0.4842522708684667</v>
       </c>
     </row>
     <row r="67">
@@ -5965,13 +5965,13 @@
         <v>30.05</v>
       </c>
       <c r="D67" t="n">
-        <v>34.5976290083399</v>
+        <v>34.58195143968543</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3212622662351068</v>
+        <v>0.3170103549647241</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.00402119203103507</v>
+        <v>-0.002999851203788345</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -5986,22 +5986,22 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2.194696368779029</v>
+        <v>2.192362088260938</v>
       </c>
       <c r="L67" t="n">
-        <v>0.008643799274912711</v>
+        <v>0.007979341350247637</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.0009652523434678254</v>
+        <v>-0.0008137773671506002</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3336098964013117</v>
+        <v>0.3180295213518891</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0046762155598358</v>
+        <v>0.005135839339052373</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.0001938570609676674</v>
+        <v>0.0008166001620623204</v>
       </c>
       <c r="Q67" t="n">
         <v>28.995</v>
@@ -6018,19 +6018,19 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>0.01322416726636053</v>
+        <v>0.01280654003312175</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0001731371896756962</v>
+        <v>0.0001819834412702878</v>
       </c>
       <c r="W67" t="n">
-        <v>4.562229347686444e-05</v>
+        <v>6.420935313038018e-05</v>
       </c>
       <c r="X67" t="n">
-        <v>0.005990136255946315</v>
+        <v>0.006293342528835937</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.4575248330257741</v>
+        <v>0.4428751455358038</v>
       </c>
     </row>
     <row r="68">
@@ -6048,13 +6048,13 @@
         <v>33.05</v>
       </c>
       <c r="D68" t="n">
-        <v>35.54515317446911</v>
+        <v>35.52102140943061</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2939337794328081</v>
+        <v>0.2951987646734038</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.01481686994613171</v>
+        <v>-0.01206080308671577</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -6069,22 +6069,22 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>2.216262200589915</v>
+        <v>2.212569999624321</v>
       </c>
       <c r="L68" t="n">
-        <v>0.005930702185700687</v>
+        <v>0.006105338539264038</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.0008360712476423337</v>
+        <v>-0.0004125497145050438</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3467142302807875</v>
+        <v>0.3369925873873175</v>
       </c>
       <c r="O68" t="n">
-        <v>0.004527388652495162</v>
+        <v>0.008578068575033307</v>
       </c>
       <c r="P68" t="n">
-        <v>0.000112189132657267</v>
+        <v>0.001518467427489923</v>
       </c>
       <c r="Q68" t="n">
         <v>29.01</v>
@@ -6101,19 +6101,19 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>0.01094529989548966</v>
+        <v>0.01106992479933209</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0001534722184735378</v>
+        <v>0.0002676714073288779</v>
       </c>
       <c r="W68" t="n">
-        <v>4.670966747733546e-05</v>
+        <v>0.0001626495793439559</v>
       </c>
       <c r="X68" t="n">
-        <v>0.005455193513667488</v>
+        <v>0.009507961790421491</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.3890523613256806</v>
+        <v>0.3932150357978619</v>
       </c>
     </row>
     <row r="69">
@@ -6131,13 +6131,13 @@
         <v>35.71666666666666</v>
       </c>
       <c r="D69" t="n">
-        <v>36.27704743837425</v>
+        <v>36.26596730971526</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2408935352022574</v>
+        <v>0.2516819019482739</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.02587000667387462</v>
+        <v>-0.02204425763778248</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -6152,22 +6152,22 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2.229095697575954</v>
+        <v>2.227356071189299</v>
       </c>
       <c r="L69" t="n">
-        <v>0.003863061996459916</v>
+        <v>0.005508003926731841</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.0006937381224151099</v>
+        <v>2.952724237245924e-05</v>
       </c>
       <c r="N69" t="n">
-        <v>0.3591648130206834</v>
+        <v>0.3652174732187516</v>
       </c>
       <c r="O69" t="n">
-        <v>0.005210081099334241</v>
+        <v>0.0135068591838371</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0004493941309906995</v>
+        <v>0.002291792353591941</v>
       </c>
       <c r="Q69" t="n">
         <v>28.98</v>
@@ -6184,19 +6184,19 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>0.008373401835163687</v>
+        <v>0.00941278097290961</v>
       </c>
       <c r="V69" t="n">
-        <v>0.0001607771425911803</v>
+        <v>0.0003973422594022253</v>
       </c>
       <c r="W69" t="n">
-        <v>7.787537641016748e-05</v>
+        <v>0.0003025505762374235</v>
       </c>
       <c r="X69" t="n">
-        <v>0.005832520028786509</v>
+        <v>0.0144100013902495</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.3037622955948031</v>
+        <v>0.3413636070570498</v>
       </c>
     </row>
     <row r="70">
@@ -6214,13 +6214,13 @@
         <v>38.41666666666666</v>
       </c>
       <c r="D70" t="n">
-        <v>36.835696706298</v>
+        <v>36.86985789883801</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1546969243125667</v>
+        <v>0.1765105008120322</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.03362783079533318</v>
+        <v>-0.02962948019904615</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -6235,22 +6235,22 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>2.236930271054624</v>
+        <v>2.242127153848393</v>
       </c>
       <c r="L70" t="n">
-        <v>0.002213116736538179</v>
+        <v>0.006280808891351908</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.000585596353735072</v>
+        <v>0.0003654081831800483</v>
       </c>
       <c r="N70" t="n">
-        <v>0.3747112984822444</v>
+        <v>0.4096754511932953</v>
       </c>
       <c r="O70" t="n">
-        <v>0.006952110029900082</v>
+        <v>0.02090710538761079</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0007055955238098011</v>
+        <v>0.002879348659543106</v>
       </c>
       <c r="Q70" t="n">
         <v>28.98</v>
@@ -6267,19 +6267,19 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0.005189001400015388</v>
+        <v>0.00758866542262381</v>
       </c>
       <c r="V70" t="n">
-        <v>0.0001987971708125328</v>
+        <v>0.0005981774591723834</v>
       </c>
       <c r="W70" t="n">
-        <v>0.0001460120295966885</v>
+        <v>0.0005138568214444482</v>
       </c>
       <c r="X70" t="n">
-        <v>0.007322832290120574</v>
+        <v>0.02205471791797375</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.1911404817795225</v>
+        <v>0.2797930157739653</v>
       </c>
     </row>
     <row r="71">
@@ -6297,13 +6297,13 @@
         <v>46.41666666666666</v>
       </c>
       <c r="D71" t="n">
-        <v>36.835696706298</v>
+        <v>37.16424874161186</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.1546969243125638</v>
+        <v>-0.1029127901185696</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.04372063136094942</v>
+        <v>-0.04022634253360428</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -6318,22 +6318,22 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>2.238313376337733</v>
+        <v>2.311574514724551</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.001867340415760699</v>
+        <v>0.01108103132768778</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.0004345179343396473</v>
+        <v>0.0008346474259039211</v>
       </c>
       <c r="N71" t="n">
-        <v>0.4586340146098989</v>
+        <v>0.6822048897137082</v>
       </c>
       <c r="O71" t="n">
-        <v>0.01402856900201359</v>
+        <v>0.04722525424249244</v>
       </c>
       <c r="P71" t="n">
-        <v>0.001063519219218576</v>
+        <v>0.003700188554177305</v>
       </c>
       <c r="Q71" t="n">
         <v>28.98</v>
@@ -6350,19 +6350,19 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>-0.005033909308933797</v>
+        <v>0.002024581679390566</v>
       </c>
       <c r="V71" t="n">
-        <v>0.0003704544549032005</v>
+        <v>0.001358713073094444</v>
       </c>
       <c r="W71" t="n">
-        <v>0.0004331306696072843</v>
+        <v>0.001321548874487664</v>
       </c>
       <c r="X71" t="n">
-        <v>0.01364594794431124</v>
+        <v>0.05049555061696176</v>
       </c>
       <c r="Y71" t="n">
-        <v>-0.1854275565508955</v>
+        <v>0.07524205713058127</v>
       </c>
     </row>
     <row r="72">

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y85"/>
+  <dimension ref="A1:AB85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,45 +511,60 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dCdt</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>d2Cdt2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dTdt</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>d2Tdt2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>T_ind</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>qP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>qP_2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>rP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>rX</t>
         </is>
@@ -609,32 +624,41 @@
         <v>0.05443836246253775</v>
       </c>
       <c r="Q2" t="n">
+        <v>5.382108602445239</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.187795120142614</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.03918978104830084</v>
+      </c>
+      <c r="T2" t="n">
         <v>36.93</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>-2.423755890127565</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>-2.832949004219552</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>0.1463532815536431</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>0.001481861422009717</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>0.001481861422009717</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>0.03252295278732637</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>3.212068818003286</v>
       </c>
     </row>
@@ -692,32 +716,41 @@
         <v>0.02803753103562011</v>
       </c>
       <c r="Q3" t="n">
+        <v>5.178095790866871</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.1304671655500824</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.04385413982233808</v>
+      </c>
+      <c r="T3" t="n">
         <v>27.99</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>-4.011728271728281</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>0.2567126075990498</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>0.04654885228669232</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>0.004259619071213121</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>0.004000927121195224</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>0.1029090724521696</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>1.124583943411706</v>
       </c>
     </row>
@@ -775,32 +808,41 @@
         <v>-0.007010515913380644</v>
       </c>
       <c r="Q4" t="n">
+        <v>5.017798817704199</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.05567206474214381</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.04111207151267104</v>
+      </c>
+      <c r="T4" t="n">
         <v>28.02</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>0.002969628796401835</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>1.255370959962038</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>0.002379050554110678</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>0.003396691945955462</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>0.003366863637048577</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>0.08418768973017335</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>0.05896524415184423</v>
       </c>
     </row>
@@ -858,32 +900,41 @@
         <v>0.0089492289119854</v>
       </c>
       <c r="Q5" t="n">
+        <v>4.991936403001823</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02718058382067734</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0344387439198068</v>
+      </c>
+      <c r="T5" t="n">
         <v>27.99</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>0.0008267716535437231</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>-0.0008032708150662968</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
         <v>0.00451333120799062</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
         <v>0.002805426233814838</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>0.002723458954427426</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>0.07162075836968011</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>0.115222492751227</v>
       </c>
     </row>
@@ -941,32 +992,41 @@
         <v>0.04451854124995235</v>
       </c>
       <c r="Q6" t="n">
+        <v>5.120752463480209</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.08716816995349497</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01448825872320491</v>
+      </c>
+      <c r="T6" t="n">
         <v>28.02</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>-0.0003846153846156497</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>-0.001597293035547397</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>0.00467285042783293</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>0.004287494039538852</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>0.004176898982023491</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>0.1136926722647963</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>0.1239112748227083</v>
       </c>
     </row>
@@ -1024,32 +1084,41 @@
         <v>0.09969346862095835</v>
       </c>
       <c r="Q7" t="n">
+        <v>5.334003110521341</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.08594037729372817</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.03093166043981172</v>
+      </c>
+      <c r="T7" t="n">
         <v>27.99</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>-0.005384615384617319</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>0.002435897435898352</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>-0.003535867629664758</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>0.008575718115458847</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>0.008697292661400426</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>0.2344311580653662</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>-0.0966586741807568</v>
       </c>
     </row>
@@ -1107,32 +1176,41 @@
         <v>0.1396218551781902</v>
       </c>
       <c r="Q8" t="n">
+        <v>5.410999804581532</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.03632983611183471</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.06796230141085968</v>
+      </c>
+      <c r="T8" t="n">
         <v>27.99</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>0.002522746071134084</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>-0.01072408683700126</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>0.0124506291077784</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>0.0129360861395104</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>0.3450799875557407</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>-0.297227370619138</v>
       </c>
     </row>
@@ -1190,32 +1268,41 @@
         <v>0.1704121024990759</v>
       </c>
       <c r="Q9" t="n">
+        <v>5.411512307924802</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.05315602091197569</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.09701100421408849</v>
+      </c>
+      <c r="T9" t="n">
         <v>27.99</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>-3.767873678472845e-15</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>-0.01996525050408979</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>0.01721826501290685</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>0.01843401115738567</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>0.4831972764674675</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>-0.5602861066626278</v>
       </c>
     </row>
@@ -1273,32 +1360,41 @@
         <v>0.1885370639025594</v>
       </c>
       <c r="Q10" t="n">
+        <v>5.310807757574504</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.155198221192089</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.1141107894689042</v>
+      </c>
+      <c r="T10" t="n">
         <v>27.99</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>-1.093301050966713e-14</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>-0.03036925123769535</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>0.02162332168057842</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>0.02409735677715759</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>0.6138776078694121</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>-0.8621711121897764</v>
       </c>
     </row>
@@ -1356,32 +1452,41 @@
         <v>0.03270764869073212</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.581432186854011</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.04980168904584292</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.01623739009660047</v>
+      </c>
+      <c r="T11" t="n">
         <v>30</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>-3.138731268731276</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>0.1665283087856843</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>0.01957634192483895</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>0.005730477378495867</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>0.005581711678475328</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>0.1541828645115554</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>0.5267164103912014</v>
       </c>
     </row>
@@ -1439,32 +1544,41 @@
         <v>-0.03311824047486412</v>
       </c>
       <c r="Q12" t="n">
+        <v>3.519108708753577</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.01900331605574701</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01893889925203274</v>
+      </c>
+      <c r="T12" t="n">
         <v>30.015</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>0.001484814398200918</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>0.9812306983742416</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>-0.01788672368346078</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>0.003388454055007017</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>0.003703461135519619</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>0.08859250230768947</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>-0.4676556280473815</v>
       </c>
     </row>
@@ -1522,32 +1636,41 @@
         <v>0.03095467918531082</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.521409515630263</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.02451419553391787</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.02220594544328378</v>
+      </c>
+      <c r="T13" t="n">
         <v>30</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>-0.003442889476873212</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>0.0007682955046346132</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>0.005551541158314535</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>0.00065335460880864</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>0.0005432342243975793</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>0.01725665996943276</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>0.1466294976475842</v>
       </c>
     </row>
@@ -1605,32 +1728,41 @@
         <v>0.182774664945801</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.614709781014519</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0720375657570913</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.02527151967257393</v>
+      </c>
+      <c r="T14" t="n">
         <v>30</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>0.003945061367620184</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>-0.000879830493848421</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>0.02060035451617961</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>0.006919419059399134</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
         <v>0.006507997618334095</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>0.1979591819880729</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>0.589360073971491</v>
       </c>
     </row>
@@ -1688,32 +1820,41 @@
         <v>0.3299149962450657</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.801428699717416</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.123717550159157</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.02759689768479523</v>
+      </c>
+      <c r="T15" t="n">
         <v>30.015</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>-0.006303879310344485</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>-0.01125986265341659</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>0.007704782304053718</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>0.02389480288689215</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>0.02356291405558334</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>0.7286976789107263</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>0.2349656118969819</v>
       </c>
     </row>
@@ -1771,32 +1912,41 @@
         <v>0.3933788333966759</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.949365425797802</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1536638112415663</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.028552341844722</v>
+      </c>
+      <c r="T16" t="n">
         <v>30</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>-0.02182112068965125</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>-0.0178349649327835</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>-0.006002205126870144</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>0.03710826675459588</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>0.03756130499155563</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>1.131656451843245</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>-0.1830436921785885</v>
       </c>
     </row>
@@ -1854,32 +2004,41 @@
         <v>0.008651385330049385</v>
       </c>
       <c r="Q17" t="n">
+        <v>5.379979298695361</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.1315608109754156</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.02468276755472088</v>
+      </c>
+      <c r="T17" t="n">
         <v>32.985</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>-2.231858630801907</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>0.6327758308205903</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>0.05986481881725748</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>0.002658414417699906</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>0.002465288474968639</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>0.08234687639444917</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>1.854368830795771</v>
       </c>
     </row>
@@ -1937,32 +2096,41 @@
         <v>-0.02156544142506893</v>
       </c>
       <c r="Q18" t="n">
+        <v>5.250260856442693</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.09002716773481589</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.0518657041594046</v>
+      </c>
+      <c r="T18" t="n">
         <v>33</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>0.006259314456038112</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>0.9303108769638049</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>0.01356364238017025</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>0.001328104886506724</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>0.001259148530008072</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>0.04259121209683257</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>0.4349746584691095</v>
       </c>
     </row>
@@ -2020,32 +2188,41 @@
         <v>0.0002592121117928302</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.18832900702664</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.0304469026530354</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.076460223068408</v>
+      </c>
+      <c r="T19" t="n">
         <v>33</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
         <v>-0.009885808030295692</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>-0.004889975030627713</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>0.0009031724472148775</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>0.0009322494558017368</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>0.0295710019941917</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>-0.1601039334494191</v>
       </c>
     </row>
@@ -2103,32 +2280,41 @@
         <v>0.02377783591582186</v>
       </c>
       <c r="Q20" t="n">
+        <v>5.196355658258678</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0595392755223374</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1023999495136532</v>
+      </c>
+      <c r="T20" t="n">
         <v>33</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>-0.0132923076923035</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>-0.01896714963961562</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>-0.01714478067395405</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>0.001193680762936769</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>0.001311853177397105</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>0.03970670091213688</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>-0.5703054782838444</v>
       </c>
     </row>
@@ -2186,32 +2372,41 @@
         <v>0.04237510135172184</v>
       </c>
       <c r="Q21" t="n">
+        <v>5.32131232830413</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1850414941355272</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1229116929752026</v>
+      </c>
+      <c r="T21" t="n">
         <v>32.97000000000001</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>-0.04050011069838533</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>-0.02430530339071363</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>-0.02211396666571151</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>0.002265294001306065</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>0.002458514514707374</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>0.07628001580501038</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>-0.7446511251075507</v>
       </c>
     </row>
@@ -2269,32 +2464,41 @@
         <v>0.05281889853409094</v>
       </c>
       <c r="Q22" t="n">
+        <v>5.534965269572661</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2987010143969968</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1344306170507666</v>
+      </c>
+      <c r="T22" t="n">
         <v>32.925</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>-0.06138668175445616</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>-0.0229850461702015</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>-0.02249997190019291</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>0.003415870656222101</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>0.003673421235716655</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>0.1159396063625789</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>-0.763681692843301</v>
       </c>
     </row>
@@ -2352,32 +2556,41 @@
         <v>0.01711461552917037</v>
       </c>
       <c r="Q23" t="n">
+        <v>4.893257105708582</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.1256881547718787</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1249147605818942</v>
+      </c>
+      <c r="T23" t="n">
         <v>36.945</v>
       </c>
-      <c r="R23" t="n">
-        <v>0.1337619892107362</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.09494554408321854</v>
-      </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="n">
+        <v>-0.003671328671323693</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.02811750367545162</v>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>0.06414132474724349</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>0.002163464610398861</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>0.002036244995661479</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>0.06357793629684773</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>1.884927092948308</v>
       </c>
     </row>
@@ -2435,32 +2648,41 @@
         <v>-0.01098395222704836</v>
       </c>
       <c r="Q24" t="n">
+        <v>4.840304718125667</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.01700711652374709</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1137135168665147</v>
+      </c>
+      <c r="T24" t="n">
         <v>36.96</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>0.02289665284659392</v>
       </c>
-      <c r="S24" t="n">
-        <v>-0.06729891126568134</v>
-      </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="n">
+        <v>-0.008859523896477145</v>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>0.001613547458548002</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>0.001641107358461638</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>0.001634604904815281</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>0.05008375949492182</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>0.04924267899408696</v>
       </c>
     </row>
@@ -2518,32 +2740,41 @@
         <v>-0.01312461346510742</v>
       </c>
       <c r="Q25" t="n">
+        <v>4.912085832008034</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.113330229929598</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.08131192069080476</v>
+      </c>
+      <c r="T25" t="n">
         <v>36.98999999999999</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>-0.01371127995324173</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>-0.02077151640995265</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>-0.02577506307782374</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>0.001122917178851983</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>0.00126355522341435</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>0.03475963876522885</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>-0.797861052096557</v>
       </c>
     </row>
@@ -2601,32 +2832,41 @@
         <v>-0.01527016551214571</v>
       </c>
       <c r="Q26" t="n">
+        <v>5.065837343203529</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1756773098781128</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.04460178470623562</v>
+      </c>
+      <c r="T26" t="n">
         <v>36.93</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>-0.01679442508710238</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>0.01663001978470402</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>-0.03575021874534758</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>0.0005451306149727292</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
         <v>0.0007779428209024674</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>0.01703192442382971</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>-1.11697088199055</v>
       </c>
     </row>
@@ -2684,32 +2924,41 @@
         <v>-0.01693171964649547</v>
       </c>
       <c r="Q27" t="n">
+        <v>5.274471711623132</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.2029449958150473</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.01617279446015786</v>
+      </c>
+      <c r="T27" t="n">
         <v>36.96</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>0.02240086000955444</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>0.01044027483421081</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>-0.02738801091550864</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>-6.922170654827162e-05</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>0.0001231666903000812</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>-0.002200225291271741</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>-0.8705332084222246</v>
       </c>
     </row>
@@ -2767,32 +3016,41 @@
         <v>-0.01787689785680881</v>
       </c>
       <c r="Q28" t="n">
+        <v>5.453394436872836</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2099536009150373</v>
+      </c>
+      <c r="S28" t="n">
+        <v>9.096167422062429e-07</v>
+      </c>
+      <c r="T28" t="n">
         <v>36.975</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>0.01221452460583805</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>-0.03394720268894091</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>-0.01343081083854204</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>-0.0005384323411703187</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
         <v>-0.0004460209975923221</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>-0.01762079925527425</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>-0.4395382734757554</v>
       </c>
     </row>
@@ -2832,13 +3090,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2.119179048041742</v>
+        <v>2.118582048862152</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.009456372285179038</v>
+        <v>-0.009853543535296438</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.03398973697388988</v>
+        <v>-0.03393127261766745</v>
       </c>
       <c r="N29" t="n">
         <v>0.04237394890341881</v>
@@ -2850,33 +3108,42 @@
         <v>0.01325311210845598</v>
       </c>
       <c r="Q29" t="n">
+        <v>4.4436849666609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.08104735890804182</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.004153435985263555</v>
+      </c>
+      <c r="T29" t="n">
         <v>29.01</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>-2.748181818181823</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>1.005687371927268</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U29" t="n">
-        <v>0.02261003493142559</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.001200259006210183</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
+        <v>0.02242130717910869</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.001200007948788349</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.001170181728185258</v>
       </c>
-      <c r="X29" t="n">
-        <v>0.03823284489599749</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.720216181802099</v>
+      <c r="AA29" t="n">
+        <v>0.03822484775586416</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.7142044802905348</v>
       </c>
     </row>
     <row r="30">
@@ -2915,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2.088927690428526</v>
+        <v>2.087943712149676</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.02615655681116524</v>
+        <v>-0.0263646264011268</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.003872547638034603</v>
+        <v>-0.00368158111912415</v>
       </c>
       <c r="N30" t="n">
         <v>0.08735887304521579</v>
@@ -2933,33 +3200,42 @@
         <v>0.003937378394383906</v>
       </c>
       <c r="Q30" t="n">
+        <v>4.36089504837672</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.07688758882839108</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.003727691778091291</v>
+      </c>
+      <c r="T30" t="n">
         <v>28.995</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>0.002695417789759347</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>1.190800664620253</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U30" t="n">
-        <v>-0.004289525333668436</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0.001356088509913993</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
+        <v>-0.00439507918344624</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.001355798815815219</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.001367861175509034</v>
       </c>
-      <c r="X30" t="n">
-        <v>0.04316477567112677</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>-0.1365371046283376</v>
+      <c r="AA30" t="n">
+        <v>0.0431555546057646</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.1398969209040258</v>
       </c>
     </row>
     <row r="31">
@@ -2998,13 +3274,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.067795170069929</v>
+        <v>2.066746654592486</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.02063577719138032</v>
+        <v>-0.02066708217998214</v>
       </c>
       <c r="M31" t="n">
-        <v>0.006350757477629117</v>
+        <v>0.006482206601184117</v>
       </c>
       <c r="N31" t="n">
         <v>0.1275061606761601</v>
@@ -3016,33 +3292,42 @@
         <v>0.002447857918222877</v>
       </c>
       <c r="Q31" t="n">
+        <v>4.294434161386915</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.07376868045082707</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.003325214549208928</v>
+      </c>
+      <c r="T31" t="n">
         <v>29.01</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>-0.007412807318470271</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>-0.006531296795447801</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U31" t="n">
-        <v>0.007552124862059606</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.00140238289834316</v>
-      </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
+        <v>0.007531914954916926</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.001402303052149108</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.001372545629770688</v>
       </c>
-      <c r="X31" t="n">
-        <v>0.04525930432374699</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0.243730808345363</v>
+      <c r="AA31" t="n">
+        <v>0.0452567274360796</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.2430785711148564</v>
       </c>
     </row>
     <row r="32">
@@ -3081,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.05200661583767</v>
+        <v>2.050969124835325</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.01471834531695149</v>
+        <v>-0.01469447030121729</v>
       </c>
       <c r="M32" t="n">
-        <v>0.00589501481217024</v>
+        <v>0.005939706142162673</v>
       </c>
       <c r="N32" t="n">
         <v>0.1711895453687214</v>
@@ -3099,33 +3384,42 @@
         <v>0.002192943138090632</v>
       </c>
       <c r="Q32" t="n">
+        <v>4.228211276665901</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.07091616962933611</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.002907514964359856</v>
+      </c>
+      <c r="T32" t="n">
         <v>28.98</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>-0.008727272727270474</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>0.003836681689712501</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U32" t="n">
-        <v>0.01151224982399719</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.001443646344088566</v>
-      </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
+        <v>0.01152026235112545</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.001443688095320562</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.001383658951160251</v>
       </c>
-      <c r="X32" t="n">
-        <v>0.04742837791405936</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0.3782140532751594</v>
+      <c r="AA32" t="n">
+        <v>0.0474297495749357</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.3784772902973303</v>
       </c>
     </row>
     <row r="33">
@@ -3164,13 +3458,13 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2.037879477419884</v>
+        <v>2.036892026179754</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.008304745121873958</v>
+        <v>-0.008251434986332407</v>
       </c>
       <c r="M33" t="n">
-        <v>0.004791853458431045</v>
+        <v>0.004813076203440217</v>
       </c>
       <c r="N33" t="n">
         <v>0.233717249579028</v>
@@ -3182,33 +3476,42 @@
         <v>0.001858787740399326</v>
       </c>
       <c r="Q33" t="n">
+        <v>4.14182795782078</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-0.06763004016716101</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.00235997287669356</v>
+      </c>
+      <c r="T33" t="n">
         <v>29.01</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>0.005052631578946531</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>0.003652687869404902</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U33" t="n">
-        <v>0.01269500588359046</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.001495535766120965</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.001407200111008051</v>
-      </c>
       <c r="X33" t="n">
-        <v>0.05023245951248487</v>
+        <v>0.0127192025930611</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4264032887105389</v>
+        <v>0.001495704134076228</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.001407200111008052</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.05023811470087122</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.4272160143279087</v>
       </c>
     </row>
     <row r="34">
@@ -3247,13 +3550,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2.030740878677251</v>
+        <v>2.029864465571743</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.001397580689606936</v>
+        <v>-0.001315331494756711</v>
       </c>
       <c r="M34" t="n">
-        <v>0.003858036097509609</v>
+        <v>0.003872853880913475</v>
       </c>
       <c r="N34" t="n">
         <v>0.3170919465744321</v>
@@ -3265,33 +3568,42 @@
         <v>0.001406724296956905</v>
       </c>
       <c r="Q34" t="n">
+        <v>4.037708494123475</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.06443277189122842</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.001619228410825142</v>
+      </c>
+      <c r="T34" t="n">
         <v>28.98</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
         <v>-0.003947368421052921</v>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
         <v>-3.304773561734311e-05</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U34" t="n">
-        <v>0.013895435626426</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.001556199325996475</v>
-      </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
+        <v>0.01393565803438747</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.001556569760096159</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.001428227296302814</v>
       </c>
-      <c r="X34" t="n">
-        <v>0.05358059640601906</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.4784256847744172</v>
+      <c r="AA34" t="n">
+        <v>0.05359335060765547</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4798105591741548</v>
       </c>
     </row>
     <row r="35">
@@ -3330,13 +3642,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2.035805105904229</v>
+        <v>2.035123809748424</v>
       </c>
       <c r="L35" t="n">
-        <v>0.00504425939445094</v>
+        <v>0.005147404323151916</v>
       </c>
       <c r="M35" t="n">
-        <v>0.00277091710397757</v>
+        <v>0.002778278444927796</v>
       </c>
       <c r="N35" t="n">
         <v>0.4275724209378097</v>
@@ -3348,33 +3660,42 @@
         <v>0.000880447129478692</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.912195091961094</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.06220509129191787</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.000756878435445342</v>
+      </c>
+      <c r="T35" t="n">
         <v>29.01</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
         <v>0.01026315789473919</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
         <v>0.004113573407202947</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U35" t="n">
-        <v>0.01464744162082032</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.001613565936864088</v>
-      </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
+        <v>0.01469895348670153</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.001614188826634182</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.001436446716125748</v>
       </c>
-      <c r="X35" t="n">
-        <v>0.0570548390909788</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0.5179257975627443</v>
+      <c r="AA35" t="n">
+        <v>0.05707686414418066</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.5197472299269156</v>
       </c>
     </row>
     <row r="36">
@@ -3413,13 +3734,13 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2.081249820890327</v>
+        <v>2.0810679366867</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01282653925998256</v>
+        <v>0.01293260428336784</v>
       </c>
       <c r="M36" t="n">
-        <v>0.000729018955751449</v>
+        <v>0.0007223751177570957</v>
       </c>
       <c r="N36" t="n">
         <v>0.6773094646637046</v>
@@ -3431,33 +3752,42 @@
         <v>-0.0001080411410060017</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.647818699384286</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.0622767600189591</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-0.0008628438105337151</v>
+      </c>
+      <c r="T36" t="n">
         <v>29.01</v>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
         <v>-0.001697894736842141</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U36" t="n">
-        <v>0.01400682681814485</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.001678444171120302</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
+        <v>0.01405833208429614</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.001679389488812514</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.001421365581058319</v>
       </c>
-      <c r="X36" t="n">
-        <v>0.06193952838895142</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.5168931217786843</v>
+      <c r="AA36" t="n">
+        <v>0.0619744133931957</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.5187938176432531</v>
       </c>
     </row>
     <row r="37">
@@ -3496,13 +3826,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.104126935900627</v>
+        <v>2.104115939627864</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01335766586415282</v>
+        <v>0.01344796698703571</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0001620711106730724</v>
+        <v>-0.000174770223113503</v>
       </c>
       <c r="N37" t="n">
         <v>0.7736707373393487</v>
@@ -3514,33 +3844,42 @@
         <v>-0.0005551800082818237</v>
       </c>
       <c r="Q37" t="n">
+        <v>3.543212033153671</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-0.06425733616056928</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-0.001595518938801424</v>
+      </c>
+      <c r="T37" t="n">
         <v>29.01</v>
       </c>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
         <v>-0.002399999999999736</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>-0.001728000000000164</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U37" t="n">
-        <v>0.01280651722767065</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.001664738806095621</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.001399411151259112</v>
-      </c>
       <c r="X37" t="n">
-        <v>0.06216569505919414</v>
+        <v>0.01284946682422651</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4782288019181078</v>
+        <v>0.001665628643318947</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.001399411151259113</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.06219892390522995</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.4798326520311891</v>
       </c>
     </row>
     <row r="38">
@@ -3579,13 +3918,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.136138838778407</v>
+        <v>2.136307726679219</v>
       </c>
       <c r="L38" t="n">
-        <v>0.01114968656306303</v>
+        <v>0.01119608700932362</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.001120220367477728</v>
+        <v>-0.001138616477818967</v>
       </c>
       <c r="N38" t="n">
         <v>0.9146965461484002</v>
@@ -3597,33 +3936,42 @@
         <v>-0.001262511799616995</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.376968681168996</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.06977303320945527</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-0.002754542340416524</v>
+      </c>
+      <c r="T38" t="n">
         <v>28.995</v>
       </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
         <v>-0.007800000000001361</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>0.001280265389876509</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U38" t="n">
-        <v>0.009878069247843929</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.001577065205328077</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
+        <v>0.009899376537334748</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.001577579980104474</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.001338415381262659</v>
       </c>
-      <c r="X38" t="n">
-        <v>0.05970870294250062</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0.3739900546739069</v>
+      <c r="AA38" t="n">
+        <v>0.05972819264660566</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.3747967623575328</v>
       </c>
     </row>
     <row r="39">
@@ -3662,13 +4010,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2.152882677952347</v>
+        <v>2.153100507460072</v>
       </c>
       <c r="L39" t="n">
-        <v>0.009019287453887026</v>
+        <v>0.009034099005476304</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.001172038739690828</v>
+        <v>-0.001189248780778295</v>
       </c>
       <c r="N39" t="n">
         <v>1.004613956853115</v>
@@ -3680,33 +4028,42 @@
         <v>-0.001716623534717529</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.257040634247031</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.0749731187999963</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-0.003498643106672418</v>
+      </c>
+      <c r="T39" t="n">
         <v>28.98</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
         <v>-0.001843707250343662</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>0.003175124770036624</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U39" t="n">
-        <v>0.007803255159356828</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.001486533797816385</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
+        <v>0.007809710490412796</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.001486703920022411</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.00128088873168627</v>
       </c>
-      <c r="X39" t="n">
-        <v>0.056667168024161</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.2974627094925246</v>
+      <c r="AA39" t="n">
+        <v>0.05667365313983593</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.2977087888821338</v>
       </c>
     </row>
     <row r="40">
@@ -3745,13 +4102,13 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.173674094847271</v>
+        <v>2.173862626110031</v>
       </c>
       <c r="L40" t="n">
-        <v>0.00618308344552404</v>
+        <v>0.006157155156069571</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0007271339905342432</v>
+        <v>-0.0007378361832202983</v>
       </c>
       <c r="N40" t="n">
         <v>1.147638215923621</v>
@@ -3763,33 +4120,42 @@
         <v>-0.002463198348949519</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.027245369937801</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-0.08686927210603346</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-0.00472196954463445</v>
+      </c>
+      <c r="T40" t="n">
         <v>29.01</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
         <v>0.005292702485967915</v>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
         <v>0.0003672343035050341</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U40" t="n">
-        <v>0.004932345324158175</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0.001292417196996624</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.001145107722561769</v>
-      </c>
       <c r="X40" t="n">
-        <v>0.04966272259376639</v>
+        <v>0.00492017133847639</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1895314439792061</v>
+        <v>0.001292053608619351</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.001145107722561768</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.04964875126255786</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.189063643585355</v>
       </c>
     </row>
     <row r="41">
@@ -3828,13 +4194,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>2.188600271910131</v>
+        <v>2.188665598589384</v>
       </c>
       <c r="L41" t="n">
-        <v>0.004837282148425159</v>
+        <v>0.004790494340636997</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0001819506659246502</v>
+        <v>-0.0001853570266502533</v>
       </c>
       <c r="N41" t="n">
         <v>1.273252413771963</v>
@@ -3846,33 +4212,42 @@
         <v>-0.003189110866347219</v>
       </c>
       <c r="Q41" t="n">
+        <v>2.752294038039425</v>
+      </c>
+      <c r="R41" t="n">
+        <v>-0.102437715694196</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-0.005911439048897982</v>
+      </c>
+      <c r="T41" t="n">
         <v>29.01</v>
       </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
         <v>-8.881784197001252e-16</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>-0.001450367332429243</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U41" t="n">
-        <v>0.003028442712860842</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.001061087283189659</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.0009611452374981003</v>
-      </c>
       <c r="X41" t="n">
-        <v>0.0409389543608467</v>
+        <v>0.003006999421581447</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.116843618777107</v>
+        <v>0.001060379630247201</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.0009611452374981006</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.040911651638466</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.1160162919992433</v>
       </c>
     </row>
     <row r="42">
@@ -3911,13 +4286,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.202485451218219</v>
+        <v>2.202393841662053</v>
       </c>
       <c r="L42" t="n">
-        <v>0.005153757308895945</v>
+        <v>0.005108257998318599</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0004841143620388914</v>
+        <v>0.00048962151407011</v>
       </c>
       <c r="N42" t="n">
         <v>1.374160465684623</v>
@@ -3929,33 +4304,42 @@
         <v>-0.004075977575900037</v>
       </c>
       <c r="Q42" t="n">
+        <v>2.414263131103091</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-0.1222637205931832</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-0.007364645709586715</v>
+      </c>
+      <c r="T42" t="n">
         <v>29.01</v>
       </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
         <v>-0.003289156626505196</v>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
         <v>-0.000863537809759762</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U42" t="n">
-        <v>0.002144761606631627</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.0007902155798456332</v>
-      </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
+        <v>0.002124199913351062</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.0007894837768204511</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.0007138822248728211</v>
       </c>
-      <c r="X42" t="n">
-        <v>0.03051038681894646</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0.0828096888010473</v>
+      <c r="AA42" t="n">
+        <v>0.03048213175293277</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.08201579757485161</v>
       </c>
     </row>
     <row r="43">
@@ -3994,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.216557122654333</v>
+        <v>2.216364617658036</v>
       </c>
       <c r="L43" t="n">
-        <v>0.007146560847689637</v>
+        <v>0.007125301339026086</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0009037293549751451</v>
+        <v>0.0009148519400879045</v>
       </c>
       <c r="N43" t="n">
         <v>1.430093764837538</v>
@@ -4012,33 +4396,42 @@
         <v>-0.004634695647620763</v>
       </c>
       <c r="Q43" t="n">
+        <v>2.086299653662603</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-0.1423826153722847</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-0.008280152870387792</v>
+      </c>
+      <c r="T43" t="n">
         <v>28.995</v>
       </c>
-      <c r="R43" t="n">
+      <c r="U43" t="n">
         <v>-0.004993057044509142</v>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
         <v>-0.0003015479359590531</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U43" t="n">
-        <v>0.002859805695050554</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.0005361940506457551</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.0004301220245453036</v>
-      </c>
       <c r="X43" t="n">
-        <v>0.02067388833973052</v>
+        <v>0.002850493671510228</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1102647512436897</v>
+        <v>0.0005358486617244983</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.0004301220245453035</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.02066057127292748</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.1099057100818981</v>
       </c>
     </row>
     <row r="44">
@@ -4077,13 +4470,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2.300815726331576</v>
+        <v>2.300873631626354</v>
       </c>
       <c r="L44" t="n">
-        <v>0.01599081315979101</v>
+        <v>0.01608083521977965</v>
       </c>
       <c r="M44" t="n">
-        <v>0.001524898282215161</v>
+        <v>0.001544333564924516</v>
       </c>
       <c r="N44" t="n">
         <v>1.41318925985422</v>
@@ -4095,33 +4488,42 @@
         <v>-0.005461783123241583</v>
       </c>
       <c r="Q44" t="n">
+        <v>0.8116881888459335</v>
+      </c>
+      <c r="R44" t="n">
+        <v>-0.2076251095201643</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-0.009635406163354884</v>
+      </c>
+      <c r="T44" t="n">
         <v>28.98</v>
       </c>
-      <c r="R44" t="n">
+      <c r="U44" t="n">
         <v>0.0008740639094950708</v>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
         <v>0.001912656664747394</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U44" t="n">
-        <v>0.007694266799697597</v>
-      </c>
-      <c r="V44" t="n">
-        <v>-0.0002818745868992157</v>
-      </c>
-      <c r="W44" t="n">
-        <v>-0.0005634958511517288</v>
-      </c>
       <c r="X44" t="n">
-        <v>-0.01088323604351843</v>
+        <v>0.007733217054651834</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.2970772309915856</v>
+        <v>-0.0002804489513801041</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-0.0005634958511517286</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-0.01082819196154852</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.2985811083836037</v>
       </c>
     </row>
     <row r="45">
@@ -4139,13 +4541,13 @@
         <v>12.81666666666666</v>
       </c>
       <c r="D45" t="n">
-        <v>24.45549776089937</v>
+        <v>24.68889995641544</v>
       </c>
       <c r="E45" t="n">
-        <v>0.445803291611619</v>
+        <v>0.4683694028493468</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.06034668239199277</v>
+        <v>-0.08062752562744983</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -4178,33 +4580,42 @@
         <v>0.01087678132715291</v>
       </c>
       <c r="Q45" t="n">
+        <v>3.751634109924598</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-0.1081815037588462</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.007504281528254799</v>
+      </c>
+      <c r="T45" t="n">
         <v>31.995</v>
       </c>
-      <c r="R45" t="n">
+      <c r="U45" t="n">
         <v>-3.384772978959054</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>0.9130218985931944</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U45" t="n">
-        <v>0.02185495879141676</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.00260592489706846</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.002536304364241857</v>
-      </c>
       <c r="X45" t="n">
+        <v>0.02259664368840858</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.002581289186550797</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.002509986473448647</v>
+      </c>
+      <c r="AA45" t="n">
         <v>0.06372919048532963</v>
       </c>
-      <c r="Y45" t="n">
-        <v>0.5344738957880404</v>
+      <c r="AB45" t="n">
+        <v>0.557886275373886</v>
       </c>
     </row>
     <row r="46">
@@ -4222,13 +4633,13 @@
         <v>14.25</v>
       </c>
       <c r="D46" t="n">
-        <v>25.06915330805948</v>
+        <v>25.31373903863702</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4114164825728679</v>
+        <v>0.4070633236283516</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.02324528555518547</v>
+        <v>-0.03999284415639892</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -4261,33 +4672,42 @@
         <v>-0.00710389630350909</v>
       </c>
       <c r="Q46" t="n">
+        <v>3.604326670005563</v>
+      </c>
+      <c r="R46" t="n">
+        <v>-0.09771938685462644</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.007021889859726835</v>
+      </c>
+      <c r="T46" t="n">
         <v>32.01</v>
       </c>
-      <c r="R46" t="n">
+      <c r="U46" t="n">
         <v>0.005351479915431057</v>
       </c>
-      <c r="S46" t="n">
+      <c r="V46" t="n">
         <v>1.205641422530969</v>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U46" t="n">
-        <v>0.01259008626540013</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0.002082188499211797</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.002001364360438363</v>
-      </c>
       <c r="X46" t="n">
+        <v>0.01225954956265338</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.002062070033326432</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.001984128263847106</v>
+      </c>
+      <c r="AA46" t="n">
         <v>0.05219870270301883</v>
       </c>
-      <c r="Y46" t="n">
-        <v>0.3156228027490097</v>
+      <c r="AB46" t="n">
+        <v>0.3103350383602442</v>
       </c>
     </row>
     <row r="47">
@@ -4305,13 +4725,13 @@
         <v>15.75</v>
       </c>
       <c r="D47" t="n">
-        <v>25.66003890680712</v>
+        <v>25.87901339418912</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3777188338396273</v>
+        <v>0.3514361884151525</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.02151288469179706</v>
+        <v>-0.03353544752169235</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -4344,33 +4764,42 @@
         <v>-0.00637303148429085</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.465680010216048</v>
+      </c>
+      <c r="R47" t="n">
+        <v>-0.08762178809163856</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.006377596591206413</v>
+      </c>
+      <c r="T47" t="n">
         <v>32.01</v>
       </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
         <v>-0.006428571428570784</v>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
         <v>-0.00507509626236555</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U47" t="n">
-        <v>0.01032553116695748</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.001622422962937229</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.001529015683270528</v>
-      </c>
       <c r="X47" t="n">
+        <v>0.009185380437406458</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.001608694880215739</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.001526304773401577</v>
+      </c>
+      <c r="AA47" t="n">
         <v>0.04163143635226656</v>
       </c>
-      <c r="Y47" t="n">
-        <v>0.2649535314775784</v>
+      <c r="AB47" t="n">
+        <v>0.2377085833703645</v>
       </c>
     </row>
     <row r="48">
@@ -4388,13 +4817,13 @@
         <v>17.75</v>
       </c>
       <c r="D48" t="n">
-        <v>26.37226351139624</v>
+        <v>26.51411675247832</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3372323030258908</v>
+        <v>0.2938301181373864</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0193730955314233</v>
+        <v>-0.02555954101228416</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -4427,33 +4856,42 @@
         <v>-0.005470297797812553</v>
       </c>
       <c r="Q48" t="n">
+        <v>3.303261283191983</v>
+      </c>
+      <c r="R48" t="n">
+        <v>-0.07581095735576482</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.005581792466871252</v>
+      </c>
+      <c r="T48" t="n">
         <v>31.98</v>
       </c>
-      <c r="R48" t="n">
+      <c r="U48" t="n">
         <v>-0.009170040485829034</v>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
         <v>-0.0006732215153267947</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U48" t="n">
-        <v>0.01078590074156519</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.001151477456453691</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.001026898118111597</v>
-      </c>
       <c r="X48" t="n">
+        <v>0.009080540634536722</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.001145316934089104</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.001040995980311698</v>
+      </c>
+      <c r="AA48" t="n">
         <v>0.03036706690902902</v>
       </c>
-      <c r="Y48" t="n">
-        <v>0.2844486165643213</v>
+      <c r="AB48" t="n">
+        <v>0.2407625145597302</v>
       </c>
     </row>
     <row r="49">
@@ -4471,13 +4909,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>27.65634127581926</v>
+        <v>27.56466149717262</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2614521506647343</v>
+        <v>0.2135249130505557</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01541382259815037</v>
+        <v>-0.01080164273625846</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -4510,33 +4948,42 @@
         <v>-0.003799960777227666</v>
       </c>
       <c r="Q49" t="n">
+        <v>3.025432170228625</v>
+      </c>
+      <c r="R49" t="n">
+        <v>-0.05466164945932772</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.004109308267022663</v>
+      </c>
+      <c r="T49" t="n">
         <v>31.995</v>
       </c>
-      <c r="R49" t="n">
+      <c r="U49" t="n">
         <v>-0.005538461538462158</v>
       </c>
-      <c r="S49" t="n">
+      <c r="V49" t="n">
         <v>0.0002927935222678262</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U49" t="n">
-        <v>0.01277841909339471</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.0004343892229278844</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0.0002544555347030464</v>
-      </c>
       <c r="X49" t="n">
+        <v>0.01107114134851897</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.0004358339969842826</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.0002794220895654797</v>
+      </c>
+      <c r="AA49" t="n">
         <v>0.0120136165958315</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0.3534043194123691</v>
+      <c r="AB49" t="n">
+        <v>0.3051722636592766</v>
       </c>
     </row>
     <row r="50">
@@ -4554,13 +5001,13 @@
         <v>23.75</v>
       </c>
       <c r="D50" t="n">
-        <v>28.06974006072264</v>
+        <v>27.90200526919842</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2370918725330791</v>
+        <v>0.2004775134057626</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01361837208848466</v>
+        <v>-0.004341779320751256</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -4593,33 +5040,42 @@
         <v>-0.003042496589870878</v>
       </c>
       <c r="Q50" t="n">
+        <v>2.940388883453159</v>
+      </c>
+      <c r="R50" t="n">
+        <v>-0.04830722622425132</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.003441566347823866</v>
+      </c>
+      <c r="T50" t="n">
         <v>31.98</v>
       </c>
-      <c r="R50" t="n">
+      <c r="U50" t="n">
         <v>-0.005399999999998961</v>
       </c>
-      <c r="S50" t="n">
+      <c r="V50" t="n">
         <v>0.002641846153846253</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U50" t="n">
-        <v>0.01255118850536495</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0.000234947974791381</v>
-      </c>
-      <c r="W50" t="n">
-        <v>5.536719556029123e-05</v>
-      </c>
       <c r="X50" t="n">
+        <v>0.01128971708020165</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.0002363603804299884</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>7.385751154063015e-05</v>
+      </c>
+      <c r="AA50" t="n">
         <v>0.00659492858018728</v>
       </c>
-      <c r="Y50" t="n">
-        <v>0.3523085987987239</v>
+      <c r="AB50" t="n">
+        <v>0.3150057454595456</v>
       </c>
     </row>
     <row r="51">
@@ -4637,13 +5093,13 @@
         <v>26.25</v>
       </c>
       <c r="D51" t="n">
-        <v>28.62141699802177</v>
+        <v>28.39596624092639</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2067876727762741</v>
+        <v>0.2026980418518516</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0107868393137892</v>
+        <v>0.002663315221819396</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -4676,33 +5132,42 @@
         <v>-0.001847930289874596</v>
       </c>
       <c r="Q51" t="n">
+        <v>2.829816114796388</v>
+      </c>
+      <c r="R51" t="n">
+        <v>-0.04109488882927403</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.002388497427756134</v>
+      </c>
+      <c r="T51" t="n">
         <v>31.98</v>
       </c>
-      <c r="R51" t="n">
+      <c r="U51" t="n">
         <v>0.01079999999999792</v>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
         <v>0.002030397093453932</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U51" t="n">
-        <v>0.01079980405549942</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.282130564689127e-05</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-0.0001400405217158347</v>
-      </c>
       <c r="X51" t="n">
+        <v>0.01071314507549516</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.292310084697419e-05</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-0.0001399160573498471</v>
+      </c>
+      <c r="AA51" t="n">
         <v>0.0003669639353787663</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0.3091056953693756</v>
+      <c r="AB51" t="n">
+        <v>0.3042101058979073</v>
       </c>
     </row>
     <row r="52">
@@ -4720,13 +5185,13 @@
         <v>27.91666666666666</v>
       </c>
       <c r="D52" t="n">
-        <v>28.95063745026737</v>
+        <v>28.73947814752466</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1902927634632174</v>
+        <v>0.2091092381586437</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.008955076321904357</v>
+        <v>0.00312787002091983</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -4759,33 +5224,42 @@
         <v>-0.001075146602099324</v>
       </c>
       <c r="Q52" t="n">
+        <v>2.764807098562525</v>
+      </c>
+      <c r="R52" t="n">
+        <v>-0.03766565703883024</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.001707250615809435</v>
+      </c>
+      <c r="T52" t="n">
         <v>32.01</v>
       </c>
-      <c r="R52" t="n">
+      <c r="U52" t="n">
         <v>0.009239991926260238</v>
       </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
         <v>-0.002523729481803018</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U52" t="n">
-        <v>0.009400590091008743</v>
-      </c>
-      <c r="V52" t="n">
-        <v>-8.299733729467654e-05</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-0.0002130620407340354</v>
-      </c>
       <c r="X52" t="n">
+        <v>0.01010361003865073</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-8.360714864137821e-05</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-0.0002244257957790428</v>
+      </c>
+      <c r="AA52" t="n">
         <v>-0.002402825821355735</v>
       </c>
-      <c r="Y52" t="n">
-        <v>0.27215307554337</v>
+      <c r="AB52" t="n">
+        <v>0.2903724799169134</v>
       </c>
     </row>
     <row r="53">
@@ -4803,13 +5277,13 @@
         <v>30.7</v>
       </c>
       <c r="D53" t="n">
-        <v>29.44663520267652</v>
+        <v>29.3354530945887</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1697457663601689</v>
+        <v>0.2144738188390969</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.006025849868610385</v>
+        <v>0.0001867597164298407</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -4842,33 +5316,42 @@
         <v>0.0001606346812521692</v>
       </c>
       <c r="Q53" t="n">
+        <v>2.666198413653078</v>
+      </c>
+      <c r="R53" t="n">
+        <v>-0.03454200862781115</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.0006178486617255188</v>
+      </c>
+      <c r="T53" t="n">
         <v>31.995</v>
       </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
         <v>-0.005164397200911885</v>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
         <v>-0.001490830113050614</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U53" t="n">
-        <v>0.007671996076401387</v>
-      </c>
-      <c r="V53" t="n">
-        <v>-0.0001338956363148501</v>
-      </c>
-      <c r="W53" t="n">
-        <v>-0.0002347210571808174</v>
-      </c>
       <c r="X53" t="n">
+        <v>0.009218553547411518</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-0.0001344031041579832</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-0.000256012555725294</v>
+      </c>
+      <c r="AA53" t="n">
         <v>-0.003942775957793638</v>
       </c>
-      <c r="Y53" t="n">
-        <v>0.2259144697381572</v>
+      <c r="AB53" t="n">
+        <v>0.2704304451900449</v>
       </c>
     </row>
     <row r="54">
@@ -4886,13 +5369,13 @@
         <v>33.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29.93609460971918</v>
+        <v>29.99077163834306</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1558999872100433</v>
+        <v>0.2092258601148522</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.003007141875694268</v>
+        <v>-0.003687345484199168</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -4925,33 +5408,42 @@
         <v>0.001434166412932715</v>
       </c>
       <c r="Q54" t="n">
+        <v>2.563807363985861</v>
+      </c>
+      <c r="R54" t="n">
+        <v>-0.03434345135035966</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-0.0005048321684275239</v>
+      </c>
+      <c r="T54" t="n">
         <v>31.98</v>
       </c>
-      <c r="R54" t="n">
+      <c r="U54" t="n">
         <v>0.00260262837013947</v>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
         <v>0.001602920970721021</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U54" t="n">
-        <v>0.006825500122633723</v>
-      </c>
-      <c r="V54" t="n">
-        <v>-5.593935988448026e-05</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-0.0001410658547978875</v>
-      </c>
       <c r="X54" t="n">
+        <v>0.008594081762279918</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-5.583737524672274e-05</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-0.0001628259141966199</v>
+      </c>
+      <c r="AA54" t="n">
         <v>-0.001674605969908931</v>
       </c>
-      <c r="Y54" t="n">
-        <v>0.204328817429813</v>
+      <c r="AB54" t="n">
+        <v>0.2577431435737859</v>
       </c>
     </row>
     <row r="55">
@@ -4969,13 +5461,13 @@
         <v>36.75</v>
       </c>
       <c r="D55" t="n">
-        <v>30.390284223113</v>
+        <v>30.6018281992158</v>
       </c>
       <c r="E55" t="n">
-        <v>0.151400568340641</v>
+        <v>0.1923604369357763</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0005402875017627914</v>
+        <v>-0.008239993382676031</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -5008,33 +5500,42 @@
         <v>0.002930754982840081</v>
       </c>
       <c r="Q55" t="n">
+        <v>2.458497161231485</v>
+      </c>
+      <c r="R55" t="n">
+        <v>-0.03753971711341153</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-0.001824148567276949</v>
+      </c>
+      <c r="T55" t="n">
         <v>32.01</v>
       </c>
-      <c r="R55" t="n">
+      <c r="U55" t="n">
         <v>0.004626865671641944</v>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
         <v>-0.0006501566143000317</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U55" t="n">
-        <v>0.007053594521764335</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0.0001547981863926214</v>
-      </c>
-      <c r="W55" t="n">
-        <v>6.82282284617594e-05</v>
-      </c>
       <c r="X55" t="n">
+        <v>0.008357633708259597</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.0001537280992190768</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>5.186252481645814e-05</v>
+      </c>
+      <c r="AA55" t="n">
         <v>0.004704360881694189</v>
       </c>
-      <c r="Y55" t="n">
-        <v>0.214360742311011</v>
+      <c r="AB55" t="n">
+        <v>0.2557588708921351</v>
       </c>
     </row>
     <row r="56">
@@ -5052,13 +5553,13 @@
         <v>39.33333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>30.78141132408451</v>
+        <v>31.07356626059552</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1573345752518907</v>
+        <v>0.165249536401546</v>
       </c>
       <c r="F56" t="n">
-        <v>0.002879070817613808</v>
+        <v>-0.01124150682098886</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -5091,33 +5592,42 @@
         <v>0.00391744027113252</v>
       </c>
       <c r="Q56" t="n">
+        <v>2.356099883078157</v>
+      </c>
+      <c r="R56" t="n">
+        <v>-0.04393991643780183</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-0.002693960155794071</v>
+      </c>
+      <c r="T56" t="n">
         <v>32.01</v>
       </c>
-      <c r="R56" t="n">
+      <c r="U56" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="S56" t="n">
+      <c r="V56" t="n">
         <v>-0.001336688081686393</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U56" t="n">
-        <v>0.0083529398606636</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0.0004771904260518148</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0.0003707714716539693</v>
-      </c>
       <c r="X56" t="n">
+        <v>0.008559599594553626</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.0004727038622162495</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.0003646773109866234</v>
+      </c>
+      <c r="AA56" t="n">
         <v>0.01468859478421604</v>
       </c>
-      <c r="Y56" t="n">
-        <v>0.2571152776164274</v>
+      <c r="AB56" t="n">
+        <v>0.2659772851655287</v>
       </c>
     </row>
     <row r="57">
@@ -5135,13 +5645,13 @@
         <v>46.93333333333334</v>
       </c>
       <c r="D57" t="n">
-        <v>32.10975323236918</v>
+        <v>31.94134358797329</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1922290848230235</v>
+        <v>0.0631129181715524</v>
       </c>
       <c r="F57" t="n">
-        <v>0.006303694859000092</v>
+        <v>-0.01563655060795684</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -5174,33 +5684,42 @@
         <v>0.005362219758256564</v>
       </c>
       <c r="Q57" t="n">
+        <v>1.925963527392448</v>
+      </c>
+      <c r="R57" t="n">
+        <v>-0.06925386137422668</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-0.003967604301159836</v>
+      </c>
+      <c r="T57" t="n">
         <v>32.01</v>
       </c>
-      <c r="R57" t="n">
+      <c r="U57" t="n">
         <v>8.881784197001252e-16</v>
       </c>
-      <c r="S57" t="n">
+      <c r="V57" t="n">
         <v>0.00133668808168651</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="U57" t="n">
-        <v>0.01377153768226499</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0.001668341670143457</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0.001398941297492627</v>
-      </c>
       <c r="X57" t="n">
+        <v>0.009760812186758203</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.00167713794468419</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.001485189100566221</v>
+      </c>
+      <c r="AA57" t="n">
         <v>0.05357003933558507</v>
       </c>
-      <c r="Y57" t="n">
-        <v>0.4422006766078022</v>
+      <c r="AB57" t="n">
+        <v>0.3117734557549207</v>
       </c>
     </row>
     <row r="58">
@@ -5257,32 +5776,41 @@
         <v>0.007802512902614564</v>
       </c>
       <c r="Q58" t="n">
+        <v>4.490809690745411</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-0.08594931119250493</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.00333617496416037</v>
+      </c>
+      <c r="T58" t="n">
         <v>29.01</v>
       </c>
-      <c r="R58" t="n">
+      <c r="U58" t="n">
         <v>-4.215569548270928</v>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
         <v>0.6769278106501221</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U58" t="n">
+      <c r="X58" t="n">
         <v>0.05994842771092763</v>
       </c>
-      <c r="V58" t="n">
+      <c r="Y58" t="n">
         <v>0.00139444938472766</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Z58" t="n">
         <v>0.001271735640737716</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AA58" t="n">
         <v>0.03813887234646138</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AB58" t="n">
         <v>1.63961880357864</v>
       </c>
     </row>
@@ -5340,32 +5868,41 @@
         <v>-0.003760463504501162</v>
       </c>
       <c r="Q59" t="n">
+        <v>4.371031064913568</v>
+      </c>
+      <c r="R59" t="n">
+        <v>-0.08136000964781998</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.003055232595542551</v>
+      </c>
+      <c r="T59" t="n">
         <v>28.995</v>
       </c>
-      <c r="R59" t="n">
+      <c r="U59" t="n">
         <v>-0.004544063647491825</v>
       </c>
-      <c r="S59" t="n">
+      <c r="V59" t="n">
         <v>1.278015112506714</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U59" t="n">
+      <c r="X59" t="n">
         <v>0.01112946783281489</v>
       </c>
-      <c r="V59" t="n">
+      <c r="Y59" t="n">
         <v>0.001096555870749458</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Z59" t="n">
         <v>0.001055057789264696</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AA59" t="n">
         <v>0.03120888483068196</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AB59" t="n">
         <v>0.3167538372520005</v>
       </c>
     </row>
@@ -5423,32 +5960,41 @@
         <v>-0.00346125297583441</v>
       </c>
       <c r="Q60" t="n">
+        <v>4.283397728433791</v>
+      </c>
+      <c r="R60" t="n">
+        <v>-0.07812301627178186</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.002807371276816465</v>
+      </c>
+      <c r="T60" t="n">
         <v>28.995</v>
       </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
         <v>0.002360552544151721</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U60" t="n">
+      <c r="X60" t="n">
         <v>0.006250466457274683</v>
       </c>
-      <c r="V60" t="n">
+      <c r="Y60" t="n">
         <v>0.0009319321880903103</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Z60" t="n">
         <v>0.0009018756663659028</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AA60" t="n">
         <v>0.02699995193956568</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AB60" t="n">
         <v>0.1810885986158573</v>
       </c>
     </row>
@@ -5506,32 +6052,41 @@
         <v>-0.003027186320082213</v>
       </c>
       <c r="Q61" t="n">
+        <v>4.17183600426774</v>
+      </c>
+      <c r="R61" t="n">
+        <v>-0.07427022279296658</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.002447797253171801</v>
+      </c>
+      <c r="T61" t="n">
         <v>28.995</v>
       </c>
-      <c r="R61" t="n">
+      <c r="U61" t="n">
         <v>4.440892098500626e-16</v>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
         <v>1.679754956076457e-16</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="X61" t="n">
         <v>0.008453890833230813</v>
       </c>
-      <c r="V61" t="n">
+      <c r="Y61" t="n">
         <v>0.0007641324124643306</v>
       </c>
-      <c r="W61" t="n">
+      <c r="Z61" t="n">
         <v>0.0007135455166146369</v>
       </c>
-      <c r="X61" t="n">
+      <c r="AA61" t="n">
         <v>0.02261111891001251</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AB61" t="n">
         <v>0.2501555067739906</v>
       </c>
     </row>
@@ -5589,32 +6144,41 @@
         <v>-0.002361504646655055</v>
       </c>
       <c r="Q62" t="n">
+        <v>3.979098951820144</v>
+      </c>
+      <c r="R62" t="n">
+        <v>-0.06852164333929281</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.001896356974107972</v>
+      </c>
+      <c r="T62" t="n">
         <v>28.995</v>
       </c>
-      <c r="R62" t="n">
+      <c r="U62" t="n">
         <v>2.220446049250313e-16</v>
       </c>
-      <c r="S62" t="n">
+      <c r="V62" t="n">
         <v>-0.0004149356467907026</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U62" t="n">
+      <c r="X62" t="n">
         <v>0.01172784274873255</v>
       </c>
-      <c r="V62" t="n">
+      <c r="Y62" t="n">
         <v>0.0005394744902894036</v>
       </c>
-      <c r="W62" t="n">
+      <c r="Z62" t="n">
         <v>0.0004513513376708359</v>
       </c>
-      <c r="X62" t="n">
+      <c r="AA62" t="n">
         <v>0.01649790494310864</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="AB62" t="n">
         <v>0.3586542799317901</v>
       </c>
     </row>
@@ -5672,32 +6236,41 @@
         <v>-0.001230388993487751</v>
       </c>
       <c r="Q63" t="n">
+        <v>3.626293769239063</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-0.06048772095122956</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.0009593584711666027</v>
+      </c>
+      <c r="T63" t="n">
         <v>28.995</v>
       </c>
-      <c r="R63" t="n">
+      <c r="U63" t="n">
         <v>-0.007007575757578266</v>
       </c>
-      <c r="S63" t="n">
+      <c r="V63" t="n">
         <v>0.005856180856182273</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U63" t="n">
+      <c r="X63" t="n">
         <v>0.01538642531270043</v>
       </c>
-      <c r="V63" t="n">
+      <c r="Y63" t="n">
         <v>0.0002521738410450705</v>
       </c>
-      <c r="W63" t="n">
+      <c r="Z63" t="n">
         <v>0.0001154987590060771</v>
       </c>
-      <c r="X63" t="n">
+      <c r="AA63" t="n">
         <v>0.008130961425105476</v>
       </c>
-      <c r="Y63" t="n">
+      <c r="AB63" t="n">
         <v>0.4961118495453845</v>
       </c>
     </row>
@@ -5755,32 +6328,41 @@
         <v>-0.0007687188886404113</v>
       </c>
       <c r="Q64" t="n">
+        <v>3.528000277359463</v>
+      </c>
+      <c r="R64" t="n">
+        <v>-0.05914425896806597</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.0005769181823391187</v>
+      </c>
+      <c r="T64" t="n">
         <v>28.98</v>
       </c>
-      <c r="R64" t="n">
+      <c r="U64" t="n">
         <v>0.0061471861471869</v>
       </c>
-      <c r="S64" t="n">
+      <c r="V64" t="n">
         <v>0.005102658473445725</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U64" t="n">
+      <c r="X64" t="n">
         <v>0.01552148455655769</v>
       </c>
-      <c r="V64" t="n">
+      <c r="Y64" t="n">
         <v>0.0001989076379162201</v>
       </c>
-      <c r="W64" t="n">
+      <c r="Z64" t="n">
         <v>5.900606001244045e-05</v>
       </c>
-      <c r="X64" t="n">
+      <c r="AA64" t="n">
         <v>0.006506905588435094</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="AB64" t="n">
         <v>0.5077574479287422</v>
       </c>
     </row>
@@ -5838,32 +6420,41 @@
         <v>-0.0002878484120212748</v>
       </c>
       <c r="Q65" t="n">
+        <v>3.43986691748777</v>
+      </c>
+      <c r="R65" t="n">
+        <v>-0.058602474241916</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.0001785726060587051</v>
+      </c>
+      <c r="T65" t="n">
         <v>29.01</v>
       </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
         <v>0.009887640449438351</v>
       </c>
-      <c r="S65" t="n">
+      <c r="V65" t="n">
         <v>-0.002731475765183992</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U65" t="n">
+      <c r="X65" t="n">
         <v>0.01507844375563558</v>
       </c>
-      <c r="V65" t="n">
+      <c r="Y65" t="n">
         <v>0.0001682178882382971</v>
       </c>
-      <c r="W65" t="n">
+      <c r="Z65" t="n">
         <v>3.137821274756879e-05</v>
       </c>
-      <c r="X65" t="n">
+      <c r="AA65" t="n">
         <v>0.005577219668908662</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="AB65" t="n">
         <v>0.4999218214613053</v>
       </c>
     </row>
@@ -5921,32 +6512,41 @@
         <v>0.0001083999204683676</v>
       </c>
       <c r="Q66" t="n">
+        <v>3.354136177248058</v>
+      </c>
+      <c r="R66" t="n">
+        <v>-0.05860245436134193</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-0.000149673310524831</v>
+      </c>
+      <c r="T66" t="n">
         <v>29.01</v>
       </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
         <v>-0.001611721611721961</v>
       </c>
-      <c r="S66" t="n">
+      <c r="V66" t="n">
         <v>-0.005105980162160129</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U66" t="n">
+      <c r="X66" t="n">
         <v>0.01440878570365691</v>
       </c>
-      <c r="V66" t="n">
+      <c r="Y66" t="n">
         <v>0.0001557063292271108</v>
       </c>
-      <c r="W66" t="n">
+      <c r="Z66" t="n">
         <v>2.447839510156408e-05</v>
       </c>
-      <c r="X66" t="n">
+      <c r="AA66" t="n">
         <v>0.005232997774245813</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="AB66" t="n">
         <v>0.4842522708684667</v>
       </c>
     </row>
@@ -6004,32 +6604,41 @@
         <v>0.0008166001620623204</v>
       </c>
       <c r="Q67" t="n">
+        <v>3.175436403096402</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-0.05999552168575839</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-0.0007363353059610753</v>
+      </c>
+      <c r="T67" t="n">
         <v>28.995</v>
       </c>
-      <c r="R67" t="n">
+      <c r="U67" t="n">
         <v>5.494505494496593e-05</v>
       </c>
-      <c r="S67" t="n">
+      <c r="V67" t="n">
         <v>-0.0003398084690739731</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U67" t="n">
+      <c r="X67" t="n">
         <v>0.01280654003312175</v>
       </c>
-      <c r="V67" t="n">
+      <c r="Y67" t="n">
         <v>0.0001819834412702878</v>
       </c>
-      <c r="W67" t="n">
+      <c r="Z67" t="n">
         <v>6.420935313038018e-05</v>
       </c>
-      <c r="X67" t="n">
+      <c r="AA67" t="n">
         <v>0.006293342528835937</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="AB67" t="n">
         <v>0.4428751455358038</v>
       </c>
     </row>
@@ -6087,32 +6696,41 @@
         <v>0.001518467427489923</v>
       </c>
       <c r="Q68" t="n">
+        <v>2.992235033403133</v>
+      </c>
+      <c r="R68" t="n">
+        <v>-0.0630266400465459</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-0.00131775116306425</v>
+      </c>
+      <c r="T68" t="n">
         <v>29.01</v>
       </c>
-      <c r="R68" t="n">
+      <c r="U68" t="n">
         <v>-0.003602941176470864</v>
       </c>
-      <c r="S68" t="n">
+      <c r="V68" t="n">
         <v>-0.0009821604226976539</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U68" t="n">
+      <c r="X68" t="n">
         <v>0.01106992479933209</v>
       </c>
-      <c r="V68" t="n">
+      <c r="Y68" t="n">
         <v>0.0002676714073288779</v>
       </c>
-      <c r="W68" t="n">
+      <c r="Z68" t="n">
         <v>0.0001626495793439559</v>
       </c>
-      <c r="X68" t="n">
+      <c r="AA68" t="n">
         <v>0.009507961790421491</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="AB68" t="n">
         <v>0.3932150357978619</v>
       </c>
     </row>
@@ -6170,32 +6788,41 @@
         <v>0.002291792353591941</v>
       </c>
       <c r="Q69" t="n">
+        <v>2.819519212679411</v>
+      </c>
+      <c r="R69" t="n">
+        <v>-0.06726924374333371</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-0.00195836142781991</v>
+      </c>
+      <c r="T69" t="n">
         <v>28.98</v>
       </c>
-      <c r="R69" t="n">
+      <c r="U69" t="n">
         <v>-0.005659937888199629</v>
       </c>
-      <c r="S69" t="n">
+      <c r="V69" t="n">
         <v>0.0006535440263062372</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U69" t="n">
+      <c r="X69" t="n">
         <v>0.00941278097290961</v>
       </c>
-      <c r="V69" t="n">
+      <c r="Y69" t="n">
         <v>0.0003973422594022253</v>
       </c>
-      <c r="W69" t="n">
+      <c r="Z69" t="n">
         <v>0.0003025505762374235</v>
       </c>
-      <c r="X69" t="n">
+      <c r="AA69" t="n">
         <v>0.0144100013902495</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="AB69" t="n">
         <v>0.3413636070570498</v>
       </c>
     </row>
@@ -6253,32 +6880,41 @@
         <v>0.002879348659543106</v>
       </c>
       <c r="Q70" t="n">
+        <v>2.631055662577874</v>
+      </c>
+      <c r="R70" t="n">
+        <v>-0.07356115845571501</v>
+      </c>
+      <c r="S70" t="n">
+        <v>-0.002445083875279956</v>
+      </c>
+      <c r="T70" t="n">
         <v>28.98</v>
       </c>
-      <c r="R70" t="n">
+      <c r="U70" t="n">
         <v>1.110223024625157e-16</v>
       </c>
-      <c r="S70" t="n">
+      <c r="V70" t="n">
         <v>0.001567307134150147</v>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U70" t="n">
+      <c r="X70" t="n">
         <v>0.00758866542262381</v>
       </c>
-      <c r="V70" t="n">
+      <c r="Y70" t="n">
         <v>0.0005981774591723834</v>
       </c>
-      <c r="W70" t="n">
+      <c r="Z70" t="n">
         <v>0.0005138568214444482</v>
       </c>
-      <c r="X70" t="n">
+      <c r="AA70" t="n">
         <v>0.02205471791797375</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="AB70" t="n">
         <v>0.2797930157739653</v>
       </c>
     </row>
@@ -6336,32 +6972,41 @@
         <v>0.003700188554177305</v>
       </c>
       <c r="Q71" t="n">
+        <v>1.953444176187408</v>
+      </c>
+      <c r="R71" t="n">
+        <v>-0.09584171314190154</v>
+      </c>
+      <c r="S71" t="n">
+        <v>-0.003125054796266683</v>
+      </c>
+      <c r="T71" t="n">
         <v>28.98</v>
       </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
         <v>-0.001567307134150175</v>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U71" t="n">
+      <c r="X71" t="n">
         <v>0.002024581679390566</v>
       </c>
-      <c r="V71" t="n">
+      <c r="Y71" t="n">
         <v>0.001358713073094444</v>
       </c>
-      <c r="W71" t="n">
+      <c r="Z71" t="n">
         <v>0.001321548874487664</v>
       </c>
-      <c r="X71" t="n">
+      <c r="AA71" t="n">
         <v>0.05049555061696176</v>
       </c>
-      <c r="Y71" t="n">
+      <c r="AB71" t="n">
         <v>0.07524205713058127</v>
       </c>
     </row>
@@ -6419,32 +7064,41 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
+        <v>4.29126486985254</v>
+      </c>
+      <c r="R72" t="n">
+        <v>-0.1033792290370099</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.006539057442742545</v>
+      </c>
+      <c r="T72" t="n">
         <v>28.995</v>
       </c>
-      <c r="R72" t="n">
+      <c r="U72" t="n">
         <v>1.19760442260443</v>
       </c>
-      <c r="S72" t="n">
+      <c r="V72" t="n">
         <v>5.446590793890114</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U72" t="n">
+      <c r="X72" t="n">
         <v>0.04574532707586186</v>
       </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
       <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
         <v>1.03864456869061</v>
       </c>
     </row>
@@ -6502,32 +7156,41 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
+        <v>4.179892704249451</v>
+      </c>
+      <c r="R73" t="n">
+        <v>-0.09633007699173546</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.006116931835647616</v>
+      </c>
+      <c r="T73" t="n">
         <v>28.995</v>
       </c>
-      <c r="R73" t="n">
+      <c r="U73" t="n">
         <v>-0.004420821114372586</v>
       </c>
-      <c r="S73" t="n">
+      <c r="V73" t="n">
         <v>-0.6091158028459269</v>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U73" t="n">
+      <c r="X73" t="n">
         <v>0.02456396897979753</v>
       </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
       <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
         <v>0.5714869321461707</v>
       </c>
     </row>
@@ -6585,32 +7248,41 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
+        <v>4.045170168661021</v>
+      </c>
+      <c r="R74" t="n">
+        <v>-0.08773564742447726</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.005580906642648598</v>
+      </c>
+      <c r="T74" t="n">
         <v>28.98</v>
       </c>
-      <c r="R74" t="n">
+      <c r="U74" t="n">
         <v>0.002448783610757843</v>
       </c>
-      <c r="S74" t="n">
+      <c r="V74" t="n">
         <v>0.002091517733637483</v>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U74" t="n">
+      <c r="X74" t="n">
         <v>0.02077447913967906</v>
       </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0</v>
-      </c>
       <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
         <v>0.4951699747232352</v>
       </c>
     </row>
@@ -6668,32 +7340,41 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
+        <v>3.945283758584152</v>
+      </c>
+      <c r="R75" t="n">
+        <v>-0.08139788037707119</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.005086564136433325</v>
+      </c>
+      <c r="T75" t="n">
         <v>28.995</v>
       </c>
-      <c r="R75" t="n">
+      <c r="U75" t="n">
         <v>0.002448783610757843</v>
       </c>
-      <c r="S75" t="n">
+      <c r="V75" t="n">
         <v>-0.002754454158137631</v>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U75" t="n">
+      <c r="X75" t="n">
         <v>0.02068617890031077</v>
       </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
-      </c>
       <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
         <v>0.5026215848024155</v>
       </c>
     </row>
@@ -6751,32 +7432,41 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
+        <v>3.831377663495088</v>
+      </c>
+      <c r="R76" t="n">
+        <v>-0.07442712225276227</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.004411762671548086</v>
+      </c>
+      <c r="T76" t="n">
         <v>28.98</v>
       </c>
-      <c r="R76" t="n">
+      <c r="U76" t="n">
         <v>-0.00659824046920976</v>
       </c>
-      <c r="S76" t="n">
+      <c r="V76" t="n">
         <v>-0.002870535133593673</v>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U76" t="n">
+      <c r="X76" t="n">
         <v>0.02043986293642015</v>
       </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
       <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
         <v>0.5083124347415087</v>
       </c>
     </row>
@@ -6834,32 +7524,41 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
+        <v>3.648595637603464</v>
+      </c>
+      <c r="R77" t="n">
+        <v>-0.06431588583730083</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.003388074231126136</v>
+      </c>
+      <c r="T77" t="n">
         <v>28.98</v>
       </c>
-      <c r="R77" t="n">
+      <c r="U77" t="n">
         <v>0.001736770691995515</v>
       </c>
-      <c r="S77" t="n">
+      <c r="V77" t="n">
         <v>0.001217265424467607</v>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U77" t="n">
+      <c r="X77" t="n">
         <v>0.01962902201719036</v>
       </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
       <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
         <v>0.5081937528597683</v>
       </c>
     </row>
@@ -6917,32 +7616,41 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
+        <v>3.338917049261011</v>
+      </c>
+      <c r="R78" t="n">
+        <v>-0.05011772496703459</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.0016185694681621</v>
+      </c>
+      <c r="T78" t="n">
         <v>29.01</v>
       </c>
-      <c r="R78" t="n">
+      <c r="U78" t="n">
         <v>-0.01377580184185945</v>
       </c>
-      <c r="S78" t="n">
+      <c r="V78" t="n">
         <v>0.003935535610344511</v>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U78" t="n">
+      <c r="X78" t="n">
         <v>0.01718166418319534</v>
       </c>
-      <c r="V78" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
       <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
         <v>0.47855134637752</v>
       </c>
     </row>
@@ -7000,32 +7708,41 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
+        <v>3.262749874551532</v>
+      </c>
+      <c r="R79" t="n">
+        <v>-0.04798832749499038</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.0009323197603370286</v>
+      </c>
+      <c r="T79" t="n">
         <v>28.98</v>
       </c>
-      <c r="R79" t="n">
+      <c r="U79" t="n">
         <v>-0.004658682590775953</v>
       </c>
-      <c r="S79" t="n">
+      <c r="V79" t="n">
         <v>0.005930868482666279</v>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U79" t="n">
+      <c r="X79" t="n">
         <v>0.01630953105759465</v>
       </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
       <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
         <v>0.4621313762975864</v>
       </c>
     </row>
@@ -7083,32 +7800,41 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
+        <v>3.189332572827509</v>
+      </c>
+      <c r="R80" t="n">
+        <v>-0.04719784172966035</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.000160708791953186</v>
+      </c>
+      <c r="T80" t="n">
         <v>28.995</v>
       </c>
-      <c r="R80" t="n">
+      <c r="U80" t="n">
         <v>0.004705043664232633</v>
       </c>
-      <c r="S80" t="n">
+      <c r="V80" t="n">
         <v>0.0007241859839866335</v>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U80" t="n">
+      <c r="X80" t="n">
         <v>0.01529578606344143</v>
       </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
       <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
         <v>0.4401129170107577</v>
       </c>
     </row>
@@ -7166,32 +7892,41 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
+        <v>3.12034244550554</v>
+      </c>
+      <c r="R81" t="n">
+        <v>-0.04744687385215529</v>
+      </c>
+      <c r="S81" t="n">
+        <v>-0.000452126974844435</v>
+      </c>
+      <c r="T81" t="n">
         <v>28.995</v>
       </c>
-      <c r="R81" t="n">
+      <c r="U81" t="n">
         <v>-0.001611721611721961</v>
       </c>
-      <c r="S81" t="n">
+      <c r="V81" t="n">
         <v>-0.002724079619464575</v>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U81" t="n">
+      <c r="X81" t="n">
         <v>0.01423167421311976</v>
       </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
-      </c>
       <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
         <v>0.4148233066433576</v>
       </c>
     </row>
@@ -7249,32 +7984,41 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
+        <v>2.973859734392465</v>
+      </c>
+      <c r="R82" t="n">
+        <v>-0.05058953336990651</v>
+      </c>
+      <c r="S82" t="n">
+        <v>-0.001519770183040392</v>
+      </c>
+      <c r="T82" t="n">
         <v>28.98</v>
       </c>
-      <c r="R82" t="n">
+      <c r="U82" t="n">
         <v>5.494505494496593e-05</v>
       </c>
-      <c r="S82" t="n">
+      <c r="V82" t="n">
         <v>0.001646268147460716</v>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U82" t="n">
+      <c r="X82" t="n">
         <v>0.01177084175533188</v>
       </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
       <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
         <v>0.3505176057965108</v>
       </c>
     </row>
@@ -7332,32 +8076,41 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
+        <v>2.815271320868581</v>
+      </c>
+      <c r="R83" t="n">
+        <v>-0.05658408257420433</v>
+      </c>
+      <c r="S83" t="n">
+        <v>-0.002555149639045278</v>
+      </c>
+      <c r="T83" t="n">
         <v>28.995</v>
       </c>
-      <c r="R83" t="n">
+      <c r="U83" t="n">
         <v>0.008248043469444966</v>
       </c>
-      <c r="S83" t="n">
+      <c r="V83" t="n">
         <v>-0.008316959792975405</v>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U83" t="n">
+      <c r="X83" t="n">
         <v>0.009057043657529436</v>
       </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
       <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
         <v>0.2733429230022186</v>
       </c>
     </row>
@@ -7415,32 +8168,41 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
+        <v>2.726598804550801</v>
+      </c>
+      <c r="R84" t="n">
+        <v>-0.0608864521354604</v>
+      </c>
+      <c r="S84" t="n">
+        <v>-0.003047017038159183</v>
+      </c>
+      <c r="T84" t="n">
         <v>29.01</v>
       </c>
-      <c r="R84" t="n">
+      <c r="U84" t="n">
         <v>-0.01283716283716529</v>
       </c>
-      <c r="S84" t="n">
+      <c r="V84" t="n">
         <v>-0.02339688154851417</v>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U84" t="n">
+      <c r="X84" t="n">
         <v>0.007540598768276501</v>
       </c>
-      <c r="V84" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
       <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
         <v>0.2283843276209666</v>
       </c>
     </row>
@@ -7498,32 +8260,41 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
+        <v>2.660908107778384</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-0.06423868457390691</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-0.00333818760650087</v>
+      </c>
+      <c r="T85" t="n">
         <v>28.98</v>
       </c>
-      <c r="R85" t="n">
+      <c r="U85" t="n">
         <v>-0.04430569430570586</v>
       </c>
-      <c r="S85" t="n">
+      <c r="V85" t="n">
         <v>-0.03654317839156326</v>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U85" t="n">
+      <c r="X85" t="n">
         <v>0.006446102990600344</v>
       </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
       <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
         <v>0.1954476002213318</v>
       </c>
     </row>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB85"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,11 @@
           <t>rX</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -624,13 +629,13 @@
         <v>0.05443836246253775</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.382108602445239</v>
+        <v>5.184</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.187795120142614</v>
+        <v>-0.4880967704861525</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03918978104830084</v>
+        <v>-0.2112393043113611</v>
       </c>
       <c r="T2" t="n">
         <v>36.93</v>
@@ -660,6 +665,9 @@
       </c>
       <c r="AB2" t="n">
         <v>3.212068818003286</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-5.802791097457179</v>
       </c>
     </row>
     <row r="3">
@@ -716,13 +724,13 @@
         <v>0.02803753103562011</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.178095790866871</v>
+        <v>5.551</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1304671655500824</v>
+        <v>0.05160039960039975</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04385413982233808</v>
+        <v>0.1746218723130543</v>
       </c>
       <c r="T3" t="n">
         <v>27.99</v>
@@ -752,6 +760,9 @@
       </c>
       <c r="AB3" t="n">
         <v>1.124583943411706</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.249695268178288</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +819,13 @@
         <v>-0.007010515913380644</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.017798817704199</v>
+        <v>5.082</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.05567206474214381</v>
+        <v>-0.2296691555796904</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04111207151267104</v>
+        <v>-0.07248445480228022</v>
       </c>
       <c r="T4" t="n">
         <v>28.02</v>
@@ -844,6 +855,9 @@
       </c>
       <c r="AB4" t="n">
         <v>0.05896524415184423</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.415177593435335</v>
       </c>
     </row>
     <row r="5">
@@ -900,13 +914,13 @@
         <v>0.0089492289119854</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.991936403001823</v>
+        <v>4.694</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02718058382067734</v>
+        <v>-0.1571836048327968</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0344387439198068</v>
+        <v>0.146435644841408</v>
       </c>
       <c r="T5" t="n">
         <v>27.99</v>
@@ -936,6 +950,9 @@
       </c>
       <c r="AB5" t="n">
         <v>0.115222492751227</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.467936919385896</v>
       </c>
     </row>
     <row r="6">
@@ -992,13 +1009,13 @@
         <v>0.04451854124995235</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.120752463480209</v>
+        <v>4.429</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08716816995349497</v>
+        <v>0.3477012333657894</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01448825872320491</v>
+        <v>0.1118647240534484</v>
       </c>
       <c r="T6" t="n">
         <v>28.02</v>
@@ -1028,6 +1045,9 @@
       </c>
       <c r="AB6" t="n">
         <v>0.1239112748227083</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.588172588883364</v>
       </c>
     </row>
     <row r="7">
@@ -1084,13 +1104,13 @@
         <v>0.09969346862095835</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.334003110521341</v>
+        <v>6.02</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08594037729372817</v>
+        <v>0.2985641025641019</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.03093166043981172</v>
+        <v>-0.478043411215818</v>
       </c>
       <c r="T7" t="n">
         <v>27.99</v>
@@ -1120,6 +1140,9 @@
       </c>
       <c r="AB7" t="n">
         <v>-0.0966586741807568</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.00605570996961</v>
       </c>
     </row>
     <row r="8">
@@ -1176,13 +1199,13 @@
         <v>0.1396218551781902</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.410999804581532</v>
+        <v>6.041</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03632983611183471</v>
+        <v>-0.459413008989952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06796230141085968</v>
+        <v>-0.366661396245335</v>
       </c>
       <c r="T8" t="n">
         <v>27.99</v>
@@ -1212,6 +1235,9 @@
       </c>
       <c r="AB8" t="n">
         <v>-0.297227370619138</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.690989079221494</v>
       </c>
     </row>
     <row r="9">
@@ -1268,13 +1294,13 @@
         <v>0.1704121024990759</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.411512307924802</v>
+        <v>5.102</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.05315602091197569</v>
+        <v>-0.4825083249806434</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09701100421408849</v>
+        <v>0.4337329331166945</v>
       </c>
       <c r="T9" t="n">
         <v>27.99</v>
@@ -1304,6 +1330,9 @@
       </c>
       <c r="AB9" t="n">
         <v>-0.5602861066626278</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.171112393228372</v>
       </c>
     </row>
     <row r="10">
@@ -1360,13 +1389,13 @@
         <v>0.1885370639025594</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.310807757574504</v>
+        <v>5.041</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.155198221192089</v>
+        <v>0.3563014284289183</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1141107894689042</v>
+        <v>1.30173552221343</v>
       </c>
       <c r="T10" t="n">
         <v>27.99</v>
@@ -1396,6 +1425,9 @@
       </c>
       <c r="AB10" t="n">
         <v>-0.8621711121897764</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12.07049448446898</v>
       </c>
     </row>
     <row r="11">
@@ -1452,13 +1484,13 @@
         <v>0.03270764869073212</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.581432186854011</v>
+        <v>3.61</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.04980168904584292</v>
+        <v>0.05807799827585247</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01623739009660047</v>
+        <v>0.04585309101989664</v>
       </c>
       <c r="T11" t="n">
         <v>30</v>
@@ -1488,6 +1520,9 @@
       </c>
       <c r="AB11" t="n">
         <v>0.5267164103912014</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.5296706066929328</v>
       </c>
     </row>
     <row r="12">
@@ -1544,13 +1579,13 @@
         <v>-0.03311824047486412</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.519108708753577</v>
+        <v>3.882</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.01900331605574701</v>
+        <v>0.005328788642799065</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01893889925203274</v>
+        <v>-0.04017829336138937</v>
       </c>
       <c r="T12" t="n">
         <v>30.015</v>
@@ -1580,6 +1615,9 @@
       </c>
       <c r="AB12" t="n">
         <v>-0.4676556280473815</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.13832222171261</v>
       </c>
     </row>
     <row r="13">
@@ -1636,13 +1674,13 @@
         <v>0.03095467918531082</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.521409515630263</v>
+        <v>3.509</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02451419553391787</v>
+        <v>-0.1054087315502568</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02220594544328378</v>
+        <v>0.02514730115285493</v>
       </c>
       <c r="T13" t="n">
         <v>30</v>
@@ -1672,6 +1710,9 @@
       </c>
       <c r="AB13" t="n">
         <v>0.1466294976475842</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.191306641151922</v>
       </c>
     </row>
     <row r="14">
@@ -1728,13 +1769,13 @@
         <v>0.182774664945801</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.614709781014519</v>
+        <v>3.432</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0720375657570913</v>
+        <v>0.09127498538866197</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02527151967257393</v>
+        <v>0.06128258130735412</v>
       </c>
       <c r="T14" t="n">
         <v>30</v>
@@ -1764,6 +1805,9 @@
       </c>
       <c r="AB14" t="n">
         <v>0.589360073971491</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.466439627179489</v>
       </c>
     </row>
     <row r="15">
@@ -1820,13 +1864,13 @@
         <v>0.3299149962450657</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.801428699717416</v>
+        <v>3.851</v>
       </c>
       <c r="R15" t="n">
-        <v>0.123717550159157</v>
+        <v>0.1404949712643679</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02759689768479523</v>
+        <v>-0.04176749301902744</v>
       </c>
       <c r="T15" t="n">
         <v>30.015</v>
@@ -1856,6 +1900,9 @@
       </c>
       <c r="AB15" t="n">
         <v>0.2349656118969819</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.050758959383074</v>
       </c>
     </row>
     <row r="16">
@@ -1912,13 +1959,13 @@
         <v>0.3933788333966759</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.949365425797802</v>
+        <v>3.956</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1536638112415663</v>
+        <v>0.05638002873563153</v>
       </c>
       <c r="S16" t="n">
-        <v>0.028552341844722</v>
+        <v>-0.1159480242223528</v>
       </c>
       <c r="T16" t="n">
         <v>30</v>
@@ -1948,6 +1995,9 @@
       </c>
       <c r="AB16" t="n">
         <v>-0.1830436921785885</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.537696032057543</v>
       </c>
     </row>
     <row r="17">
@@ -2004,13 +2054,13 @@
         <v>0.008651385330049385</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.379979298695361</v>
+        <v>5.223</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.1315608109754156</v>
+        <v>0.1204419051471333</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02468276755472088</v>
+        <v>0.1014219077559285</v>
       </c>
       <c r="T17" t="n">
         <v>32.985</v>
@@ -2040,6 +2090,9 @@
       </c>
       <c r="AB17" t="n">
         <v>1.854368830795771</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.402530114214224</v>
       </c>
     </row>
     <row r="18">
@@ -2096,13 +2149,13 @@
         <v>-0.02156544142506893</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.250260856442693</v>
+        <v>5.29</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.09002716773481589</v>
+        <v>0.08244304875452446</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0518657041594046</v>
+        <v>-0.007424586209027598</v>
       </c>
       <c r="T18" t="n">
         <v>33</v>
@@ -2132,6 +2185,9 @@
       </c>
       <c r="AB18" t="n">
         <v>0.4349746584691095</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.6634139576301</v>
       </c>
     </row>
     <row r="19">
@@ -2188,13 +2244,13 @@
         <v>0.0002592121117928302</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.18832900702664</v>
+        <v>5.384</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.0304469026530354</v>
+        <v>0.09699014778325177</v>
       </c>
       <c r="S19" t="n">
-        <v>0.076460223068408</v>
+        <v>0.00233882684867398</v>
       </c>
       <c r="T19" t="n">
         <v>33</v>
@@ -2224,6 +2280,9 @@
       </c>
       <c r="AB19" t="n">
         <v>-0.1601039334494191</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.856841057740805</v>
       </c>
     </row>
     <row r="20">
@@ -2280,13 +2339,13 @@
         <v>0.02377783591582186</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.196355658258678</v>
+        <v>5.477</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0595392755223374</v>
+        <v>0.08513538461538417</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1023999495136532</v>
+        <v>-0.1250652767269084</v>
       </c>
       <c r="T20" t="n">
         <v>33</v>
@@ -2316,6 +2375,9 @@
       </c>
       <c r="AB20" t="n">
         <v>-0.5703054782838444</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.799973865714499</v>
       </c>
     </row>
     <row r="21">
@@ -2372,13 +2434,13 @@
         <v>0.04237510135172184</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.32131232830413</v>
+        <v>5.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1850414941355272</v>
+        <v>-0.1832171151129178</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1229116929752026</v>
+        <v>-0.3754960165602028</v>
       </c>
       <c r="T21" t="n">
         <v>32.97000000000001</v>
@@ -2408,6 +2470,9 @@
       </c>
       <c r="AB21" t="n">
         <v>-0.7446511251075507</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.185766247945754</v>
       </c>
     </row>
     <row r="22">
@@ -2464,13 +2529,13 @@
         <v>0.05281889853409094</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.534965269572661</v>
+        <v>5.211012191461332</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2987010143969968</v>
+        <v>-0.6069439608236866</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1344306170507666</v>
+        <v>-0.5838855208981423</v>
       </c>
       <c r="T22" t="n">
         <v>32.925</v>
@@ -2500,6 +2565,9 @@
       </c>
       <c r="AB22" t="n">
         <v>-0.763681692843301</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.711532299826835</v>
       </c>
     </row>
     <row r="23">
@@ -2556,13 +2624,13 @@
         <v>0.01711461552917037</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.893257105708582</v>
+        <v>4.88</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.1256881547718787</v>
+        <v>0.121785587294063</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1249147605818942</v>
+        <v>0.229667085832981</v>
       </c>
       <c r="T23" t="n">
         <v>36.945</v>
@@ -2592,6 +2660,9 @@
       </c>
       <c r="AB23" t="n">
         <v>1.884927092948308</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.2044999054645352</v>
       </c>
     </row>
     <row r="24">
@@ -2648,13 +2719,13 @@
         <v>-0.01098395222704836</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.840304718125667</v>
+        <v>4.596</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01700711652374709</v>
+        <v>0.2547547780362032</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1137135168665147</v>
+        <v>0.113795308497991</v>
       </c>
       <c r="T24" t="n">
         <v>36.96</v>
@@ -2684,6 +2755,9 @@
       </c>
       <c r="AB24" t="n">
         <v>0.04924267899408696</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.298504437124906</v>
       </c>
     </row>
     <row r="25">
@@ -2740,13 +2814,13 @@
         <v>-0.01312461346510742</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.912085832008034</v>
+        <v>5.278</v>
       </c>
       <c r="R25" t="n">
-        <v>0.113330229929598</v>
+        <v>0.3587375803623618</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08131192069080476</v>
+        <v>-0.112727149228043</v>
       </c>
       <c r="T25" t="n">
         <v>36.98999999999999</v>
@@ -2776,6 +2850,9 @@
       </c>
       <c r="AB25" t="n">
         <v>-0.797861052096557</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.80538107476989</v>
       </c>
     </row>
     <row r="26">
@@ -2832,13 +2909,13 @@
         <v>-0.01527016551214571</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.065837343203529</v>
+        <v>5.278</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1756773098781128</v>
+        <v>0.01811846689895535</v>
       </c>
       <c r="S26" t="n">
-        <v>0.04460178470623562</v>
+        <v>-0.1835944771732361</v>
       </c>
       <c r="T26" t="n">
         <v>36.93</v>
@@ -2868,6 +2945,9 @@
       </c>
       <c r="AB26" t="n">
         <v>-1.11697088199055</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>13.88204385935657</v>
       </c>
     </row>
     <row r="27">
@@ -2924,13 +3004,13 @@
         <v>-0.01693171964649547</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.274471711623132</v>
+        <v>5.317</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2029449958150473</v>
+        <v>-0.001536072623029572</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01617279446015786</v>
+        <v>-0.04882468907366223</v>
       </c>
       <c r="T27" t="n">
         <v>36.96</v>
@@ -2960,6 +3040,9 @@
       </c>
       <c r="AB27" t="n">
         <v>-0.8705332084222246</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>15.28262305416456</v>
       </c>
     </row>
     <row r="28">
@@ -3016,13 +3099,13 @@
         <v>-0.01787689785680881</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.453394436872836</v>
+        <v>5.288</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2099536009150373</v>
+        <v>-0.06538700430004596</v>
       </c>
       <c r="S28" t="n">
-        <v>9.096167422062429e-07</v>
+        <v>-0.09852361479637552</v>
       </c>
       <c r="T28" t="n">
         <v>36.975</v>
@@ -3052,6 +3135,9 @@
       </c>
       <c r="AB28" t="n">
         <v>-0.4395382734757554</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>15.58170267730281</v>
       </c>
     </row>
     <row r="29">
@@ -3108,13 +3194,13 @@
         <v>0.01325311210845598</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.4436849666609</v>
+        <v>4.179</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.08104735890804182</v>
+        <v>-0.0243722943722946</v>
       </c>
       <c r="S29" t="n">
-        <v>0.004153435985263555</v>
+        <v>0.1120958962498602</v>
       </c>
       <c r="T29" t="n">
         <v>29.01</v>
@@ -3144,6 +3230,9 @@
       </c>
       <c r="AB29" t="n">
         <v>0.7142044802905348</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.330188487440613</v>
       </c>
     </row>
     <row r="30">
@@ -3200,13 +3289,13 @@
         <v>0.003937378394383906</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.36089504837672</v>
+        <v>4.18</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.07688758882839108</v>
+        <v>-0.006328035443194491</v>
       </c>
       <c r="S30" t="n">
-        <v>0.003727691778091291</v>
+        <v>-0.01289331915412382</v>
       </c>
       <c r="T30" t="n">
         <v>28.995</v>
@@ -3236,6 +3325,9 @@
       </c>
       <c r="AB30" t="n">
         <v>-0.1398969209040258</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.611344073523441</v>
       </c>
     </row>
     <row r="31">
@@ -3292,13 +3384,13 @@
         <v>0.002447857918222877</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.294434161386915</v>
+        <v>4.169</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.07376868045082707</v>
+        <v>-0.04006899180484025</v>
       </c>
       <c r="S31" t="n">
-        <v>0.003325214549208928</v>
+        <v>-0.02013419468071367</v>
       </c>
       <c r="T31" t="n">
         <v>29.01</v>
@@ -3328,6 +3420,9 @@
       </c>
       <c r="AB31" t="n">
         <v>0.2430785711148564</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.859946810771716</v>
       </c>
     </row>
     <row r="32">
@@ -3384,13 +3479,13 @@
         <v>0.002192943138090632</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.228211276665901</v>
+        <v>4.106</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.07091616962933611</v>
+        <v>-0.0413426573426563</v>
       </c>
       <c r="S32" t="n">
-        <v>0.002907514964359856</v>
+        <v>0.006681932355861783</v>
       </c>
       <c r="T32" t="n">
         <v>28.98</v>
@@ -3420,6 +3515,9 @@
       </c>
       <c r="AB32" t="n">
         <v>0.3784772902973303</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.04908911365771</v>
       </c>
     </row>
     <row r="33">
@@ -3476,13 +3574,13 @@
         <v>0.001858787740399326</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.14182795782078</v>
+        <v>4.101</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.06763004016716101</v>
+        <v>-0.01923219814241506</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00235997287669356</v>
+        <v>0.005004321979409698</v>
       </c>
       <c r="T33" t="n">
         <v>29.01</v>
@@ -3512,6 +3610,9 @@
       </c>
       <c r="AB33" t="n">
         <v>0.4272160143279087</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.158583948368213</v>
       </c>
     </row>
     <row r="34">
@@ -3568,13 +3669,13 @@
         <v>0.001406724296956905</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.037708494123475</v>
+        <v>4.04</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.06443277189122842</v>
+        <v>-0.03674724602203172</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001619228410825142</v>
+        <v>-0.008567712689067595</v>
       </c>
       <c r="T34" t="n">
         <v>28.98</v>
@@ -3604,6 +3705,9 @@
       </c>
       <c r="AB34" t="n">
         <v>0.4798105591741548</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.1853250864187432</v>
       </c>
     </row>
     <row r="35">
@@ -3660,13 +3764,13 @@
         <v>0.000880447129478692</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.912195091961094</v>
+        <v>3.971</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.06220509129191787</v>
+        <v>-0.04758097165991881</v>
       </c>
       <c r="S35" t="n">
-        <v>0.000756878435445342</v>
+        <v>-0.003986266036997179</v>
       </c>
       <c r="T35" t="n">
         <v>29.01</v>
@@ -3696,6 +3800,9 @@
       </c>
       <c r="AB35" t="n">
         <v>0.5197472299269156</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.7233749756991107</v>
       </c>
     </row>
     <row r="36">
@@ -3752,13 +3859,13 @@
         <v>-0.0001080411410060017</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.647818699384286</v>
+        <v>3.642</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.0622767600189591</v>
+        <v>-0.05142307692307679</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.0008628438105337151</v>
+        <v>0.001965044534412978</v>
       </c>
       <c r="T36" t="n">
         <v>29.01</v>
@@ -3788,6 +3895,9 @@
       </c>
       <c r="AB36" t="n">
         <v>0.5187938176432531</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-1.777320557315394</v>
       </c>
     </row>
     <row r="37">
@@ -3844,13 +3954,13 @@
         <v>-0.0005551800082818237</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.543212033153671</v>
+        <v>3.572</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.06425733616056928</v>
+        <v>-0.04631999999999981</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.001595518938801424</v>
+        <v>-0.0002364923076923538</v>
       </c>
       <c r="T37" t="n">
         <v>29.01</v>
@@ -3880,6 +3990,9 @@
       </c>
       <c r="AB37" t="n">
         <v>0.4798326520311891</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-1.827902391620322</v>
       </c>
     </row>
     <row r="38">
@@ -3936,13 +4049,13 @@
         <v>-0.001262511799616995</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.376968681168996</v>
+        <v>3.44</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.06977303320945527</v>
+        <v>-0.05928000000000022</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.002754542340416524</v>
+        <v>-0.003660195348837152</v>
       </c>
       <c r="T38" t="n">
         <v>28.995</v>
@@ -3972,6 +4085,9 @@
       </c>
       <c r="AB38" t="n">
         <v>0.3747967623575328</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>-1.49888559811747</v>
       </c>
     </row>
     <row r="39">
@@ -4028,13 +4144,13 @@
         <v>-0.001716623534717529</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.257040634247031</v>
+        <v>3.334</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.0749731187999963</v>
+        <v>-0.06368720930232546</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.003498643106672418</v>
+        <v>-0.005705195358700371</v>
       </c>
       <c r="T39" t="n">
         <v>28.98</v>
@@ -4064,6 +4180,9 @@
       </c>
       <c r="AB39" t="n">
         <v>0.2977087888821338</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-1.200014726026039</v>
       </c>
     </row>
     <row r="40">
@@ -4120,13 +4239,13 @@
         <v>-0.002463198348949519</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.027245369937801</v>
+        <v>3.151</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.08686927210603346</v>
+        <v>-0.09513423124589948</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.00472196954463445</v>
+        <v>-0.01059677734848656</v>
       </c>
       <c r="T40" t="n">
         <v>29.01</v>
@@ -4156,6 +4275,9 @@
       </c>
       <c r="AB40" t="n">
         <v>0.189063643585355</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>-0.8100541190990447</v>
       </c>
     </row>
     <row r="41">
@@ -4212,13 +4334,13 @@
         <v>-0.003189110866347219</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.752294038039425</v>
+        <v>2.778</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.102437715694196</v>
+        <v>-0.1250981909152303</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.005911439048897982</v>
+        <v>-0.01115875793578195</v>
       </c>
       <c r="T41" t="n">
         <v>29.01</v>
@@ -4248,6 +4370,9 @@
       </c>
       <c r="AB41" t="n">
         <v>0.1160162919992433</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>-0.6259893618765752</v>
       </c>
     </row>
     <row r="42">
@@ -4304,13 +4429,13 @@
         <v>-0.004075977575900037</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.414263131103091</v>
+        <v>2.405</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.1222637205931832</v>
+        <v>-0.1619067920031776</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.007364645709586715</v>
+        <v>-0.009896672088702197</v>
       </c>
       <c r="T42" t="n">
         <v>29.01</v>
@@ -4340,6 +4465,9 @@
       </c>
       <c r="AB42" t="n">
         <v>0.08201579757485161</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-0.6633517402212648</v>
       </c>
     </row>
     <row r="43">
@@ -4396,13 +4524,13 @@
         <v>-0.004634695647620763</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.086299653662603</v>
+        <v>1.92</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.1423826153722847</v>
+        <v>-0.1820371434474639</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.008280152870387792</v>
+        <v>-0.003548965325650622</v>
       </c>
       <c r="T43" t="n">
         <v>28.995</v>
@@ -4432,6 +4560,9 @@
       </c>
       <c r="AB43" t="n">
         <v>0.1099057100818981</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>-0.9194498805502402</v>
       </c>
     </row>
     <row r="44">
@@ -4488,13 +4619,13 @@
         <v>-0.005461783123241583</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8116881888459335</v>
+        <v>0.848</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.2076251095201643</v>
+        <v>-0.1123335659346869</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.009635406163354884</v>
+        <v>0.02268953580970839</v>
       </c>
       <c r="T44" t="n">
         <v>28.98</v>
@@ -4524,6 +4655,9 @@
       </c>
       <c r="AB44" t="n">
         <v>0.2985811083836037</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>-1.998857655475034</v>
       </c>
     </row>
     <row r="45">
@@ -4580,13 +4714,13 @@
         <v>0.01087678132715291</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.751634109924598</v>
+        <v>3.504</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.1081815037588462</v>
+        <v>0.004369139904023767</v>
       </c>
       <c r="S45" t="n">
-        <v>0.007504281528254799</v>
+        <v>0.01440927302218155</v>
       </c>
       <c r="T45" t="n">
         <v>31.995</v>
@@ -4616,6 +4750,9 @@
       </c>
       <c r="AB45" t="n">
         <v>0.557886275373886</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>-1.036977167359194</v>
       </c>
     </row>
     <row r="46">
@@ -4672,13 +4809,13 @@
         <v>-0.00710389630350909</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.604326670005563</v>
+        <v>3.434</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.09771938685462644</v>
+        <v>-0.06080690627202245</v>
       </c>
       <c r="S46" t="n">
-        <v>0.007021889859726835</v>
+        <v>-0.02470380297996579</v>
       </c>
       <c r="T46" t="n">
         <v>32.01</v>
@@ -4708,6 +4845,9 @@
       </c>
       <c r="AB46" t="n">
         <v>0.3103350383602442</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.092856710913152</v>
       </c>
     </row>
     <row r="47">
@@ -4764,13 +4904,13 @@
         <v>-0.00637303148429085</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.465680010216048</v>
+        <v>3.324</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.08762178809163856</v>
+        <v>-0.06526190476190463</v>
       </c>
       <c r="S47" t="n">
-        <v>0.006377596591206413</v>
+        <v>0.001595388495633288</v>
       </c>
       <c r="T47" t="n">
         <v>32.01</v>
@@ -4800,6 +4940,9 @@
       </c>
       <c r="AB47" t="n">
         <v>0.2377085833703645</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.256852204810589</v>
       </c>
     </row>
     <row r="48">
@@ -4856,13 +4999,13 @@
         <v>-0.005470297797812553</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.303261283191983</v>
+        <v>3.215</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.07581095735576482</v>
+        <v>-0.04989676113360325</v>
       </c>
       <c r="S48" t="n">
-        <v>0.005581792466871252</v>
+        <v>0.007705590900327696</v>
       </c>
       <c r="T48" t="n">
         <v>31.98</v>
@@ -4892,6 +5035,9 @@
       </c>
       <c r="AB48" t="n">
         <v>0.2407625145597302</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.5724246734257523</v>
       </c>
     </row>
     <row r="49">
@@ -4948,13 +5094,13 @@
         <v>-0.003799960777227666</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.025432170228625</v>
+        <v>3.042</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.05466164945932772</v>
+        <v>-0.01628974358974355</v>
       </c>
       <c r="S49" t="n">
-        <v>0.004109308267022663</v>
+        <v>0.002903851551956846</v>
       </c>
       <c r="T49" t="n">
         <v>31.995</v>
@@ -4984,6 +5130,9 @@
       </c>
       <c r="AB49" t="n">
         <v>0.3051722636592766</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>-0.9508965773725447</v>
       </c>
     </row>
     <row r="50">
@@ -5040,13 +5189,13 @@
         <v>-0.003042496589870878</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.940388883453159</v>
+        <v>3.03</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.04830722622425132</v>
+        <v>-0.01455999999999991</v>
       </c>
       <c r="S50" t="n">
-        <v>0.003441566347823866</v>
+        <v>-0.005828492307692312</v>
       </c>
       <c r="T50" t="n">
         <v>31.98</v>
@@ -5076,6 +5225,9 @@
       </c>
       <c r="AB50" t="n">
         <v>0.3150057454595456</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>-1.173932627829475</v>
       </c>
     </row>
     <row r="51">
@@ -5132,13 +5284,13 @@
         <v>-0.001847930289874596</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.829816114796388</v>
+        <v>2.966</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.04109488882927403</v>
+        <v>-0.05488000000000004</v>
       </c>
       <c r="S51" t="n">
-        <v>0.002388497427756134</v>
+        <v>-0.009211589800174978</v>
       </c>
       <c r="T51" t="n">
         <v>31.98</v>
@@ -5168,6 +5320,9 @@
       </c>
       <c r="AB51" t="n">
         <v>0.3042101058979073</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-1.022414594764808</v>
       </c>
     </row>
     <row r="52">
@@ -5224,13 +5379,13 @@
         <v>-0.001075146602099324</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.764807098562525</v>
+        <v>2.842</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.03766565703883024</v>
+        <v>-0.06254774944493047</v>
       </c>
       <c r="S52" t="n">
-        <v>0.001707250615809435</v>
+        <v>-0.0001214833357782589</v>
       </c>
       <c r="T52" t="n">
         <v>32.01</v>
@@ -5260,6 +5415,9 @@
       </c>
       <c r="AB52" t="n">
         <v>0.2903724799169134</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>-0.8086885580720576</v>
       </c>
     </row>
     <row r="53">
@@ -5316,13 +5474,13 @@
         <v>0.0001606346812521692</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.666198413653078</v>
+        <v>2.723</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.03454200862781115</v>
+        <v>-0.04206596642780003</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0006178486617255188</v>
+        <v>0.00370098193486991</v>
       </c>
       <c r="T53" t="n">
         <v>31.995</v>
@@ -5352,6 +5510,9 @@
       </c>
       <c r="AB53" t="n">
         <v>0.2704304451900449</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>-0.5455376838656428</v>
       </c>
     </row>
     <row r="54">
@@ -5408,13 +5569,13 @@
         <v>0.001434166412932715</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.563807363985861</v>
+        <v>2.597</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.03434345135035966</v>
+        <v>-0.04300293546493239</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.0005048321684275239</v>
+        <v>-0.0004882235739605677</v>
       </c>
       <c r="T54" t="n">
         <v>31.98</v>
@@ -5444,6 +5605,9 @@
       </c>
       <c r="AB54" t="n">
         <v>0.2577431435737859</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>-0.462673759667947</v>
       </c>
     </row>
     <row r="55">
@@ -5500,13 +5664,13 @@
         <v>0.002930754982840081</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.458497161231485</v>
+        <v>2.463</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.03753971711341153</v>
+        <v>-0.0450017653667148</v>
       </c>
       <c r="S55" t="n">
-        <v>-0.001824148567276949</v>
+        <v>-0.001241633240984915</v>
       </c>
       <c r="T55" t="n">
         <v>32.01</v>
@@ -5536,6 +5700,9 @@
       </c>
       <c r="AB55" t="n">
         <v>0.2557588708921351</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>-0.5925120549491631</v>
       </c>
     </row>
     <row r="56">
@@ -5592,13 +5759,13 @@
         <v>0.00391744027113252</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.356099883078157</v>
+        <v>2.346</v>
       </c>
       <c r="R56" t="n">
-        <v>-0.04393991643780183</v>
+        <v>-0.04948921998782908</v>
       </c>
       <c r="S56" t="n">
-        <v>-0.002693960155794071</v>
+        <v>-0.002121073335170386</v>
       </c>
       <c r="T56" t="n">
         <v>32.01</v>
@@ -5628,6 +5795,9 @@
       </c>
       <c r="AB56" t="n">
         <v>0.2659772851655287</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>-0.9270946213544438</v>
       </c>
     </row>
     <row r="57">
@@ -5684,13 +5854,13 @@
         <v>0.005362219758256564</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.925963527392448</v>
+        <v>1.876</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.06925386137422668</v>
+        <v>-0.0741949905384866</v>
       </c>
       <c r="S57" t="n">
-        <v>-0.003967604301159836</v>
+        <v>-0.004380445230792118</v>
       </c>
       <c r="T57" t="n">
         <v>32.01</v>
@@ -5720,6 +5890,9 @@
       </c>
       <c r="AB57" t="n">
         <v>0.3117734557549207</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>-2.22648472982898</v>
       </c>
     </row>
     <row r="58">
@@ -5776,13 +5949,13 @@
         <v>0.007802512902614564</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.490809690745411</v>
+        <v>4.23</v>
       </c>
       <c r="R58" t="n">
-        <v>-0.08594931119250493</v>
+        <v>-0.04709440936393117</v>
       </c>
       <c r="S58" t="n">
-        <v>0.00333617496416037</v>
+        <v>0.112937955611399</v>
       </c>
       <c r="T58" t="n">
         <v>29.01</v>
@@ -5812,6 +5985,9 @@
       </c>
       <c r="AB58" t="n">
         <v>1.63961880357864</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-1.18934854841909</v>
       </c>
     </row>
     <row r="59">
@@ -5868,13 +6044,13 @@
         <v>-0.003760463504501162</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.371031064913568</v>
+        <v>4.278</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.08136000964781998</v>
+        <v>0.02019889840881239</v>
       </c>
       <c r="S59" t="n">
-        <v>0.003055232595542551</v>
+        <v>-0.01216435835344395</v>
       </c>
       <c r="T59" t="n">
         <v>28.995</v>
@@ -5904,6 +6080,9 @@
       </c>
       <c r="AB59" t="n">
         <v>0.3167538372520005</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.839222131285208</v>
       </c>
     </row>
     <row r="60">
@@ -5960,13 +6139,13 @@
         <v>-0.00346125297583441</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.283397728433791</v>
+        <v>4.289</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.07812301627178186</v>
+        <v>-0.04308441558441545</v>
       </c>
       <c r="S60" t="n">
-        <v>0.002807371276816465</v>
+        <v>-0.04475767231777314</v>
       </c>
       <c r="T60" t="n">
         <v>28.995</v>
@@ -5996,6 +6175,9 @@
       </c>
       <c r="AB60" t="n">
         <v>0.1810885986158573</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.618074207300888</v>
       </c>
     </row>
     <row r="61">
@@ -6052,13 +6234,13 @@
         <v>-0.003027186320082213</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.17183600426774</v>
+        <v>4.122</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.07427022279296658</v>
+        <v>-0.08375144708394533</v>
       </c>
       <c r="S61" t="n">
-        <v>0.002447797253171801</v>
+        <v>-0.01306044838440818</v>
       </c>
       <c r="T61" t="n">
         <v>28.995</v>
@@ -6088,6 +6270,9 @@
       </c>
       <c r="AB61" t="n">
         <v>0.2501555067739906</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.465281615898401</v>
       </c>
     </row>
     <row r="62">
@@ -6144,13 +6329,13 @@
         <v>-0.002361504646655055</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.979098951820144</v>
+        <v>4.046</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.06852164333929281</v>
+        <v>-0.04542750894571571</v>
       </c>
       <c r="S62" t="n">
-        <v>0.001896356974107972</v>
+        <v>0.01053506813459414</v>
       </c>
       <c r="T62" t="n">
         <v>28.995</v>
@@ -6180,6 +6365,9 @@
       </c>
       <c r="AB62" t="n">
         <v>0.3586542799317901</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>-0.1437343420758286</v>
       </c>
     </row>
     <row r="63">
@@ -6236,13 +6424,13 @@
         <v>-0.001230388993487751</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.626293769239063</v>
+        <v>3.596</v>
       </c>
       <c r="R63" t="n">
-        <v>-0.06048772095122956</v>
+        <v>-0.02745734370734354</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0009593584711666027</v>
+        <v>-0.008569105796206915</v>
       </c>
       <c r="T63" t="n">
         <v>28.995</v>
@@ -6272,6 +6460,9 @@
       </c>
       <c r="AB63" t="n">
         <v>0.4961118495453845</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>-1.845336128953297</v>
       </c>
     </row>
     <row r="64">
@@ -6328,13 +6519,13 @@
         <v>-0.0007687188886404113</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.528000277359463</v>
+        <v>3.577</v>
       </c>
       <c r="R64" t="n">
-        <v>-0.05914425896806597</v>
+        <v>-0.04738816738816731</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005769181823391187</v>
+        <v>-0.01493323787331291</v>
       </c>
       <c r="T64" t="n">
         <v>28.98</v>
@@ -6364,6 +6555,9 @@
       </c>
       <c r="AB64" t="n">
         <v>0.5077574479287422</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-1.9059684657569</v>
       </c>
     </row>
     <row r="65">
@@ -6420,13 +6614,13 @@
         <v>-0.0002878484120212748</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.43986691748777</v>
+        <v>3.457</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.058602474241916</v>
+        <v>-0.07367977528089908</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0001785726060587051</v>
+        <v>-0.005803414230380478</v>
       </c>
       <c r="T65" t="n">
         <v>29.01</v>
@@ -6456,6 +6650,9 @@
       </c>
       <c r="AB65" t="n">
         <v>0.4999218214613053</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>-1.708820698722495</v>
       </c>
     </row>
     <row r="66">
@@ -6512,13 +6709,13 @@
         <v>0.0001083999204683676</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.354136177248058</v>
+        <v>3.358</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.05860245436134193</v>
+        <v>-0.06537789987789966</v>
       </c>
       <c r="S66" t="n">
-        <v>-0.000149673310524831</v>
+        <v>0.003710269929774715</v>
       </c>
       <c r="T66" t="n">
         <v>29.01</v>
@@ -6548,6 +6745,9 @@
       </c>
       <c r="AB66" t="n">
         <v>0.4842522708684667</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>-1.457232128454974</v>
       </c>
     </row>
     <row r="67">
@@ -6604,13 +6804,13 @@
         <v>0.0008166001620623204</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.175436403096402</v>
+        <v>3.173</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.05999552168575839</v>
+        <v>-0.06635733511424119</v>
       </c>
       <c r="S67" t="n">
-        <v>-0.0007363353059610753</v>
+        <v>0.0006501891024152592</v>
       </c>
       <c r="T67" t="n">
         <v>28.995</v>
@@ -6640,6 +6840,9 @@
       </c>
       <c r="AB67" t="n">
         <v>0.4428751455358038</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-1.040928247386846</v>
       </c>
     </row>
     <row r="68">
@@ -6696,13 +6899,13 @@
         <v>0.001518467427489923</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.992235033403133</v>
+        <v>2.958</v>
       </c>
       <c r="R68" t="n">
-        <v>-0.0630266400465459</v>
+        <v>-0.06151960784313726</v>
       </c>
       <c r="S68" t="n">
-        <v>-0.00131775116306425</v>
+        <v>0.003819154909326017</v>
       </c>
       <c r="T68" t="n">
         <v>29.01</v>
@@ -6732,6 +6935,9 @@
       </c>
       <c r="AB68" t="n">
         <v>0.3932150357978619</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>-0.7891848947269442</v>
       </c>
     </row>
     <row r="69">
@@ -6788,13 +6994,13 @@
         <v>0.002291792353591941</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.819519212679411</v>
+        <v>2.818</v>
       </c>
       <c r="R69" t="n">
-        <v>-0.06726924374333371</v>
+        <v>-0.04610478490913283</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.00195836142781991</v>
+        <v>0.001334471343549186</v>
       </c>
       <c r="T69" t="n">
         <v>28.98</v>
@@ -6824,6 +7030,9 @@
       </c>
       <c r="AB69" t="n">
         <v>0.3413636070570498</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-0.7072462025365256</v>
       </c>
     </row>
     <row r="70">
@@ -6880,13 +7089,13 @@
         <v>0.002879348659543106</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.631055662577874</v>
+        <v>2.711</v>
       </c>
       <c r="R70" t="n">
-        <v>-0.07356115845571501</v>
+        <v>-0.05465620331956053</v>
       </c>
       <c r="S70" t="n">
-        <v>-0.002445083875279956</v>
+        <v>-0.005176699384183049</v>
       </c>
       <c r="T70" t="n">
         <v>28.98</v>
@@ -6916,6 +7125,9 @@
       </c>
       <c r="AB70" t="n">
         <v>0.2797930157739653</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-0.8011639035919315</v>
       </c>
     </row>
     <row r="71">
@@ -6972,13 +7184,13 @@
         <v>0.003700188554177305</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.953444176187408</v>
+        <v>1.917564923015524</v>
       </c>
       <c r="R71" t="n">
-        <v>-0.09584171314190154</v>
+        <v>-0.1437025659265583</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.003125054796266683</v>
+        <v>-0.0170848912675664</v>
       </c>
       <c r="T71" t="n">
         <v>28.98</v>
@@ -7008,6 +7220,9 @@
       </c>
       <c r="AB71" t="n">
         <v>0.07524205713058127</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-1.371002725428623</v>
       </c>
     </row>
     <row r="72">
@@ -7064,13 +7279,13 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.29126486985254</v>
+        <v>4.079</v>
       </c>
       <c r="R72" t="n">
-        <v>-0.1033792290370099</v>
+        <v>-0.08287120906523882</v>
       </c>
       <c r="S72" t="n">
-        <v>0.006539057442742545</v>
+        <v>-0.02162104983269235</v>
       </c>
       <c r="T72" t="n">
         <v>28.995</v>
@@ -7100,6 +7315,9 @@
       </c>
       <c r="AB72" t="n">
         <v>1.03864456869061</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-2.886203344510287</v>
       </c>
     </row>
     <row r="73">
@@ -7156,13 +7374,13 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.179892704249451</v>
+        <v>4.038</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.09633007699173546</v>
+        <v>-0.05267536219197266</v>
       </c>
       <c r="S73" t="n">
-        <v>0.006116931835647616</v>
+        <v>0.01842907930880282</v>
       </c>
       <c r="T73" t="n">
         <v>28.995</v>
@@ -7192,6 +7410,9 @@
       </c>
       <c r="AB73" t="n">
         <v>0.5714869321461707</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-1.457258038784022</v>
       </c>
     </row>
     <row r="74">
@@ -7248,13 +7469,13 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.045170168661021</v>
+        <v>3.93</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.08773564742447726</v>
+        <v>-0.04223588529461475</v>
       </c>
       <c r="S74" t="n">
-        <v>0.005580906642648598</v>
+        <v>0.006595986242658187</v>
       </c>
       <c r="T74" t="n">
         <v>28.98</v>
@@ -7284,6 +7505,9 @@
       </c>
       <c r="AB74" t="n">
         <v>0.4951699747232352</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-1.265738417756439</v>
       </c>
     </row>
     <row r="75">
@@ -7340,13 +7564,13 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.945283758584152</v>
+        <v>3.91</v>
       </c>
       <c r="R75" t="n">
-        <v>-0.08139788037707119</v>
+        <v>-0.03492885270456325</v>
       </c>
       <c r="S75" t="n">
-        <v>0.005086564136433325</v>
+        <v>-0.00145165825128493</v>
       </c>
       <c r="T75" t="n">
         <v>28.995</v>
@@ -7376,6 +7600,9 @@
       </c>
       <c r="AB75" t="n">
         <v>0.5026215848024155</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.325871585602914</v>
       </c>
     </row>
     <row r="76">
@@ -7432,13 +7659,13 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.831377663495088</v>
+        <v>3.826</v>
       </c>
       <c r="R76" t="n">
-        <v>-0.07442712225276227</v>
+        <v>-0.05092192082111441</v>
       </c>
       <c r="S76" t="n">
-        <v>0.004411762671548086</v>
+        <v>-0.006108362231804951</v>
       </c>
       <c r="T76" t="n">
         <v>28.98</v>
@@ -7468,6 +7695,9 @@
       </c>
       <c r="AB76" t="n">
         <v>0.5083124347415087</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>-1.393291090628012</v>
       </c>
     </row>
     <row r="77">
@@ -7524,13 +7754,13 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.648595637603464</v>
+        <v>3.721</v>
       </c>
       <c r="R77" t="n">
-        <v>-0.06431588583730083</v>
+        <v>-0.04395754183627318</v>
       </c>
       <c r="S77" t="n">
-        <v>0.003388074231126136</v>
+        <v>0.0009205293628549282</v>
       </c>
       <c r="T77" t="n">
         <v>28.98</v>
@@ -7560,6 +7790,9 @@
       </c>
       <c r="AB77" t="n">
         <v>0.5081937528597683</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>-1.495745290291192</v>
       </c>
     </row>
     <row r="78">
@@ -7616,13 +7849,13 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.338917049261011</v>
+        <v>3.422</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.05011772496703459</v>
+        <v>-0.05858720384093563</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0016185694681621</v>
+        <v>-0.002409845609047872</v>
       </c>
       <c r="T78" t="n">
         <v>29.01</v>
@@ -7652,6 +7885,9 @@
       </c>
       <c r="AB78" t="n">
         <v>0.47855134637752</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>-1.653052737327525</v>
       </c>
     </row>
     <row r="79">
@@ -7708,13 +7944,13 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.262749874551532</v>
+        <v>3.328</v>
       </c>
       <c r="R79" t="n">
-        <v>-0.04798832749499038</v>
+        <v>-0.06227013972744544</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0009323197603370286</v>
+        <v>-0.002281102675119218</v>
       </c>
       <c r="T79" t="n">
         <v>28.98</v>
@@ -7744,6 +7980,9 @@
       </c>
       <c r="AB79" t="n">
         <v>0.4621313762975864</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>-1.683074665953119</v>
       </c>
     </row>
     <row r="80">
@@ -7800,13 +8039,13 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.189332572827509</v>
+        <v>3.228</v>
       </c>
       <c r="R80" t="n">
-        <v>-0.04719784172966035</v>
+        <v>-0.06569895173441775</v>
       </c>
       <c r="S80" t="n">
-        <v>0.000160708791953186</v>
+        <v>-0.0005008970921516163</v>
       </c>
       <c r="T80" t="n">
         <v>28.995</v>
@@ -7836,6 +8075,9 @@
       </c>
       <c r="AB80" t="n">
         <v>0.4401129170107577</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>-1.703905076199792</v>
       </c>
     </row>
     <row r="81">
@@ -7892,13 +8134,13 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.12034244550554</v>
+        <v>3.13</v>
       </c>
       <c r="R81" t="n">
-        <v>-0.04744687385215529</v>
+        <v>-0.06405871905871907</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.000452126974844435</v>
+        <v>0.002412451169891895</v>
       </c>
       <c r="T81" t="n">
         <v>28.995</v>
@@ -7928,6 +8170,9 @@
       </c>
       <c r="AB81" t="n">
         <v>0.4148233066433576</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>-1.716994537241806</v>
       </c>
     </row>
     <row r="82">
@@ -7984,13 +8229,13 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.973859734392465</v>
+        <v>2.953</v>
       </c>
       <c r="R82" t="n">
-        <v>-0.05058953336990651</v>
+        <v>-0.04862236658369257</v>
       </c>
       <c r="S82" t="n">
-        <v>-0.001519770183040392</v>
+        <v>-0.001644053893141581</v>
       </c>
       <c r="T82" t="n">
         <v>28.98</v>
@@ -8020,6 +8265,9 @@
       </c>
       <c r="AB82" t="n">
         <v>0.3505176057965108</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>-1.727173376227441</v>
       </c>
     </row>
     <row r="83">
@@ -8076,13 +8324,13 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.815271320868581</v>
+        <v>2.836</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.05658408257420433</v>
+        <v>-0.0735314464133654</v>
       </c>
       <c r="S83" t="n">
-        <v>-0.002555149639045278</v>
+        <v>-0.003153424161267297</v>
       </c>
       <c r="T83" t="n">
         <v>28.995</v>
@@ -8112,6 +8360,9 @@
       </c>
       <c r="AB83" t="n">
         <v>0.2733429230022186</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>-1.719585285772643</v>
       </c>
     </row>
     <row r="84">
@@ -8168,13 +8419,13 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.726598804550801</v>
+        <v>2.698</v>
       </c>
       <c r="R84" t="n">
-        <v>-0.0608864521354604</v>
+        <v>-0.07436563436563448</v>
       </c>
       <c r="S84" t="n">
-        <v>-0.003047017038159183</v>
+        <v>0.01272827474437706</v>
       </c>
       <c r="T84" t="n">
         <v>29.01</v>
@@ -8204,6 +8455,9 @@
       </c>
       <c r="AB84" t="n">
         <v>0.2283843276209666</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>-1.708451505245871</v>
       </c>
     </row>
     <row r="85">
@@ -8260,13 +8514,13 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.660908107778384</v>
+        <v>2.632</v>
       </c>
       <c r="R85" t="n">
-        <v>-0.06423868457390691</v>
+        <v>-0.05134865134865096</v>
       </c>
       <c r="S85" t="n">
-        <v>-0.00333818760650087</v>
+        <v>0.03111359766892498</v>
       </c>
       <c r="T85" t="n">
         <v>28.98</v>
@@ -8296,6 +8550,9 @@
       </c>
       <c r="AB85" t="n">
         <v>0.1954476002213318</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>-1.698722903124076</v>
       </c>
     </row>
   </sheetData>
